--- a/reports/manual_image_qa.xlsx
+++ b/reports/manual_image_qa.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1841" uniqueCount="829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1841" uniqueCount="846">
   <si>
     <t xml:space="preserve">Destination ID</t>
   </si>
@@ -67,7 +67,7 @@
     <t xml:space="preserve">Chubu</t>
   </si>
   <si>
-    <t xml:space="preserve">https://images.unsplash.com/photo-1578637387939-43c525550085?auto=format&amp;fit=crop&amp;q=80&amp;w=1200</t>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/0/0c/Nagoya_Station_-_View_from_the_Main_Building_in_Nagoya_Campus_of_Aichi_University_2022-6-29.jpg/330px-Nagoya_Station_-_View_from_the_Main_Building_in_Nagoya_Campus_of_Aichi_University_2022-6-29.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">OK</t>
@@ -130,321 +130,330 @@
     <t xml:space="preserve">Kanagawa</t>
   </si>
   <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/b/b5/View_of_Mount_Fuji_from_Lake_Ashi.jpg/330px-View_of_Mount_Fuji_from_Lake_Ashi.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shirakawa-village</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shirakawa Village</t>
+  </si>
+  <si>
+    <t xml:space="preserve">village</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gifu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/a/a2/Shirakawa-go_%282017-07-22%29.jpg/1280px-Shirakawa-go_%282017-07-22%29.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abeno-harukas-300-osaka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abeno Harukas 300 (Osaka Skyline)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">viewpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">poi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/2/26/Abeno_Harukas_Osaka_Japan01-r.jpg/330px-Abeno_Harukas_Osaka_Japan01-r.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">akasaka-minato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akasaka (Minato)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Akasaka_skyline_201806.jpg/960px-Akasaka_skyline_201806.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">akihabara-chiyoda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akihabara (Chiyoda)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/6/60/Sotokanda%2C_Akihabara_Electric_Town_at_night_20231114.png/3840px-Sotokanda%2C_Akihabara_Electric_Town_at_night_20231114.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amanohashidate-kyoto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amanohashidate (Bridge to Heaven)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/9/9f/Amanohashidate_aerial_view_2026.jpg/3840px-Amanohashidate_aerial_view_2026.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">arima-onsen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arima Onsen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hyogo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/2/2c/170811_Rokko-Arima_Ropeway_Kobe_Japan00n.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">art-tower-mito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Art Tower Mito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ibaraki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/c/c2/Mito_Art_Tower.JPG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">asakusa-taito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asakusa (Taito)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/8/81/Day2-2_%2840909714314%29.jpg/3840px-Day2-2_%2840909714314%29.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ashigara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashigara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/0/0c/Wizyta_japo%C5%84skiego_kr%C4%85%C5%BCownika_Ashigara_w_Niemczech_%281-E-8502%29.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">atsuta-shrine-nagoya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atsuta Shrine (Nagoya)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/c/c6/Atsuta_Shrine.jpg/3840px-Atsuta_Shrine.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bitchu-matsuyama-castle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bitchu Matsuyama Castle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Okayama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chugoku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/9/9e/Bitchu_Matsuyama_Castle_1.JPG/1280px-Bitchu_Matsuyama_Castle_1.JPG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boso-peninsula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boso Peninsula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/3/3e/B%C5%8Ds%C5%8D_Peninsula_by_Sentinel-2%2C_2018-10-30.jpg/3840px-B%C5%8Ds%C5%8D_Peninsula_by_Sentinel-2%2C_2018-10-30.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chiba-city</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiba City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/d/d9/Chiba_montage.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chiba-nokogiriyama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nokogiriyama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/3/35/The_port_of_Kanaya.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chiba-port-tower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiba Port Tower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/1/15/Chiba_Port_Tower_2023-1.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chiba-sawara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sawara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/7/72/Inou-tadataka-house%2Ckatori-city%2Cjapan.JPG/330px-Inou-tadataka-house%2Ckatori-city%2Cjapan.JPG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chiba-yoro-valley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoro Valley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://images.unsplash.com/photo-1441974231531-c6227db76b6e?q=80&amp;w=1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chofu-tokyo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chofu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/1/17/Cyofushiyakusyo.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">choshi-chiba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Choshi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/c/c2/Choshi_Montage_2.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">disneyland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tokyo Disneyland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/4/4b/Tokyo_Disneyland_Cinderella_Castle_2023-07-02.jpg/1920px-Tokyo_Disneyland_Cinderella_Castle_2023-07-02.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">disneysea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DisneySea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/e/e4/Tokyo_Disney_Sea_Aerial_2019.png/330px-Tokyo_Disney_Sea_Aerial_2019.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">edo-castle-tokyo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edo Castle Ruins (Imperial Palace)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/5/5f/Edo_P_detail.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enoshima-island</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enoshima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/8/83/EnoshimaAeralPhoto1988JP14.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fuji-5-lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuji Five Lakes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yamanashi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/a/a7/Fuji_Five_Lakes_and_Mount_Fuji.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fukui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fukui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/b/bd/Skyline_of_Fukui_City02.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gala-yuzawa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gala Yuzawa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niigata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/73/F8_Tanigawa_79_Gala-Yuzawa_20060115.JPG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gero-onsen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gero Onsen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/1/15/260125_Gero_Onsen_Gero_Gifu_pref_Japan02s3.jpg/3840px-260125_Gero_Onsen_Gero_Gifu_pref_Japan02s3.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ghibli-museum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ghibli Museum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/4/45/Ghibli_Museum_2024.JPG/3840px-Ghibli_Museum_2024.JPG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gifu-castle-gifu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gifu Castle (Mt. Kinka)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/0/01/Gifu_Castle.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gifu-gujo-hachiman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gujo Hachiman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/1/12/Gujo_hachiman_castle_P8117454.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gifu-magome-juku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magome-juku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/d/dc/1_magome_juku_2024.jpg/3840px-1_magome_juku_2024.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gifu-shirakawa-go</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shirakawa-go</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://images.unsplash.com/photo-1507525428034-b723cf961d3e?auto=format&amp;fit=crop&amp;q=80&amp;w=1200</t>
   </si>
   <si>
-    <t xml:space="preserve">shirakawa-village</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shirakawa Village</t>
-  </si>
-  <si>
-    <t xml:space="preserve">village</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gifu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/a/a2/Shirakawa-go_%282017-07-22%29.jpg/1280px-Shirakawa-go_%282017-07-22%29.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abeno-harukas-300-osaka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abeno Harukas 300 (Osaka Skyline)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">viewpoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">poi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">akasaka-minato</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akasaka (Minato)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Akasaka_skyline_201806.jpg/960px-Akasaka_skyline_201806.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">akihabara-chiyoda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akihabara (Chiyoda)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/6/60/Sotokanda%2C_Akihabara_Electric_Town_at_night_20231114.png/3840px-Sotokanda%2C_Akihabara_Electric_Town_at_night_20231114.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amanohashidate-kyoto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amanohashidate (Bridge to Heaven)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/9/9f/Amanohashidate_aerial_view_2026.jpg/3840px-Amanohashidate_aerial_view_2026.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">arima-onsen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arima Onsen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hyogo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/2/2c/170811_Rokko-Arima_Ropeway_Kobe_Japan00n.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">art-tower-mito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Art Tower Mito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ibaraki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/c/c2/Mito_Art_Tower.JPG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">asakusa-taito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asakusa (Taito)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/8/81/Day2-2_%2840909714314%29.jpg/3840px-Day2-2_%2840909714314%29.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ashigara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashigara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/0/0c/Wizyta_japo%C5%84skiego_kr%C4%85%C5%BCownika_Ashigara_w_Niemczech_%281-E-8502%29.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">atsuta-shrine-nagoya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atsuta Shrine (Nagoya)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/c/c6/Atsuta_Shrine.jpg/3840px-Atsuta_Shrine.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bitchu-matsuyama-castle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bitchu Matsuyama Castle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Okayama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chugoku</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/9/9e/Bitchu_Matsuyama_Castle_1.JPG/1280px-Bitchu_Matsuyama_Castle_1.JPG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boso-peninsula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boso Peninsula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chiba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/3/3e/B%C5%8Ds%C5%8D_Peninsula_by_Sentinel-2%2C_2018-10-30.jpg/3840px-B%C5%8Ds%C5%8D_Peninsula_by_Sentinel-2%2C_2018-10-30.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chiba-city</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chiba City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/d/d9/Chiba_montage.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chiba-nokogiriyama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nokogiriyama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/3/35/The_port_of_Kanaya.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chiba-port-tower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chiba Port Tower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/1/15/Chiba_Port_Tower_2023-1.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chiba-sawara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sawara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://images.unsplash.com/photo-1540959733332-eab4deabeeaf?q=80&amp;w=1000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chiba-yoro-valley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoro Valley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://images.unsplash.com/photo-1441974231531-c6227db76b6e?q=80&amp;w=1000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chofu-tokyo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chofu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/1/17/Cyofushiyakusyo.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">choshi-chiba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Choshi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/c/c2/Choshi_Montage_2.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">disneyland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tokyo Disneyland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/4/4b/Tokyo_Disneyland_Cinderella_Castle_2023-07-02.jpg/1920px-Tokyo_Disneyland_Cinderella_Castle_2023-07-02.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">disneysea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DisneySea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">edo-castle-tokyo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edo Castle Ruins (Imperial Palace)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/5/5f/Edo_P_detail.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enoshima-island</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enoshima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/8/83/EnoshimaAeralPhoto1988JP14.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fuji-5-lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuji Five Lakes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yamanashi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/a/a7/Fuji_Five_Lakes_and_Mount_Fuji.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fukui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fukui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/b/bd/Skyline_of_Fukui_City02.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gala-yuzawa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gala Yuzawa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niigata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/73/F8_Tanigawa_79_Gala-Yuzawa_20060115.JPG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gero-onsen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gero Onsen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/1/15/260125_Gero_Onsen_Gero_Gifu_pref_Japan02s3.jpg/3840px-260125_Gero_Onsen_Gero_Gifu_pref_Japan02s3.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ghibli-museum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ghibli Museum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/4/45/Ghibli_Museum_2024.JPG/3840px-Ghibli_Museum_2024.JPG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gifu-castle-gifu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gifu Castle (Mt. Kinka)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/0/01/Gifu_Castle.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gifu-gujo-hachiman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gujo Hachiman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/1/12/Gujo_hachiman_castle_P8117454.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gifu-magome-juku</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magome-juku</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/d/dc/1_magome_juku_2024.jpg/3840px-1_magome_juku_2024.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gifu-shirakawa-go</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shirakawa-go</t>
-  </si>
-  <si>
     <t xml:space="preserve">ginza-urban</t>
   </si>
   <si>
@@ -463,6 +472,9 @@
     <t xml:space="preserve">Gunma</t>
   </si>
   <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/8/82/Ikaho_Onsen_03.jpg/250px-Ikaho_Onsen_03.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">gunma-kusatsu-onsen</t>
   </si>
   <si>
@@ -496,6 +508,9 @@
     <t xml:space="preserve">Hakkeijima Sea Paradise</t>
   </si>
   <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/b/b2/Yokohama_Hakkeijima_Sea_Paradise_-_01.jpg/330px-Yokohama_Hakkeijima_Sea_Paradise_-_01.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">hakodate-night-view</t>
   </si>
   <si>
@@ -514,147 +529,153 @@
     <t xml:space="preserve">Harry Potter Studio</t>
   </si>
   <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/5/55/Warner_Bros._Studio_Tour_Tokyo_entrance_%282%29_2023-08-17.jpg/330px-Warner_Bros._Studio_Tour_Tokyo_entrance_%282%29_2023-08-17.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">higashiyama-sky-tower-nagoya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Higashiyama Sky Tower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://images.unsplash.com/photo-1545569341-9eb8b30979d9?auto=format&amp;fit=crop&amp;q=80&amp;w=1200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hikone-castle-shiga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hikone Castle (National Treasure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shiga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/9/9f/Hikone_Castle_November_2016_-02.jpg/1280px-Hikone_Castle_November_2016_-02.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">himeji-castle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Himeji Castle (White Heron Castle)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/c/c1/Himeji_castle_in_may_2015.jpg/1280px-Himeji_castle_in_may_2015.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hirosaki-castle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hirosaki Castle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aomori</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tohoku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/f/f3/Hirosaki-castle_Aomori_with_Sakura_blossoms.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ibaraki-fukuroda-falls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fukuroda Falls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/8/80/Fukuroda_Falls_-_%E8%A2%8B%E7%94%B0%E3%81%AE%E6%BB%9D%28%E3%81%B5%E3%81%8F%E3%82%8D%E3%81%A0%E3%81%AE%E3%81%9F%E3%81%8D%29.jpg/3840px-Fukuroda_Falls_-_%E8%A2%8B%E7%94%B0%E3%81%AE%E6%BB%9D%28%E3%81%B5%E3%81%8F%E3%82%8D%E3%81%A0%E3%81%AE%E3%81%9F%E3%81%8D%29.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ibaraki-hitachi-seaside-park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hitachi Seaside Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/b/bc/Ferris_wheel_of_the_Hitachi_beach_park%2Chitachi-kaihin-koen%2Chitachinaka-city%2Cjapan.JPG/330px-Ferris_wheel_of_the_Hitachi_beach_park%2Chitachi-kaihin-koen%2Chitachinaka-city%2Cjapan.JPG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ibaraki-mount-tsukuba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mount Tsukuba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/2/2a/Mount_Tsukuba_seen_from_the_WSW_%282006%29.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ikebukuro-toshima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ikebukuro (Toshima)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Sunshine_60_Observatory_%40_Sunshine_Building_%40_Ikebukuro_%2811547419543%29.jpg/3840px-Sunshine_60_Observatory_%40_Sunshine_Building_%40_Ikebukuro_%2811547419543%29.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">imperial-palace-chiyoda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imperial Palace (Chiyoda)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/5/5f/Edo_P_detail.jpg/960px-Edo_P_detail.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ise-grand-shrine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ise Grand Shrine (Ise Jingu)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/8/8d/Naiku_04.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">izu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Izu Peninsula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shizuoka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/a/ad/Izu_Peninsula_Shizuoka_Japan_SRTM.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">izumo-taisha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Izumo Taisha Grand Shrine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shimane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/e/e6/Izumo-taisha14bs4592.jpg/3840px-Izumo-taisha14bs4592.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jogashima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miura Peninsula &amp; Jogashima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/d/d2/Miura_Peninsula_Kanagawa_Japan_SRTM.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joypolis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joypolis Odaiba</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://images.unsplash.com/photo-1503899036084-c55cdd92da26?auto=format&amp;fit=crop&amp;q=80&amp;w=1200</t>
   </si>
   <si>
-    <t xml:space="preserve">higashiyama-sky-tower-nagoya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Higashiyama Sky Tower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://images.unsplash.com/photo-1545569341-9eb8b30979d9?auto=format&amp;fit=crop&amp;q=80&amp;w=1200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hikone-castle-shiga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hikone Castle (National Treasure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shiga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/9/9f/Hikone_Castle_November_2016_-02.jpg/1280px-Hikone_Castle_November_2016_-02.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">himeji-castle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Himeji Castle (White Heron Castle)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/c/c1/Himeji_castle_in_may_2015.jpg/1280px-Himeji_castle_in_may_2015.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hirosaki-castle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hirosaki Castle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aomori</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tohoku</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/f/f3/Hirosaki-castle_Aomori_with_Sakura_blossoms.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ibaraki-fukuroda-falls</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fukuroda Falls</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/8/80/Fukuroda_Falls_-_%E8%A2%8B%E7%94%B0%E3%81%AE%E6%BB%9D%28%E3%81%B5%E3%81%8F%E3%82%8D%E3%81%A0%E3%81%AE%E3%81%9F%E3%81%8D%29.jpg/3840px-Fukuroda_Falls_-_%E8%A2%8B%E7%94%B0%E3%81%AE%E6%BB%9D%28%E3%81%B5%E3%81%8F%E3%82%8D%E3%81%A0%E3%81%AE%E3%81%9F%E3%81%8D%29.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ibaraki-hitachi-seaside-park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hitachi Seaside Park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ibaraki-mount-tsukuba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mount Tsukuba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/2/2a/Mount_Tsukuba_seen_from_the_WSW_%282006%29.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ikebukuro-toshima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ikebukuro (Toshima)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Sunshine_60_Observatory_%40_Sunshine_Building_%40_Ikebukuro_%2811547419543%29.jpg/3840px-Sunshine_60_Observatory_%40_Sunshine_Building_%40_Ikebukuro_%2811547419543%29.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">imperial-palace-chiyoda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imperial Palace (Chiyoda)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/5/5f/Edo_P_detail.jpg/960px-Edo_P_detail.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ise-grand-shrine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ise Grand Shrine (Ise Jingu)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/8/8d/Naiku_04.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">izu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Izu Peninsula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shizuoka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/a/ad/Izu_Peninsula_Shizuoka_Japan_SRTM.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">izumo-taisha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Izumo Taisha Grand Shrine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shimane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/e/e6/Izumo-taisha14bs4592.jpg/3840px-Izumo-taisha14bs4592.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jogashima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miura Peninsula &amp; Jogashima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/d/d2/Miura_Peninsula_Kanagawa_Japan_SRTM.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">joypolis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joypolis Odaiba</t>
-  </si>
-  <si>
     <t xml:space="preserve">kairakuen-mito</t>
   </si>
   <si>
@@ -889,6 +910,9 @@
     <t xml:space="preserve">Ehime</t>
   </si>
   <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/c/c9/Matsuyama_castle%28Iyo%296.JPG/330px-Matsuyama_castle%28Iyo%296.JPG</t>
+  </si>
+  <si>
     <t xml:space="preserve">mirai-tower-nagoya</t>
   </si>
   <si>
@@ -1087,6 +1111,9 @@
     <t xml:space="preserve">Odawara &amp; Manazuru</t>
   </si>
   <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/3/38/Aerial_views_of_Odawara_Japan.jpg/250px-Aerial_views_of_Odawara_Japan.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">okuhida</t>
   </si>
   <si>
@@ -1111,7 +1138,7 @@
     <t xml:space="preserve">Omiya Railway Museum</t>
   </si>
   <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/3/3a/Logo_of_Railway_museum%28Saitama%29.svg/1280px-Logo_of_Railway_museum%28Saitama%29.svg.png</t>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/0/0d/Namakubi0kei.JPG/330px-Namakubi0kei.JPG</t>
   </si>
   <si>
     <t xml:space="preserve">osaka-castle</t>
@@ -1120,6 +1147,9 @@
     <t xml:space="preserve">Osaka Castle (Osaka-jo)</t>
   </si>
   <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/8/84/Osaka-zu_byobu.jpg/500px-Osaka-zu_byobu.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">oze-national-park</t>
   </si>
   <si>
@@ -1216,6 +1246,9 @@
     <t xml:space="preserve">Takaoka</t>
   </si>
   <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/c/c4/Takaoka_montage.JPG/330px-Takaoka_montage.JPG</t>
+  </si>
+  <si>
     <t xml:space="preserve">takato-castle-nagano</t>
   </si>
   <si>
@@ -1240,12 +1273,18 @@
     <t xml:space="preserve">teamLab Planets</t>
   </si>
   <si>
+    <t xml:space="preserve">https://images.unsplash.com/photo-1593073862407-a3ce22748763?w=500&amp;auto=format&amp;fit=crop&amp;q=60&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxzZWFyY2h8Mnx8dGVhbWxhYiUyMHBsYW5ldHMlMjB0b2t5b3xlbnwwfHwwfHx8MA%3D%3D</t>
+  </si>
+  <si>
     <t xml:space="preserve">toki-messe-tower-niigata</t>
   </si>
   <si>
     <t xml:space="preserve">Befco Bakauke Observatory (Toki Messe)</t>
   </si>
   <si>
+    <t xml:space="preserve">https://media.istockphoto.com/id/1707386560/ja/%E3%82%B9%E3%83%88%E3%83%83%E3%82%AF%E3%83%95%E3%82%A9%E3%83%88/%E3%82%B9%E3%83%AD%E3%83%90%E3%82%AD%E3%82%A2%E3%81%AE%E3%82%BF%E3%83%88%E3%83%A9%E5%B1%B1%E3%81%AB%E3%81%82%E3%82%8B%E5%A4%A9%E6%96%87%E8%A6%B3%E6%B8%AC%E8%80%85%E3%81%AE%E5%BB%BA%E7%89%A9.jpg?s=2048x2048&amp;w=is&amp;k=20&amp;c=PGN1QnPNdRCMtsy6jNAm4F_J59flQUHKgfV5UhNrrN4=</t>
+  </si>
+  <si>
     <t xml:space="preserve">tokyo-hinohara</t>
   </si>
   <si>
@@ -1333,6 +1372,9 @@
     <t xml:space="preserve">Ueno (Taito)</t>
   </si>
   <si>
+    <t xml:space="preserve">https://images.unsplash.com/photo-1556326059-3cfc41f90fb1?q=80&amp;w=1170&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
     <t xml:space="preserve">ushiku-daibutsu</t>
   </si>
   <si>
@@ -1348,6 +1390,9 @@
     <t xml:space="preserve">Utsunomiya &amp; Oya</t>
   </si>
   <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/7/7e/Utsunomiya_montage.jpg/250px-Utsunomiya_montage.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">uwajima-castle</t>
   </si>
   <si>
@@ -1393,6 +1438,9 @@
     <t xml:space="preserve">Yokohama Landmark Tower (Sky Garden)</t>
   </si>
   <si>
+    <t xml:space="preserve">https://images.unsplash.com/photo-1609375855883-411e45d77365?q=80&amp;w=1074&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
     <t xml:space="preserve">yokohama-marine-tower</t>
   </si>
   <si>
@@ -1940,6 +1988,9 @@
   </si>
   <si>
     <t xml:space="preserve">Fujikawaguchiko Town</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://images.unsplash.com/photo-1749498682646-45e7c11506ec?q=80&amp;w=1170&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
   </si>
   <si>
     <t xml:space="preserve">matsumoto-city</t>
@@ -2927,7 +2978,7 @@
         <v>20</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H8" s="0" t="s">
         <v>16</v>
@@ -2935,10 +2986,10 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>29</v>
@@ -2947,7 +2998,7 @@
         <v>30</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H9" s="0" t="s">
         <v>16</v>
@@ -2955,10 +3006,10 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E10" s="0" t="s">
         <v>29</v>
@@ -2967,7 +3018,7 @@
         <v>30</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H10" s="0" t="s">
         <v>16</v>
@@ -2975,10 +3026,10 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E11" s="0" t="s">
         <v>19</v>
@@ -2987,7 +3038,7 @@
         <v>20</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H11" s="0" t="s">
         <v>16</v>
@@ -2995,19 +3046,19 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F12" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H12" s="0" t="s">
         <v>16</v>
@@ -3015,19 +3066,19 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F13" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H13" s="0" t="s">
         <v>16</v>
@@ -3035,10 +3086,10 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E14" s="0" t="s">
         <v>29</v>
@@ -3047,7 +3098,7 @@
         <v>30</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H14" s="0" t="s">
         <v>16</v>
@@ -3055,10 +3106,10 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E15" s="0" t="s">
         <v>35</v>
@@ -3067,7 +3118,7 @@
         <v>30</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H15" s="0" t="s">
         <v>16</v>
@@ -3075,10 +3126,10 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E16" s="0" t="s">
         <v>13</v>
@@ -3087,7 +3138,7 @@
         <v>14</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H16" s="0" t="s">
         <v>16</v>
@@ -3095,19 +3146,19 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H17" s="0" t="s">
         <v>16</v>
@@ -3115,19 +3166,19 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F18" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H18" s="0" t="s">
         <v>16</v>
@@ -3135,10 +3186,10 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>11</v>
@@ -3147,13 +3198,13 @@
         <v>12</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F19" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H19" s="0" t="s">
         <v>16</v>
@@ -3161,19 +3212,19 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F20" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H20" s="0" t="s">
         <v>16</v>
@@ -3181,19 +3232,19 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F21" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H21" s="0" t="s">
         <v>16</v>
@@ -3201,19 +3252,19 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F22" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H22" s="0" t="s">
         <v>16</v>
@@ -3221,19 +3272,19 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F23" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H23" s="0" t="s">
         <v>16</v>
@@ -3241,10 +3292,10 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E24" s="0" t="s">
         <v>29</v>
@@ -3253,7 +3304,7 @@
         <v>30</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H24" s="0" t="s">
         <v>16</v>
@@ -3261,19 +3312,19 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F25" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H25" s="0" t="s">
         <v>16</v>
@@ -3281,19 +3332,19 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F26" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H26" s="0" t="s">
         <v>16</v>
@@ -3301,19 +3352,19 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F27" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="H27" s="0" t="s">
         <v>16</v>
@@ -3321,10 +3372,10 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E28" s="0" t="s">
         <v>29</v>
@@ -3333,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H28" s="0" t="s">
         <v>16</v>
@@ -3341,10 +3392,10 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E29" s="0" t="s">
         <v>35</v>
@@ -3353,7 +3404,7 @@
         <v>30</v>
       </c>
       <c r="G29" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H29" s="0" t="s">
         <v>16</v>
@@ -3361,19 +3412,19 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F30" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H30" s="0" t="s">
         <v>16</v>
@@ -3381,19 +3432,19 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F31" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H31" s="0" t="s">
         <v>16</v>
@@ -3401,19 +3452,19 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F32" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G32" s="0" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H32" s="0" t="s">
         <v>16</v>
@@ -3421,10 +3472,10 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E33" s="0" t="s">
         <v>40</v>
@@ -3433,7 +3484,7 @@
         <v>14</v>
       </c>
       <c r="G33" s="0" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H33" s="0" t="s">
         <v>16</v>
@@ -3441,10 +3492,10 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E34" s="0" t="s">
         <v>29</v>
@@ -3453,7 +3504,7 @@
         <v>30</v>
       </c>
       <c r="G34" s="0" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H34" s="0" t="s">
         <v>16</v>
@@ -3461,10 +3512,10 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E35" s="0" t="s">
         <v>40</v>
@@ -3473,7 +3524,7 @@
         <v>14</v>
       </c>
       <c r="G35" s="0" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H35" s="0" t="s">
         <v>16</v>
@@ -3481,10 +3532,10 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E36" s="0" t="s">
         <v>40</v>
@@ -3493,7 +3544,7 @@
         <v>14</v>
       </c>
       <c r="G36" s="0" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H36" s="0" t="s">
         <v>16</v>
@@ -3501,10 +3552,10 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E37" s="0" t="s">
         <v>40</v>
@@ -3513,7 +3564,7 @@
         <v>14</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H37" s="0" t="s">
         <v>16</v>
@@ -3521,10 +3572,10 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E38" s="0" t="s">
         <v>40</v>
@@ -3533,7 +3584,7 @@
         <v>14</v>
       </c>
       <c r="G38" s="0" t="s">
-        <v>36</v>
+        <v>143</v>
       </c>
       <c r="H38" s="0" t="s">
         <v>16</v>
@@ -3541,10 +3592,10 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E39" s="0" t="s">
         <v>29</v>
@@ -3553,7 +3604,7 @@
         <v>30</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H39" s="0" t="s">
         <v>16</v>
@@ -3561,19 +3612,19 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F40" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>36</v>
+        <v>150</v>
       </c>
       <c r="H40" s="0" t="s">
         <v>16</v>
@@ -3581,19 +3632,19 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F41" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G41" s="0" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H41" s="0" t="s">
         <v>16</v>
@@ -3601,19 +3652,19 @@
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F42" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="H42" s="0" t="s">
         <v>16</v>
@@ -3621,10 +3672,10 @@
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E43" s="0" t="s">
         <v>29</v>
@@ -3633,7 +3684,7 @@
         <v>30</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="H43" s="0" t="s">
         <v>16</v>
@@ -3641,10 +3692,10 @@
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E44" s="0" t="s">
         <v>35</v>
@@ -3653,7 +3704,7 @@
         <v>30</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>36</v>
+        <v>162</v>
       </c>
       <c r="H44" s="0" t="s">
         <v>16</v>
@@ -3661,19 +3712,19 @@
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="H45" s="0" t="s">
         <v>16</v>
@@ -3681,10 +3732,10 @@
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E46" s="0" t="s">
         <v>29</v>
@@ -3693,7 +3744,7 @@
         <v>30</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="H46" s="0" t="s">
         <v>16</v>
@@ -3701,10 +3752,10 @@
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="E47" s="0" t="s">
         <v>13</v>
@@ -3713,7 +3764,7 @@
         <v>14</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="H47" s="0" t="s">
         <v>16</v>
@@ -3721,19 +3772,19 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="F48" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="H48" s="0" t="s">
         <v>16</v>
@@ -3741,19 +3792,19 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F49" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G49" s="0" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="H49" s="0" t="s">
         <v>16</v>
@@ -3761,19 +3812,19 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="H50" s="0" t="s">
         <v>16</v>
@@ -3781,19 +3832,19 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F51" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G51" s="0" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="H51" s="0" t="s">
         <v>16</v>
@@ -3801,19 +3852,19 @@
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F52" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="H52" s="0" t="s">
         <v>16</v>
@@ -3821,19 +3872,19 @@
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F53" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="H53" s="0" t="s">
         <v>16</v>
@@ -3841,10 +3892,10 @@
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="E54" s="0" t="s">
         <v>29</v>
@@ -3853,7 +3904,7 @@
         <v>30</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="H54" s="0" t="s">
         <v>16</v>
@@ -3861,10 +3912,10 @@
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E55" s="0" t="s">
         <v>29</v>
@@ -3873,7 +3924,7 @@
         <v>30</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="H55" s="0" t="s">
         <v>16</v>
@@ -3881,19 +3932,19 @@
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F56" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="H56" s="0" t="s">
         <v>16</v>
@@ -3901,19 +3952,19 @@
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="F57" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="H57" s="0" t="s">
         <v>16</v>
@@ -3921,19 +3972,19 @@
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="H58" s="0" t="s">
         <v>16</v>
@@ -3941,10 +3992,10 @@
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E59" s="0" t="s">
         <v>35</v>
@@ -3953,7 +4004,7 @@
         <v>30</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="H59" s="0" t="s">
         <v>16</v>
@@ -3961,10 +4012,10 @@
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E60" s="0" t="s">
         <v>29</v>
@@ -3973,7 +4024,7 @@
         <v>30</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>164</v>
+        <v>217</v>
       </c>
       <c r="H60" s="0" t="s">
         <v>16</v>
@@ -3981,19 +4032,19 @@
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F61" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="H61" s="0" t="s">
         <v>16</v>
@@ -4001,19 +4052,19 @@
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="F62" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="H62" s="0" t="s">
         <v>16</v>
@@ -4021,19 +4072,19 @@
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="F63" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G63" s="0" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="H63" s="0" t="s">
         <v>16</v>
@@ -4041,19 +4092,19 @@
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="F64" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="H64" s="0" t="s">
         <v>16</v>
@@ -4061,19 +4112,19 @@
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="F65" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G65" s="0" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H65" s="0" t="s">
         <v>16</v>
@@ -4081,13 +4132,13 @@
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="F66" s="0" t="s">
         <v>30</v>
@@ -4101,19 +4152,19 @@
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F67" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G67" s="0" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="H67" s="0" t="s">
         <v>16</v>
@@ -4121,19 +4172,19 @@
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="F68" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="H68" s="0" t="s">
         <v>16</v>
@@ -4141,19 +4192,19 @@
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="F69" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G69" s="0" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="H69" s="0" t="s">
         <v>16</v>
@@ -4161,19 +4212,19 @@
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F70" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="H70" s="0" t="s">
         <v>16</v>
@@ -4181,19 +4232,19 @@
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>36</v>
+        <v>143</v>
       </c>
       <c r="H71" s="0" t="s">
         <v>16</v>
@@ -4201,19 +4252,19 @@
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="H72" s="0" t="s">
         <v>16</v>
@@ -4221,19 +4272,19 @@
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="G73" s="0" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="H73" s="0" t="s">
         <v>16</v>
@@ -4241,19 +4292,19 @@
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="F74" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="H74" s="0" t="s">
         <v>16</v>
@@ -4261,10 +4312,10 @@
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="E75" s="0" t="s">
         <v>19</v>
@@ -4273,7 +4324,7 @@
         <v>20</v>
       </c>
       <c r="G75" s="0" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="H75" s="0" t="s">
         <v>16</v>
@@ -4281,19 +4332,19 @@
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="F76" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="H76" s="0" t="s">
         <v>16</v>
@@ -4301,10 +4352,10 @@
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="E77" s="0" t="s">
         <v>35</v>
@@ -4313,7 +4364,7 @@
         <v>30</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="H77" s="0" t="s">
         <v>16</v>
@@ -4321,10 +4372,10 @@
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="E78" s="0" t="s">
         <v>29</v>
@@ -4333,7 +4384,7 @@
         <v>30</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="H78" s="0" t="s">
         <v>16</v>
@@ -4341,19 +4392,19 @@
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="H79" s="0" t="s">
         <v>16</v>
@@ -4361,19 +4412,19 @@
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F80" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="H80" s="0" t="s">
         <v>16</v>
@@ -4381,19 +4432,19 @@
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G81" s="0" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="H81" s="0" t="s">
         <v>16</v>
@@ -4401,19 +4452,19 @@
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="H82" s="0" t="s">
         <v>16</v>
@@ -4421,19 +4472,19 @@
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="G83" s="0" t="s">
-        <v>36</v>
+        <v>296</v>
       </c>
       <c r="H83" s="0" t="s">
         <v>16</v>
@@ -4441,10 +4492,10 @@
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="E84" s="0" t="s">
         <v>13</v>
@@ -4453,7 +4504,7 @@
         <v>14</v>
       </c>
       <c r="G84" s="0" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="H84" s="0" t="s">
         <v>16</v>
@@ -4461,19 +4512,19 @@
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F85" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="H85" s="0" t="s">
         <v>16</v>
@@ -4481,19 +4532,19 @@
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G86" s="0" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="H86" s="0" t="s">
         <v>16</v>
@@ -4501,19 +4552,19 @@
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F87" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G87" s="0" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="H87" s="0" t="s">
         <v>16</v>
@@ -4521,19 +4572,19 @@
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="E88" s="0" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="F88" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G88" s="0" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H88" s="0" t="s">
         <v>16</v>
@@ -4541,19 +4592,19 @@
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="E89" s="0" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="G89" s="0" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="H89" s="0" t="s">
         <v>16</v>
@@ -4561,19 +4612,19 @@
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="E90" s="0" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="F90" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G90" s="0" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="H90" s="0" t="s">
         <v>16</v>
@@ -4581,19 +4632,19 @@
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="E91" s="0" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="F91" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G91" s="0" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="H91" s="0" t="s">
         <v>16</v>
@@ -4601,19 +4652,19 @@
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="E92" s="0" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="F92" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G92" s="0" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="H92" s="0" t="s">
         <v>16</v>
@@ -4621,10 +4672,10 @@
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="C93" s="0" t="s">
         <v>11</v>
@@ -4633,13 +4684,13 @@
         <v>12</v>
       </c>
       <c r="E93" s="0" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="F93" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G93" s="0" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="H93" s="0" t="s">
         <v>16</v>
@@ -4647,19 +4698,19 @@
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="E94" s="0" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="F94" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G94" s="0" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="H94" s="0" t="s">
         <v>16</v>
@@ -4667,19 +4718,19 @@
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="E95" s="0" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="F95" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G95" s="0" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="H95" s="0" t="s">
         <v>16</v>
@@ -4687,19 +4738,19 @@
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="E96" s="0" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="F96" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G96" s="0" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="H96" s="0" t="s">
         <v>16</v>
@@ -4707,19 +4758,19 @@
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="E97" s="0" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="F97" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G97" s="0" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="H97" s="0" t="s">
         <v>16</v>
@@ -4727,10 +4778,10 @@
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="E98" s="0" t="s">
         <v>13</v>
@@ -4739,7 +4790,7 @@
         <v>14</v>
       </c>
       <c r="G98" s="0" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="H98" s="0" t="s">
         <v>16</v>
@@ -4747,19 +4798,19 @@
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="F99" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G99" s="0" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="H99" s="0" t="s">
         <v>16</v>
@@ -4767,10 +4818,10 @@
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="E100" s="0" t="s">
         <v>19</v>
@@ -4779,7 +4830,7 @@
         <v>20</v>
       </c>
       <c r="G100" s="0" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="H100" s="0" t="s">
         <v>16</v>
@@ -4787,19 +4838,19 @@
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="E101" s="0" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="F101" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G101" s="0" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="H101" s="0" t="s">
         <v>16</v>
@@ -4807,19 +4858,19 @@
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="E102" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F102" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G102" s="0" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="H102" s="0" t="s">
         <v>16</v>
@@ -4827,10 +4878,10 @@
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="E103" s="0" t="s">
         <v>29</v>
@@ -4839,7 +4890,7 @@
         <v>30</v>
       </c>
       <c r="G103" s="0" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="H103" s="0" t="s">
         <v>16</v>
@@ -4847,10 +4898,10 @@
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="E104" s="0" t="s">
         <v>35</v>
@@ -4859,7 +4910,7 @@
         <v>30</v>
       </c>
       <c r="G104" s="0" t="s">
-        <v>15</v>
+        <v>363</v>
       </c>
       <c r="H104" s="0" t="s">
         <v>16</v>
@@ -4867,10 +4918,10 @@
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="E105" s="0" t="s">
         <v>40</v>
@@ -4879,7 +4930,7 @@
         <v>14</v>
       </c>
       <c r="G105" s="0" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="H105" s="0" t="s">
         <v>16</v>
@@ -4887,10 +4938,10 @@
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="E106" s="0" t="s">
         <v>29</v>
@@ -4899,7 +4950,7 @@
         <v>30</v>
       </c>
       <c r="G106" s="0" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="H106" s="0" t="s">
         <v>16</v>
@@ -4907,19 +4958,19 @@
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="E107" s="0" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="F107" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G107" s="0" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="H107" s="0" t="s">
         <v>16</v>
@@ -4927,10 +4978,10 @@
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="E108" s="0" t="s">
         <v>24</v>
@@ -4939,7 +4990,7 @@
         <v>20</v>
       </c>
       <c r="G108" s="0" t="s">
-        <v>36</v>
+        <v>375</v>
       </c>
       <c r="H108" s="0" t="s">
         <v>16</v>
@@ -4947,19 +4998,19 @@
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="E109" s="0" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F109" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G109" s="0" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="H109" s="0" t="s">
         <v>16</v>
@@ -4967,10 +5018,10 @@
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="E110" s="0" t="s">
         <v>29</v>
@@ -4979,7 +5030,7 @@
         <v>30</v>
       </c>
       <c r="G110" s="0" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="H110" s="0" t="s">
         <v>16</v>
@@ -4987,19 +5038,19 @@
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="E111" s="0" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F111" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G111" s="0" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="H111" s="0" t="s">
         <v>16</v>
@@ -5007,10 +5058,10 @@
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="0" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="C112" s="0" t="s">
         <v>11</v>
@@ -5019,13 +5070,13 @@
         <v>12</v>
       </c>
       <c r="E112" s="0" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="F112" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G112" s="0" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="H112" s="0" t="s">
         <v>16</v>
@@ -5033,19 +5084,19 @@
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="E113" s="0" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="F113" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G113" s="0" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="H113" s="0" t="s">
         <v>16</v>
@@ -5053,19 +5104,19 @@
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="0" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="E114" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F114" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G114" s="0" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="H114" s="0" t="s">
         <v>16</v>
@@ -5073,10 +5124,10 @@
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="0" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="E115" s="0" t="s">
         <v>29</v>
@@ -5085,7 +5136,7 @@
         <v>30</v>
       </c>
       <c r="G115" s="0" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="H115" s="0" t="s">
         <v>16</v>
@@ -5093,10 +5144,10 @@
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="E116" s="0" t="s">
         <v>29</v>
@@ -5105,7 +5156,7 @@
         <v>30</v>
       </c>
       <c r="G116" s="0" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="H116" s="0" t="s">
         <v>16</v>
@@ -5113,10 +5164,10 @@
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="E117" s="0" t="s">
         <v>29</v>
@@ -5125,7 +5176,7 @@
         <v>30</v>
       </c>
       <c r="G117" s="0" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="H117" s="0" t="s">
         <v>16</v>
@@ -5133,10 +5184,10 @@
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="E118" s="0" t="s">
         <v>29</v>
@@ -5145,7 +5196,7 @@
         <v>30</v>
       </c>
       <c r="G118" s="0" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="H118" s="0" t="s">
         <v>16</v>
@@ -5153,19 +5204,19 @@
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="E119" s="0" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="F119" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G119" s="0" t="s">
-        <v>36</v>
+        <v>408</v>
       </c>
       <c r="H119" s="0" t="s">
         <v>16</v>
@@ -5173,19 +5224,19 @@
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="E120" s="0" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="F120" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G120" s="0" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="H120" s="0" t="s">
         <v>16</v>
@@ -5193,19 +5244,19 @@
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="E121" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F121" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G121" s="0" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="H121" s="0" t="s">
         <v>16</v>
@@ -5213,10 +5264,10 @@
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="0" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="E122" s="0" t="s">
         <v>29</v>
@@ -5225,7 +5276,7 @@
         <v>30</v>
       </c>
       <c r="G122" s="0" t="s">
-        <v>36</v>
+        <v>417</v>
       </c>
       <c r="H122" s="0" t="s">
         <v>16</v>
@@ -5233,19 +5284,19 @@
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="E123" s="0" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F123" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G123" s="0" t="s">
-        <v>36</v>
+        <v>420</v>
       </c>
       <c r="H123" s="0" t="s">
         <v>16</v>
@@ -5253,10 +5304,10 @@
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="0" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="E124" s="0" t="s">
         <v>29</v>
@@ -5265,7 +5316,7 @@
         <v>30</v>
       </c>
       <c r="G124" s="0" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="H124" s="0" t="s">
         <v>16</v>
@@ -5273,10 +5324,10 @@
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="0" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="E125" s="0" t="s">
         <v>29</v>
@@ -5285,7 +5336,7 @@
         <v>30</v>
       </c>
       <c r="G125" s="0" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="H125" s="0" t="s">
         <v>16</v>
@@ -5293,10 +5344,10 @@
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="0" t="s">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="E126" s="0" t="s">
         <v>29</v>
@@ -5305,7 +5356,7 @@
         <v>30</v>
       </c>
       <c r="G126" s="0" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="H126" s="0" t="s">
         <v>16</v>
@@ -5313,10 +5364,10 @@
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="0" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="E127" s="0" t="s">
         <v>29</v>
@@ -5325,7 +5376,7 @@
         <v>30</v>
       </c>
       <c r="G127" s="0" t="s">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="H127" s="0" t="s">
         <v>16</v>
@@ -5333,10 +5384,10 @@
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="0" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="E128" s="0" t="s">
         <v>29</v>
@@ -5345,7 +5396,7 @@
         <v>30</v>
       </c>
       <c r="G128" s="0" t="s">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="H128" s="0" t="s">
         <v>16</v>
@@ -5353,10 +5404,10 @@
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="0" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="E129" s="0" t="s">
         <v>29</v>
@@ -5365,7 +5416,7 @@
         <v>30</v>
       </c>
       <c r="G129" s="0" t="s">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="H129" s="0" t="s">
         <v>16</v>
@@ -5373,10 +5424,10 @@
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="0" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="B130" s="0" t="s">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="E130" s="0" t="s">
         <v>29</v>
@@ -5385,7 +5436,7 @@
         <v>30</v>
       </c>
       <c r="G130" s="0" t="s">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="H130" s="0" t="s">
         <v>16</v>
@@ -5393,19 +5444,19 @@
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="0" t="s">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="E131" s="0" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="F131" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G131" s="0" t="s">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="H131" s="0" t="s">
         <v>16</v>
@@ -5413,19 +5464,19 @@
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="0" t="s">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="B132" s="0" t="s">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c r="E132" s="0" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="F132" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G132" s="0" t="s">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="H132" s="0" t="s">
         <v>16</v>
@@ -5433,10 +5484,10 @@
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="s">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="E133" s="0" t="s">
         <v>29</v>
@@ -5445,7 +5496,7 @@
         <v>30</v>
       </c>
       <c r="G133" s="0" t="s">
-        <v>36</v>
+        <v>450</v>
       </c>
       <c r="H133" s="0" t="s">
         <v>16</v>
@@ -5453,19 +5504,19 @@
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="E134" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F134" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G134" s="0" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="H134" s="0" t="s">
         <v>16</v>
@@ -5473,19 +5524,19 @@
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="0" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="E135" s="0" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="F135" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G135" s="0" t="s">
-        <v>36</v>
+        <v>456</v>
       </c>
       <c r="H135" s="0" t="s">
         <v>16</v>
@@ -5493,19 +5544,19 @@
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="0" t="s">
-        <v>442</v>
+        <v>457</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>443</v>
+        <v>458</v>
       </c>
       <c r="E136" s="0" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="F136" s="0" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="G136" s="0" t="s">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="H136" s="0" t="s">
         <v>16</v>
@@ -5513,19 +5564,19 @@
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="0" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>446</v>
+        <v>461</v>
       </c>
       <c r="E137" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F137" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G137" s="0" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="H137" s="0" t="s">
         <v>16</v>
@@ -5533,19 +5584,19 @@
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="0" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="B138" s="0" t="s">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="E138" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F138" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G138" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H138" s="0" t="s">
         <v>16</v>
@@ -5553,19 +5604,19 @@
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="0" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>450</v>
+        <v>465</v>
       </c>
       <c r="E139" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F139" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G139" s="0" t="s">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="H139" s="0" t="s">
         <v>16</v>
@@ -5573,10 +5624,10 @@
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="0" t="s">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="C140" s="0" t="s">
         <v>11</v>
@@ -5591,7 +5642,7 @@
         <v>30</v>
       </c>
       <c r="G140" s="0" t="s">
-        <v>454</v>
+        <v>469</v>
       </c>
       <c r="H140" s="0" t="s">
         <v>16</v>
@@ -5599,10 +5650,10 @@
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="0" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="E141" s="0" t="s">
         <v>35</v>
@@ -5611,7 +5662,7 @@
         <v>30</v>
       </c>
       <c r="G141" s="0" t="s">
-        <v>36</v>
+        <v>472</v>
       </c>
       <c r="H141" s="0" t="s">
         <v>16</v>
@@ -5619,10 +5670,10 @@
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="0" t="s">
-        <v>457</v>
+        <v>473</v>
       </c>
       <c r="B142" s="0" t="s">
-        <v>458</v>
+        <v>474</v>
       </c>
       <c r="E142" s="0" t="s">
         <v>35</v>
@@ -5631,7 +5682,7 @@
         <v>30</v>
       </c>
       <c r="G142" s="0" t="s">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="H142" s="0" t="s">
         <v>16</v>
@@ -5639,10 +5690,10 @@
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="0" t="s">
-        <v>460</v>
+        <v>476</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>461</v>
+        <v>477</v>
       </c>
       <c r="E143" s="0" t="s">
         <v>29</v>
@@ -5651,7 +5702,7 @@
         <v>30</v>
       </c>
       <c r="G143" s="0" t="s">
-        <v>462</v>
+        <v>478</v>
       </c>
       <c r="H143" s="0" t="s">
         <v>16</v>
@@ -5659,10 +5710,10 @@
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="0" t="s">
-        <v>463</v>
+        <v>479</v>
       </c>
       <c r="B144" s="0" t="s">
-        <v>464</v>
+        <v>480</v>
       </c>
       <c r="E144" s="0" t="s">
         <v>35</v>
@@ -5671,7 +5722,7 @@
         <v>30</v>
       </c>
       <c r="G144" s="0" t="s">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="H144" s="0" t="s">
         <v>16</v>
@@ -5679,10 +5730,10 @@
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="0" t="s">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="B145" s="0" t="s">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="C145" s="0" t="s">
         <v>28</v>
@@ -5697,7 +5748,7 @@
         <v>30</v>
       </c>
       <c r="G145" s="0" t="s">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="H145" s="0" t="s">
         <v>16</v>
@@ -5705,10 +5756,10 @@
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="0" t="s">
-        <v>469</v>
+        <v>485</v>
       </c>
       <c r="B146" s="0" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="C146" s="0" t="s">
         <v>28</v>
@@ -5723,7 +5774,7 @@
         <v>30</v>
       </c>
       <c r="G146" s="0" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H146" s="0" t="s">
         <v>16</v>
@@ -5731,10 +5782,10 @@
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="0" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="B147" s="0" t="s">
-        <v>472</v>
+        <v>488</v>
       </c>
       <c r="C147" s="0" t="s">
         <v>28</v>
@@ -5749,7 +5800,7 @@
         <v>30</v>
       </c>
       <c r="G147" s="0" t="s">
-        <v>473</v>
+        <v>489</v>
       </c>
       <c r="H147" s="0" t="s">
         <v>16</v>
@@ -5757,10 +5808,10 @@
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="0" t="s">
-        <v>474</v>
+        <v>490</v>
       </c>
       <c r="B148" s="0" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="C148" s="0" t="s">
         <v>28</v>
@@ -5775,7 +5826,7 @@
         <v>30</v>
       </c>
       <c r="G148" s="0" t="s">
-        <v>476</v>
+        <v>492</v>
       </c>
       <c r="H148" s="0" t="s">
         <v>16</v>
@@ -5783,10 +5834,10 @@
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="0" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="B149" s="0" t="s">
-        <v>478</v>
+        <v>494</v>
       </c>
       <c r="C149" s="0" t="s">
         <v>28</v>
@@ -5801,7 +5852,7 @@
         <v>30</v>
       </c>
       <c r="G149" s="0" t="s">
-        <v>479</v>
+        <v>495</v>
       </c>
       <c r="H149" s="0" t="s">
         <v>16</v>
@@ -5809,10 +5860,10 @@
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="0" t="s">
-        <v>480</v>
+        <v>496</v>
       </c>
       <c r="B150" s="0" t="s">
-        <v>481</v>
+        <v>497</v>
       </c>
       <c r="C150" s="0" t="s">
         <v>28</v>
@@ -5827,7 +5878,7 @@
         <v>30</v>
       </c>
       <c r="G150" s="0" t="s">
-        <v>482</v>
+        <v>498</v>
       </c>
       <c r="H150" s="0" t="s">
         <v>16</v>
@@ -5835,10 +5886,10 @@
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="0" t="s">
-        <v>483</v>
+        <v>499</v>
       </c>
       <c r="B151" s="0" t="s">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="C151" s="0" t="s">
         <v>28</v>
@@ -5853,7 +5904,7 @@
         <v>30</v>
       </c>
       <c r="G151" s="0" t="s">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="H151" s="0" t="s">
         <v>16</v>
@@ -5861,10 +5912,10 @@
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="0" t="s">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="B152" s="0" t="s">
-        <v>486</v>
+        <v>502</v>
       </c>
       <c r="C152" s="0" t="s">
         <v>28</v>
@@ -5879,7 +5930,7 @@
         <v>30</v>
       </c>
       <c r="G152" s="0" t="s">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c r="H152" s="0" t="s">
         <v>16</v>
@@ -5887,10 +5938,10 @@
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="0" t="s">
-        <v>488</v>
+        <v>504</v>
       </c>
       <c r="B153" s="0" t="s">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="C153" s="0" t="s">
         <v>28</v>
@@ -5905,7 +5956,7 @@
         <v>30</v>
       </c>
       <c r="G153" s="0" t="s">
-        <v>490</v>
+        <v>506</v>
       </c>
       <c r="H153" s="0" t="s">
         <v>16</v>
@@ -5913,10 +5964,10 @@
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="0" t="s">
-        <v>491</v>
+        <v>507</v>
       </c>
       <c r="B154" s="0" t="s">
-        <v>492</v>
+        <v>508</v>
       </c>
       <c r="C154" s="0" t="s">
         <v>28</v>
@@ -5931,7 +5982,7 @@
         <v>30</v>
       </c>
       <c r="G154" s="0" t="s">
-        <v>493</v>
+        <v>509</v>
       </c>
       <c r="H154" s="0" t="s">
         <v>16</v>
@@ -5939,10 +5990,10 @@
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="0" t="s">
-        <v>494</v>
+        <v>510</v>
       </c>
       <c r="B155" s="0" t="s">
-        <v>495</v>
+        <v>511</v>
       </c>
       <c r="C155" s="0" t="s">
         <v>28</v>
@@ -5957,7 +6008,7 @@
         <v>30</v>
       </c>
       <c r="G155" s="0" t="s">
-        <v>496</v>
+        <v>512</v>
       </c>
       <c r="H155" s="0" t="s">
         <v>16</v>
@@ -5965,10 +6016,10 @@
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="0" t="s">
-        <v>497</v>
+        <v>513</v>
       </c>
       <c r="B156" s="0" t="s">
-        <v>498</v>
+        <v>514</v>
       </c>
       <c r="C156" s="0" t="s">
         <v>28</v>
@@ -5983,7 +6034,7 @@
         <v>30</v>
       </c>
       <c r="G156" s="0" t="s">
-        <v>499</v>
+        <v>515</v>
       </c>
       <c r="H156" s="0" t="s">
         <v>16</v>
@@ -5991,10 +6042,10 @@
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="0" t="s">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c r="B157" s="0" t="s">
-        <v>501</v>
+        <v>517</v>
       </c>
       <c r="C157" s="0" t="s">
         <v>28</v>
@@ -6009,7 +6060,7 @@
         <v>30</v>
       </c>
       <c r="G157" s="0" t="s">
-        <v>502</v>
+        <v>518</v>
       </c>
       <c r="H157" s="0" t="s">
         <v>16</v>
@@ -6017,10 +6068,10 @@
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="0" t="s">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="B158" s="0" t="s">
-        <v>504</v>
+        <v>520</v>
       </c>
       <c r="C158" s="0" t="s">
         <v>28</v>
@@ -6035,7 +6086,7 @@
         <v>30</v>
       </c>
       <c r="G158" s="0" t="s">
-        <v>505</v>
+        <v>521</v>
       </c>
       <c r="H158" s="0" t="s">
         <v>16</v>
@@ -6043,10 +6094,10 @@
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="0" t="s">
-        <v>506</v>
+        <v>522</v>
       </c>
       <c r="B159" s="0" t="s">
-        <v>507</v>
+        <v>523</v>
       </c>
       <c r="C159" s="0" t="s">
         <v>28</v>
@@ -6061,7 +6112,7 @@
         <v>30</v>
       </c>
       <c r="G159" s="0" t="s">
-        <v>508</v>
+        <v>524</v>
       </c>
       <c r="H159" s="0" t="s">
         <v>16</v>
@@ -6069,10 +6120,10 @@
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="0" t="s">
-        <v>509</v>
+        <v>525</v>
       </c>
       <c r="B160" s="0" t="s">
-        <v>510</v>
+        <v>526</v>
       </c>
       <c r="C160" s="0" t="s">
         <v>28</v>
@@ -6087,7 +6138,7 @@
         <v>30</v>
       </c>
       <c r="G160" s="0" t="s">
-        <v>511</v>
+        <v>527</v>
       </c>
       <c r="H160" s="0" t="s">
         <v>16</v>
@@ -6095,10 +6146,10 @@
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="0" t="s">
-        <v>512</v>
+        <v>528</v>
       </c>
       <c r="B161" s="0" t="s">
-        <v>513</v>
+        <v>529</v>
       </c>
       <c r="C161" s="0" t="s">
         <v>28</v>
@@ -6113,7 +6164,7 @@
         <v>30</v>
       </c>
       <c r="G161" s="0" t="s">
-        <v>514</v>
+        <v>530</v>
       </c>
       <c r="H161" s="0" t="s">
         <v>16</v>
@@ -6121,10 +6172,10 @@
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="0" t="s">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="B162" s="0" t="s">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="C162" s="0" t="s">
         <v>28</v>
@@ -6139,7 +6190,7 @@
         <v>30</v>
       </c>
       <c r="G162" s="0" t="s">
-        <v>517</v>
+        <v>533</v>
       </c>
       <c r="H162" s="0" t="s">
         <v>16</v>
@@ -6147,10 +6198,10 @@
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="0" t="s">
-        <v>518</v>
+        <v>534</v>
       </c>
       <c r="B163" s="0" t="s">
-        <v>519</v>
+        <v>535</v>
       </c>
       <c r="C163" s="0" t="s">
         <v>28</v>
@@ -6165,7 +6216,7 @@
         <v>30</v>
       </c>
       <c r="G163" s="0" t="s">
-        <v>520</v>
+        <v>536</v>
       </c>
       <c r="H163" s="0" t="s">
         <v>16</v>
@@ -6173,10 +6224,10 @@
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="0" t="s">
-        <v>521</v>
+        <v>537</v>
       </c>
       <c r="B164" s="0" t="s">
-        <v>522</v>
+        <v>538</v>
       </c>
       <c r="C164" s="0" t="s">
         <v>28</v>
@@ -6191,7 +6242,7 @@
         <v>30</v>
       </c>
       <c r="G164" s="0" t="s">
-        <v>523</v>
+        <v>539</v>
       </c>
       <c r="H164" s="0" t="s">
         <v>16</v>
@@ -6199,10 +6250,10 @@
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="0" t="s">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="B165" s="0" t="s">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="C165" s="0" t="s">
         <v>28</v>
@@ -6217,7 +6268,7 @@
         <v>30</v>
       </c>
       <c r="G165" s="0" t="s">
-        <v>526</v>
+        <v>542</v>
       </c>
       <c r="H165" s="0" t="s">
         <v>16</v>
@@ -6225,10 +6276,10 @@
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="0" t="s">
-        <v>527</v>
+        <v>543</v>
       </c>
       <c r="B166" s="0" t="s">
-        <v>528</v>
+        <v>544</v>
       </c>
       <c r="C166" s="0" t="s">
         <v>28</v>
@@ -6243,7 +6294,7 @@
         <v>30</v>
       </c>
       <c r="G166" s="0" t="s">
-        <v>529</v>
+        <v>545</v>
       </c>
       <c r="H166" s="0" t="s">
         <v>16</v>
@@ -6251,10 +6302,10 @@
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="0" t="s">
-        <v>530</v>
+        <v>546</v>
       </c>
       <c r="B167" s="0" t="s">
-        <v>531</v>
+        <v>547</v>
       </c>
       <c r="C167" s="0" t="s">
         <v>11</v>
@@ -6269,7 +6320,7 @@
         <v>30</v>
       </c>
       <c r="G167" s="0" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="H167" s="0" t="s">
         <v>16</v>
@@ -6277,10 +6328,10 @@
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="0" t="s">
-        <v>533</v>
+        <v>549</v>
       </c>
       <c r="B168" s="0" t="s">
-        <v>534</v>
+        <v>550</v>
       </c>
       <c r="C168" s="0" t="s">
         <v>11</v>
@@ -6295,7 +6346,7 @@
         <v>30</v>
       </c>
       <c r="G168" s="0" t="s">
-        <v>535</v>
+        <v>551</v>
       </c>
       <c r="H168" s="0" t="s">
         <v>16</v>
@@ -6303,10 +6354,10 @@
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="0" t="s">
-        <v>536</v>
+        <v>552</v>
       </c>
       <c r="B169" s="0" t="s">
-        <v>537</v>
+        <v>553</v>
       </c>
       <c r="C169" s="0" t="s">
         <v>11</v>
@@ -6321,7 +6372,7 @@
         <v>30</v>
       </c>
       <c r="G169" s="0" t="s">
-        <v>538</v>
+        <v>554</v>
       </c>
       <c r="H169" s="0" t="s">
         <v>16</v>
@@ -6329,10 +6380,10 @@
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="0" t="s">
-        <v>539</v>
+        <v>555</v>
       </c>
       <c r="B170" s="0" t="s">
-        <v>540</v>
+        <v>556</v>
       </c>
       <c r="C170" s="0" t="s">
         <v>11</v>
@@ -6347,7 +6398,7 @@
         <v>30</v>
       </c>
       <c r="G170" s="0" t="s">
-        <v>541</v>
+        <v>557</v>
       </c>
       <c r="H170" s="0" t="s">
         <v>16</v>
@@ -6355,10 +6406,10 @@
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="0" t="s">
-        <v>542</v>
+        <v>558</v>
       </c>
       <c r="B171" s="0" t="s">
-        <v>543</v>
+        <v>559</v>
       </c>
       <c r="C171" s="0" t="s">
         <v>11</v>
@@ -6373,7 +6424,7 @@
         <v>30</v>
       </c>
       <c r="G171" s="0" t="s">
-        <v>544</v>
+        <v>560</v>
       </c>
       <c r="H171" s="0" t="s">
         <v>16</v>
@@ -6381,10 +6432,10 @@
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="0" t="s">
-        <v>545</v>
+        <v>561</v>
       </c>
       <c r="B172" s="0" t="s">
-        <v>546</v>
+        <v>562</v>
       </c>
       <c r="C172" s="0" t="s">
         <v>11</v>
@@ -6399,7 +6450,7 @@
         <v>30</v>
       </c>
       <c r="G172" s="0" t="s">
-        <v>547</v>
+        <v>563</v>
       </c>
       <c r="H172" s="0" t="s">
         <v>16</v>
@@ -6407,10 +6458,10 @@
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="0" t="s">
-        <v>548</v>
+        <v>564</v>
       </c>
       <c r="B173" s="0" t="s">
-        <v>549</v>
+        <v>565</v>
       </c>
       <c r="C173" s="0" t="s">
         <v>11</v>
@@ -6425,7 +6476,7 @@
         <v>30</v>
       </c>
       <c r="G173" s="0" t="s">
-        <v>550</v>
+        <v>566</v>
       </c>
       <c r="H173" s="0" t="s">
         <v>16</v>
@@ -6433,10 +6484,10 @@
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="0" t="s">
-        <v>551</v>
+        <v>567</v>
       </c>
       <c r="B174" s="0" t="s">
-        <v>552</v>
+        <v>568</v>
       </c>
       <c r="C174" s="0" t="s">
         <v>11</v>
@@ -6445,13 +6496,13 @@
         <v>12</v>
       </c>
       <c r="E174" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F174" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G174" s="0" t="s">
-        <v>553</v>
+        <v>569</v>
       </c>
       <c r="H174" s="0" t="s">
         <v>16</v>
@@ -6459,10 +6510,10 @@
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="0" t="s">
-        <v>554</v>
+        <v>570</v>
       </c>
       <c r="B175" s="0" t="s">
-        <v>555</v>
+        <v>571</v>
       </c>
       <c r="C175" s="0" t="s">
         <v>11</v>
@@ -6471,13 +6522,13 @@
         <v>12</v>
       </c>
       <c r="E175" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F175" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G175" s="0" t="s">
-        <v>556</v>
+        <v>572</v>
       </c>
       <c r="H175" s="0" t="s">
         <v>16</v>
@@ -6485,10 +6536,10 @@
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="0" t="s">
-        <v>557</v>
+        <v>573</v>
       </c>
       <c r="B176" s="0" t="s">
-        <v>558</v>
+        <v>574</v>
       </c>
       <c r="C176" s="0" t="s">
         <v>11</v>
@@ -6497,13 +6548,13 @@
         <v>12</v>
       </c>
       <c r="E176" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F176" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G176" s="0" t="s">
-        <v>559</v>
+        <v>575</v>
       </c>
       <c r="H176" s="0" t="s">
         <v>16</v>
@@ -6511,10 +6562,10 @@
     </row>
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="0" t="s">
-        <v>560</v>
+        <v>576</v>
       </c>
       <c r="B177" s="0" t="s">
-        <v>561</v>
+        <v>577</v>
       </c>
       <c r="C177" s="0" t="s">
         <v>11</v>
@@ -6523,13 +6574,13 @@
         <v>12</v>
       </c>
       <c r="E177" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F177" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G177" s="0" t="s">
-        <v>562</v>
+        <v>578</v>
       </c>
       <c r="H177" s="0" t="s">
         <v>16</v>
@@ -6537,10 +6588,10 @@
     </row>
     <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="0" t="s">
-        <v>563</v>
+        <v>579</v>
       </c>
       <c r="B178" s="0" t="s">
-        <v>564</v>
+        <v>580</v>
       </c>
       <c r="C178" s="0" t="s">
         <v>11</v>
@@ -6549,13 +6600,13 @@
         <v>12</v>
       </c>
       <c r="E178" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F178" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G178" s="0" t="s">
-        <v>565</v>
+        <v>581</v>
       </c>
       <c r="H178" s="0" t="s">
         <v>16</v>
@@ -6563,10 +6614,10 @@
     </row>
     <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="0" t="s">
-        <v>566</v>
+        <v>582</v>
       </c>
       <c r="B179" s="0" t="s">
-        <v>567</v>
+        <v>583</v>
       </c>
       <c r="C179" s="0" t="s">
         <v>11</v>
@@ -6575,13 +6626,13 @@
         <v>12</v>
       </c>
       <c r="E179" s="0" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="F179" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G179" s="0" t="s">
-        <v>568</v>
+        <v>584</v>
       </c>
       <c r="H179" s="0" t="s">
         <v>16</v>
@@ -6589,10 +6640,10 @@
     </row>
     <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="0" t="s">
-        <v>569</v>
+        <v>585</v>
       </c>
       <c r="B180" s="0" t="s">
-        <v>570</v>
+        <v>586</v>
       </c>
       <c r="C180" s="0" t="s">
         <v>11</v>
@@ -6601,13 +6652,13 @@
         <v>12</v>
       </c>
       <c r="E180" s="0" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="F180" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G180" s="0" t="s">
-        <v>571</v>
+        <v>587</v>
       </c>
       <c r="H180" s="0" t="s">
         <v>16</v>
@@ -6615,10 +6666,10 @@
     </row>
     <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="0" t="s">
-        <v>572</v>
+        <v>588</v>
       </c>
       <c r="B181" s="0" t="s">
-        <v>573</v>
+        <v>589</v>
       </c>
       <c r="C181" s="0" t="s">
         <v>11</v>
@@ -6627,13 +6678,13 @@
         <v>12</v>
       </c>
       <c r="E181" s="0" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="F181" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G181" s="0" t="s">
-        <v>574</v>
+        <v>590</v>
       </c>
       <c r="H181" s="0" t="s">
         <v>16</v>
@@ -6641,10 +6692,10 @@
     </row>
     <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="0" t="s">
-        <v>575</v>
+        <v>591</v>
       </c>
       <c r="B182" s="0" t="s">
-        <v>576</v>
+        <v>592</v>
       </c>
       <c r="C182" s="0" t="s">
         <v>11</v>
@@ -6653,13 +6704,13 @@
         <v>12</v>
       </c>
       <c r="E182" s="0" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="F182" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G182" s="0" t="s">
-        <v>577</v>
+        <v>593</v>
       </c>
       <c r="H182" s="0" t="s">
         <v>16</v>
@@ -6667,10 +6718,10 @@
     </row>
     <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="0" t="s">
-        <v>578</v>
+        <v>594</v>
       </c>
       <c r="B183" s="0" t="s">
-        <v>579</v>
+        <v>595</v>
       </c>
       <c r="C183" s="0" t="s">
         <v>11</v>
@@ -6679,13 +6730,13 @@
         <v>12</v>
       </c>
       <c r="E183" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F183" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G183" s="0" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H183" s="0" t="s">
         <v>16</v>
@@ -6693,10 +6744,10 @@
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="0" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="B184" s="0" t="s">
-        <v>582</v>
+        <v>598</v>
       </c>
       <c r="C184" s="0" t="s">
         <v>11</v>
@@ -6705,13 +6756,13 @@
         <v>12</v>
       </c>
       <c r="E184" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F184" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G184" s="0" t="s">
-        <v>583</v>
+        <v>599</v>
       </c>
       <c r="H184" s="0" t="s">
         <v>16</v>
@@ -6719,10 +6770,10 @@
     </row>
     <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="0" t="s">
-        <v>584</v>
+        <v>600</v>
       </c>
       <c r="B185" s="0" t="s">
-        <v>585</v>
+        <v>601</v>
       </c>
       <c r="C185" s="0" t="s">
         <v>11</v>
@@ -6731,13 +6782,13 @@
         <v>12</v>
       </c>
       <c r="E185" s="0" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="F185" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G185" s="0" t="s">
-        <v>586</v>
+        <v>602</v>
       </c>
       <c r="H185" s="0" t="s">
         <v>16</v>
@@ -6745,10 +6796,10 @@
     </row>
     <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="0" t="s">
-        <v>587</v>
+        <v>603</v>
       </c>
       <c r="B186" s="0" t="s">
-        <v>588</v>
+        <v>604</v>
       </c>
       <c r="C186" s="0" t="s">
         <v>11</v>
@@ -6757,13 +6808,13 @@
         <v>12</v>
       </c>
       <c r="E186" s="0" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="F186" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G186" s="0" t="s">
-        <v>589</v>
+        <v>605</v>
       </c>
       <c r="H186" s="0" t="s">
         <v>16</v>
@@ -6771,10 +6822,10 @@
     </row>
     <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="0" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="B187" s="0" t="s">
-        <v>591</v>
+        <v>607</v>
       </c>
       <c r="C187" s="0" t="s">
         <v>34</v>
@@ -6783,13 +6834,13 @@
         <v>12</v>
       </c>
       <c r="E187" s="0" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F187" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G187" s="0" t="s">
-        <v>592</v>
+        <v>608</v>
       </c>
       <c r="H187" s="0" t="s">
         <v>16</v>
@@ -6797,10 +6848,10 @@
     </row>
     <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="0" t="s">
-        <v>593</v>
+        <v>609</v>
       </c>
       <c r="B188" s="0" t="s">
-        <v>594</v>
+        <v>610</v>
       </c>
       <c r="C188" s="0" t="s">
         <v>34</v>
@@ -6809,13 +6860,13 @@
         <v>12</v>
       </c>
       <c r="E188" s="0" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F188" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G188" s="0" t="s">
-        <v>595</v>
+        <v>611</v>
       </c>
       <c r="H188" s="0" t="s">
         <v>16</v>
@@ -6823,10 +6874,10 @@
     </row>
     <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="0" t="s">
-        <v>596</v>
+        <v>612</v>
       </c>
       <c r="B189" s="0" t="s">
-        <v>597</v>
+        <v>613</v>
       </c>
       <c r="C189" s="0" t="s">
         <v>11</v>
@@ -6841,7 +6892,7 @@
         <v>14</v>
       </c>
       <c r="G189" s="0" t="s">
-        <v>598</v>
+        <v>614</v>
       </c>
       <c r="H189" s="0" t="s">
         <v>16</v>
@@ -6849,10 +6900,10 @@
     </row>
     <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="0" t="s">
-        <v>599</v>
+        <v>615</v>
       </c>
       <c r="B190" s="0" t="s">
-        <v>600</v>
+        <v>616</v>
       </c>
       <c r="C190" s="0" t="s">
         <v>11</v>
@@ -6867,7 +6918,7 @@
         <v>14</v>
       </c>
       <c r="G190" s="0" t="s">
-        <v>601</v>
+        <v>617</v>
       </c>
       <c r="H190" s="0" t="s">
         <v>16</v>
@@ -6875,10 +6926,10 @@
     </row>
     <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="0" t="s">
-        <v>602</v>
+        <v>618</v>
       </c>
       <c r="B191" s="0" t="s">
-        <v>603</v>
+        <v>619</v>
       </c>
       <c r="C191" s="0" t="s">
         <v>11</v>
@@ -6893,7 +6944,7 @@
         <v>14</v>
       </c>
       <c r="G191" s="0" t="s">
-        <v>604</v>
+        <v>620</v>
       </c>
       <c r="H191" s="0" t="s">
         <v>16</v>
@@ -6901,10 +6952,10 @@
     </row>
     <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="0" t="s">
-        <v>605</v>
+        <v>621</v>
       </c>
       <c r="B192" s="0" t="s">
-        <v>606</v>
+        <v>622</v>
       </c>
       <c r="C192" s="0" t="s">
         <v>11</v>
@@ -6919,7 +6970,7 @@
         <v>14</v>
       </c>
       <c r="G192" s="0" t="s">
-        <v>607</v>
+        <v>623</v>
       </c>
       <c r="H192" s="0" t="s">
         <v>16</v>
@@ -6927,10 +6978,10 @@
     </row>
     <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="0" t="s">
-        <v>608</v>
+        <v>624</v>
       </c>
       <c r="B193" s="0" t="s">
-        <v>609</v>
+        <v>625</v>
       </c>
       <c r="C193" s="0" t="s">
         <v>11</v>
@@ -6945,7 +6996,7 @@
         <v>14</v>
       </c>
       <c r="G193" s="0" t="s">
-        <v>610</v>
+        <v>626</v>
       </c>
       <c r="H193" s="0" t="s">
         <v>16</v>
@@ -6953,10 +7004,10 @@
     </row>
     <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="0" t="s">
-        <v>611</v>
+        <v>627</v>
       </c>
       <c r="B194" s="0" t="s">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="C194" s="0" t="s">
         <v>11</v>
@@ -6971,7 +7022,7 @@
         <v>14</v>
       </c>
       <c r="G194" s="0" t="s">
-        <v>613</v>
+        <v>629</v>
       </c>
       <c r="H194" s="0" t="s">
         <v>16</v>
@@ -6979,10 +7030,10 @@
     </row>
     <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="0" t="s">
-        <v>614</v>
+        <v>630</v>
       </c>
       <c r="B195" s="0" t="s">
-        <v>615</v>
+        <v>631</v>
       </c>
       <c r="C195" s="0" t="s">
         <v>11</v>
@@ -6991,13 +7042,13 @@
         <v>12</v>
       </c>
       <c r="E195" s="0" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="F195" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G195" s="0" t="s">
-        <v>616</v>
+        <v>632</v>
       </c>
       <c r="H195" s="0" t="s">
         <v>16</v>
@@ -7005,10 +7056,10 @@
     </row>
     <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="0" t="s">
-        <v>617</v>
+        <v>633</v>
       </c>
       <c r="B196" s="0" t="s">
-        <v>618</v>
+        <v>634</v>
       </c>
       <c r="C196" s="0" t="s">
         <v>11</v>
@@ -7017,13 +7068,13 @@
         <v>12</v>
       </c>
       <c r="E196" s="0" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="F196" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G196" s="0" t="s">
-        <v>619</v>
+        <v>635</v>
       </c>
       <c r="H196" s="0" t="s">
         <v>16</v>
@@ -7031,10 +7082,10 @@
     </row>
     <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="0" t="s">
-        <v>620</v>
+        <v>636</v>
       </c>
       <c r="B197" s="0" t="s">
-        <v>621</v>
+        <v>637</v>
       </c>
       <c r="C197" s="0" t="s">
         <v>11</v>
@@ -7043,13 +7094,13 @@
         <v>12</v>
       </c>
       <c r="E197" s="0" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="F197" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G197" s="0" t="s">
-        <v>622</v>
+        <v>638</v>
       </c>
       <c r="H197" s="0" t="s">
         <v>16</v>
@@ -7057,10 +7108,10 @@
     </row>
     <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="0" t="s">
-        <v>623</v>
+        <v>639</v>
       </c>
       <c r="B198" s="0" t="s">
-        <v>624</v>
+        <v>640</v>
       </c>
       <c r="C198" s="0" t="s">
         <v>11</v>
@@ -7069,13 +7120,13 @@
         <v>12</v>
       </c>
       <c r="E198" s="0" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="F198" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G198" s="0" t="s">
-        <v>625</v>
+        <v>641</v>
       </c>
       <c r="H198" s="0" t="s">
         <v>16</v>
@@ -7083,10 +7134,10 @@
     </row>
     <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="0" t="s">
-        <v>626</v>
+        <v>642</v>
       </c>
       <c r="B199" s="0" t="s">
-        <v>627</v>
+        <v>643</v>
       </c>
       <c r="C199" s="0" t="s">
         <v>11</v>
@@ -7095,13 +7146,13 @@
         <v>12</v>
       </c>
       <c r="E199" s="0" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="F199" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G199" s="0" t="s">
-        <v>628</v>
+        <v>644</v>
       </c>
       <c r="H199" s="0" t="s">
         <v>16</v>
@@ -7109,10 +7160,10 @@
     </row>
     <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="0" t="s">
-        <v>629</v>
+        <v>645</v>
       </c>
       <c r="B200" s="0" t="s">
-        <v>630</v>
+        <v>646</v>
       </c>
       <c r="C200" s="0" t="s">
         <v>11</v>
@@ -7121,13 +7172,13 @@
         <v>12</v>
       </c>
       <c r="E200" s="0" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="F200" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G200" s="0" t="s">
-        <v>631</v>
+        <v>647</v>
       </c>
       <c r="H200" s="0" t="s">
         <v>16</v>
@@ -7135,10 +7186,10 @@
     </row>
     <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="0" t="s">
-        <v>632</v>
+        <v>648</v>
       </c>
       <c r="B201" s="0" t="s">
-        <v>633</v>
+        <v>649</v>
       </c>
       <c r="C201" s="0" t="s">
         <v>11</v>
@@ -7147,13 +7198,13 @@
         <v>12</v>
       </c>
       <c r="E201" s="0" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="F201" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G201" s="0" t="s">
-        <v>634</v>
+        <v>650</v>
       </c>
       <c r="H201" s="0" t="s">
         <v>16</v>
@@ -7161,10 +7212,10 @@
     </row>
     <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="0" t="s">
-        <v>635</v>
+        <v>651</v>
       </c>
       <c r="B202" s="0" t="s">
-        <v>636</v>
+        <v>652</v>
       </c>
       <c r="C202" s="0" t="s">
         <v>11</v>
@@ -7173,13 +7224,13 @@
         <v>12</v>
       </c>
       <c r="E202" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F202" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G202" s="0" t="s">
-        <v>637</v>
+        <v>653</v>
       </c>
       <c r="H202" s="0" t="s">
         <v>16</v>
@@ -7187,10 +7238,10 @@
     </row>
     <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="0" t="s">
-        <v>638</v>
+        <v>654</v>
       </c>
       <c r="B203" s="0" t="s">
-        <v>639</v>
+        <v>655</v>
       </c>
       <c r="C203" s="0" t="s">
         <v>34</v>
@@ -7199,13 +7250,13 @@
         <v>12</v>
       </c>
       <c r="E203" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F203" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G203" s="0" t="s">
-        <v>36</v>
+        <v>656</v>
       </c>
       <c r="H203" s="0" t="s">
         <v>16</v>
@@ -7213,10 +7264,10 @@
     </row>
     <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="0" t="s">
-        <v>640</v>
+        <v>657</v>
       </c>
       <c r="B204" s="0" t="s">
-        <v>641</v>
+        <v>658</v>
       </c>
       <c r="C204" s="0" t="s">
         <v>11</v>
@@ -7225,13 +7276,13 @@
         <v>12</v>
       </c>
       <c r="E204" s="0" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="F204" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G204" s="0" t="s">
-        <v>642</v>
+        <v>659</v>
       </c>
       <c r="H204" s="0" t="s">
         <v>16</v>
@@ -7239,10 +7290,10 @@
     </row>
     <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="0" t="s">
-        <v>643</v>
+        <v>660</v>
       </c>
       <c r="B205" s="0" t="s">
-        <v>644</v>
+        <v>661</v>
       </c>
       <c r="C205" s="0" t="s">
         <v>34</v>
@@ -7251,13 +7302,13 @@
         <v>12</v>
       </c>
       <c r="E205" s="0" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="F205" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G205" s="0" t="s">
-        <v>645</v>
+        <v>662</v>
       </c>
       <c r="H205" s="0" t="s">
         <v>16</v>
@@ -7265,10 +7316,10 @@
     </row>
     <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="0" t="s">
-        <v>646</v>
+        <v>663</v>
       </c>
       <c r="B206" s="0" t="s">
-        <v>647</v>
+        <v>664</v>
       </c>
       <c r="C206" s="0" t="s">
         <v>39</v>
@@ -7277,13 +7328,13 @@
         <v>12</v>
       </c>
       <c r="E206" s="0" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="F206" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G206" s="0" t="s">
-        <v>648</v>
+        <v>665</v>
       </c>
       <c r="H206" s="0" t="s">
         <v>16</v>
@@ -7291,10 +7342,10 @@
     </row>
     <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="0" t="s">
-        <v>649</v>
+        <v>666</v>
       </c>
       <c r="B207" s="0" t="s">
-        <v>650</v>
+        <v>667</v>
       </c>
       <c r="C207" s="0" t="s">
         <v>11</v>
@@ -7309,7 +7360,7 @@
         <v>20</v>
       </c>
       <c r="G207" s="0" t="s">
-        <v>651</v>
+        <v>668</v>
       </c>
       <c r="H207" s="0" t="s">
         <v>16</v>
@@ -7317,10 +7368,10 @@
     </row>
     <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="0" t="s">
-        <v>652</v>
+        <v>669</v>
       </c>
       <c r="B208" s="0" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="C208" s="0" t="s">
         <v>11</v>
@@ -7335,7 +7386,7 @@
         <v>20</v>
       </c>
       <c r="G208" s="0" t="s">
-        <v>654</v>
+        <v>671</v>
       </c>
       <c r="H208" s="0" t="s">
         <v>16</v>
@@ -7343,10 +7394,10 @@
     </row>
     <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="0" t="s">
-        <v>655</v>
+        <v>672</v>
       </c>
       <c r="B209" s="0" t="s">
-        <v>656</v>
+        <v>673</v>
       </c>
       <c r="C209" s="0" t="s">
         <v>11</v>
@@ -7361,7 +7412,7 @@
         <v>20</v>
       </c>
       <c r="G209" s="0" t="s">
-        <v>657</v>
+        <v>674</v>
       </c>
       <c r="H209" s="0" t="s">
         <v>16</v>
@@ -7369,10 +7420,10 @@
     </row>
     <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="0" t="s">
-        <v>658</v>
+        <v>675</v>
       </c>
       <c r="B210" s="0" t="s">
-        <v>659</v>
+        <v>676</v>
       </c>
       <c r="C210" s="0" t="s">
         <v>11</v>
@@ -7381,13 +7432,13 @@
         <v>12</v>
       </c>
       <c r="E210" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F210" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G210" s="0" t="s">
-        <v>660</v>
+        <v>677</v>
       </c>
       <c r="H210" s="0" t="s">
         <v>16</v>
@@ -7395,10 +7446,10 @@
     </row>
     <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="0" t="s">
-        <v>661</v>
+        <v>678</v>
       </c>
       <c r="B211" s="0" t="s">
-        <v>662</v>
+        <v>679</v>
       </c>
       <c r="C211" s="0" t="s">
         <v>11</v>
@@ -7407,13 +7458,13 @@
         <v>12</v>
       </c>
       <c r="E211" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F211" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G211" s="0" t="s">
-        <v>663</v>
+        <v>680</v>
       </c>
       <c r="H211" s="0" t="s">
         <v>16</v>
@@ -7421,10 +7472,10 @@
     </row>
     <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="0" t="s">
-        <v>664</v>
+        <v>681</v>
       </c>
       <c r="B212" s="0" t="s">
-        <v>665</v>
+        <v>682</v>
       </c>
       <c r="C212" s="0" t="s">
         <v>11</v>
@@ -7433,13 +7484,13 @@
         <v>12</v>
       </c>
       <c r="E212" s="0" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="F212" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G212" s="0" t="s">
-        <v>666</v>
+        <v>683</v>
       </c>
       <c r="H212" s="0" t="s">
         <v>16</v>
@@ -7447,10 +7498,10 @@
     </row>
     <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="0" t="s">
-        <v>667</v>
+        <v>684</v>
       </c>
       <c r="B213" s="0" t="s">
-        <v>668</v>
+        <v>685</v>
       </c>
       <c r="C213" s="0" t="s">
         <v>34</v>
@@ -7459,13 +7510,13 @@
         <v>12</v>
       </c>
       <c r="E213" s="0" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="F213" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G213" s="0" t="s">
-        <v>669</v>
+        <v>686</v>
       </c>
       <c r="H213" s="0" t="s">
         <v>16</v>
@@ -7473,10 +7524,10 @@
     </row>
     <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="0" t="s">
-        <v>670</v>
+        <v>687</v>
       </c>
       <c r="B214" s="0" t="s">
-        <v>671</v>
+        <v>688</v>
       </c>
       <c r="C214" s="0" t="s">
         <v>11</v>
@@ -7485,13 +7536,13 @@
         <v>12</v>
       </c>
       <c r="E214" s="0" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="F214" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G214" s="0" t="s">
-        <v>672</v>
+        <v>689</v>
       </c>
       <c r="H214" s="0" t="s">
         <v>16</v>
@@ -7499,10 +7550,10 @@
     </row>
     <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="0" t="s">
-        <v>673</v>
+        <v>690</v>
       </c>
       <c r="B215" s="0" t="s">
-        <v>674</v>
+        <v>691</v>
       </c>
       <c r="C215" s="0" t="s">
         <v>11</v>
@@ -7511,13 +7562,13 @@
         <v>12</v>
       </c>
       <c r="E215" s="0" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="F215" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G215" s="0" t="s">
-        <v>675</v>
+        <v>692</v>
       </c>
       <c r="H215" s="0" t="s">
         <v>16</v>
@@ -7525,10 +7576,10 @@
     </row>
     <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="0" t="s">
-        <v>676</v>
+        <v>693</v>
       </c>
       <c r="B216" s="0" t="s">
-        <v>677</v>
+        <v>694</v>
       </c>
       <c r="C216" s="0" t="s">
         <v>11</v>
@@ -7537,13 +7588,13 @@
         <v>12</v>
       </c>
       <c r="E216" s="0" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="F216" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G216" s="0" t="s">
-        <v>678</v>
+        <v>695</v>
       </c>
       <c r="H216" s="0" t="s">
         <v>16</v>
@@ -7551,10 +7602,10 @@
     </row>
     <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="0" t="s">
-        <v>679</v>
+        <v>696</v>
       </c>
       <c r="B217" s="0" t="s">
-        <v>680</v>
+        <v>697</v>
       </c>
       <c r="C217" s="0" t="s">
         <v>34</v>
@@ -7563,13 +7614,13 @@
         <v>12</v>
       </c>
       <c r="E217" s="0" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="F217" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G217" s="0" t="s">
-        <v>681</v>
+        <v>698</v>
       </c>
       <c r="H217" s="0" t="s">
         <v>16</v>
@@ -7577,10 +7628,10 @@
     </row>
     <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="0" t="s">
-        <v>682</v>
+        <v>699</v>
       </c>
       <c r="B218" s="0" t="s">
-        <v>683</v>
+        <v>700</v>
       </c>
       <c r="C218" s="0" t="s">
         <v>34</v>
@@ -7589,13 +7640,13 @@
         <v>12</v>
       </c>
       <c r="E218" s="0" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="F218" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G218" s="0" t="s">
-        <v>684</v>
+        <v>701</v>
       </c>
       <c r="H218" s="0" t="s">
         <v>16</v>
@@ -7603,10 +7654,10 @@
     </row>
     <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="0" t="s">
-        <v>685</v>
+        <v>702</v>
       </c>
       <c r="B219" s="0" t="s">
-        <v>686</v>
+        <v>703</v>
       </c>
       <c r="C219" s="0" t="s">
         <v>11</v>
@@ -7615,13 +7666,13 @@
         <v>12</v>
       </c>
       <c r="E219" s="0" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="F219" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G219" s="0" t="s">
-        <v>687</v>
+        <v>704</v>
       </c>
       <c r="H219" s="0" t="s">
         <v>16</v>
@@ -7629,10 +7680,10 @@
     </row>
     <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="0" t="s">
-        <v>688</v>
+        <v>705</v>
       </c>
       <c r="B220" s="0" t="s">
-        <v>689</v>
+        <v>706</v>
       </c>
       <c r="C220" s="0" t="s">
         <v>11</v>
@@ -7641,13 +7692,13 @@
         <v>12</v>
       </c>
       <c r="E220" s="0" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="F220" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G220" s="0" t="s">
-        <v>690</v>
+        <v>707</v>
       </c>
       <c r="H220" s="0" t="s">
         <v>16</v>
@@ -7655,10 +7706,10 @@
     </row>
     <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="0" t="s">
-        <v>691</v>
+        <v>708</v>
       </c>
       <c r="B221" s="0" t="s">
-        <v>692</v>
+        <v>709</v>
       </c>
       <c r="C221" s="0" t="s">
         <v>11</v>
@@ -7667,13 +7718,13 @@
         <v>12</v>
       </c>
       <c r="E221" s="0" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="F221" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G221" s="0" t="s">
-        <v>693</v>
+        <v>710</v>
       </c>
       <c r="H221" s="0" t="s">
         <v>16</v>
@@ -7681,10 +7732,10 @@
     </row>
     <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="0" t="s">
-        <v>694</v>
+        <v>711</v>
       </c>
       <c r="B222" s="0" t="s">
-        <v>695</v>
+        <v>712</v>
       </c>
       <c r="C222" s="0" t="s">
         <v>11</v>
@@ -7693,13 +7744,13 @@
         <v>12</v>
       </c>
       <c r="E222" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F222" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G222" s="0" t="s">
-        <v>696</v>
+        <v>713</v>
       </c>
       <c r="H222" s="0" t="s">
         <v>16</v>
@@ -7707,10 +7758,10 @@
     </row>
     <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="0" t="s">
-        <v>697</v>
+        <v>714</v>
       </c>
       <c r="B223" s="0" t="s">
-        <v>698</v>
+        <v>715</v>
       </c>
       <c r="C223" s="0" t="s">
         <v>11</v>
@@ -7719,13 +7770,13 @@
         <v>12</v>
       </c>
       <c r="E223" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F223" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G223" s="0" t="s">
-        <v>699</v>
+        <v>716</v>
       </c>
       <c r="H223" s="0" t="s">
         <v>16</v>
@@ -7733,10 +7784,10 @@
     </row>
     <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="0" t="s">
-        <v>700</v>
+        <v>717</v>
       </c>
       <c r="B224" s="0" t="s">
-        <v>701</v>
+        <v>718</v>
       </c>
       <c r="C224" s="0" t="s">
         <v>11</v>
@@ -7745,13 +7796,13 @@
         <v>12</v>
       </c>
       <c r="E224" s="0" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="F224" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G224" s="0" t="s">
-        <v>702</v>
+        <v>719</v>
       </c>
       <c r="H224" s="0" t="s">
         <v>16</v>
@@ -7759,10 +7810,10 @@
     </row>
     <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="0" t="s">
-        <v>703</v>
+        <v>720</v>
       </c>
       <c r="B225" s="0" t="s">
-        <v>704</v>
+        <v>721</v>
       </c>
       <c r="C225" s="0" t="s">
         <v>11</v>
@@ -7771,13 +7822,13 @@
         <v>12</v>
       </c>
       <c r="E225" s="0" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="F225" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G225" s="0" t="s">
-        <v>705</v>
+        <v>722</v>
       </c>
       <c r="H225" s="0" t="s">
         <v>16</v>
@@ -7785,10 +7836,10 @@
     </row>
     <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="0" t="s">
-        <v>706</v>
+        <v>723</v>
       </c>
       <c r="B226" s="0" t="s">
-        <v>707</v>
+        <v>724</v>
       </c>
       <c r="C226" s="0" t="s">
         <v>11</v>
@@ -7797,13 +7848,13 @@
         <v>12</v>
       </c>
       <c r="E226" s="0" t="s">
-        <v>708</v>
+        <v>725</v>
       </c>
       <c r="F226" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G226" s="0" t="s">
-        <v>709</v>
+        <v>726</v>
       </c>
       <c r="H226" s="0" t="s">
         <v>16</v>
@@ -7811,10 +7862,10 @@
     </row>
     <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="0" t="s">
-        <v>710</v>
+        <v>727</v>
       </c>
       <c r="B227" s="0" t="s">
-        <v>711</v>
+        <v>728</v>
       </c>
       <c r="C227" s="0" t="s">
         <v>11</v>
@@ -7823,13 +7874,13 @@
         <v>12</v>
       </c>
       <c r="E227" s="0" t="s">
-        <v>712</v>
+        <v>729</v>
       </c>
       <c r="F227" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G227" s="0" t="s">
-        <v>713</v>
+        <v>730</v>
       </c>
       <c r="H227" s="0" t="s">
         <v>16</v>
@@ -7837,10 +7888,10 @@
     </row>
     <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="0" t="s">
-        <v>714</v>
+        <v>731</v>
       </c>
       <c r="B228" s="0" t="s">
-        <v>715</v>
+        <v>732</v>
       </c>
       <c r="C228" s="0" t="s">
         <v>11</v>
@@ -7849,13 +7900,13 @@
         <v>12</v>
       </c>
       <c r="E228" s="0" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="F228" s="0" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="G228" s="0" t="s">
-        <v>716</v>
+        <v>733</v>
       </c>
       <c r="H228" s="0" t="s">
         <v>16</v>
@@ -7863,10 +7914,10 @@
     </row>
     <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="0" t="s">
-        <v>717</v>
+        <v>734</v>
       </c>
       <c r="B229" s="0" t="s">
-        <v>718</v>
+        <v>735</v>
       </c>
       <c r="C229" s="0" t="s">
         <v>11</v>
@@ -7875,13 +7926,13 @@
         <v>12</v>
       </c>
       <c r="E229" s="0" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="F229" s="0" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="G229" s="0" t="s">
-        <v>719</v>
+        <v>736</v>
       </c>
       <c r="H229" s="0" t="s">
         <v>16</v>
@@ -7889,10 +7940,10 @@
     </row>
     <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="0" t="s">
-        <v>720</v>
+        <v>737</v>
       </c>
       <c r="B230" s="0" t="s">
-        <v>721</v>
+        <v>738</v>
       </c>
       <c r="C230" s="0" t="s">
         <v>11</v>
@@ -7901,13 +7952,13 @@
         <v>12</v>
       </c>
       <c r="E230" s="0" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="F230" s="0" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="G230" s="0" t="s">
-        <v>722</v>
+        <v>739</v>
       </c>
       <c r="H230" s="0" t="s">
         <v>16</v>
@@ -7915,10 +7966,10 @@
     </row>
     <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="0" t="s">
-        <v>723</v>
+        <v>740</v>
       </c>
       <c r="B231" s="0" t="s">
-        <v>724</v>
+        <v>741</v>
       </c>
       <c r="C231" s="0" t="s">
         <v>11</v>
@@ -7927,13 +7978,13 @@
         <v>12</v>
       </c>
       <c r="E231" s="0" t="s">
-        <v>725</v>
+        <v>742</v>
       </c>
       <c r="F231" s="0" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="G231" s="0" t="s">
-        <v>726</v>
+        <v>743</v>
       </c>
       <c r="H231" s="0" t="s">
         <v>16</v>
@@ -7941,10 +7992,10 @@
     </row>
     <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="0" t="s">
-        <v>727</v>
+        <v>744</v>
       </c>
       <c r="B232" s="0" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="C232" s="0" t="s">
         <v>11</v>
@@ -7953,13 +8004,13 @@
         <v>12</v>
       </c>
       <c r="E232" s="0" t="s">
-        <v>725</v>
+        <v>742</v>
       </c>
       <c r="F232" s="0" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="G232" s="0" t="s">
-        <v>729</v>
+        <v>746</v>
       </c>
       <c r="H232" s="0" t="s">
         <v>16</v>
@@ -7967,10 +8018,10 @@
     </row>
     <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="0" t="s">
-        <v>730</v>
+        <v>747</v>
       </c>
       <c r="B233" s="0" t="s">
-        <v>731</v>
+        <v>748</v>
       </c>
       <c r="C233" s="0" t="s">
         <v>11</v>
@@ -7979,13 +8030,13 @@
         <v>12</v>
       </c>
       <c r="E233" s="0" t="s">
-        <v>732</v>
+        <v>749</v>
       </c>
       <c r="F233" s="0" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="G233" s="0" t="s">
-        <v>733</v>
+        <v>750</v>
       </c>
       <c r="H233" s="0" t="s">
         <v>16</v>
@@ -7993,10 +8044,10 @@
     </row>
     <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="0" t="s">
-        <v>734</v>
+        <v>751</v>
       </c>
       <c r="B234" s="0" t="s">
-        <v>735</v>
+        <v>752</v>
       </c>
       <c r="C234" s="0" t="s">
         <v>11</v>
@@ -8005,13 +8056,13 @@
         <v>12</v>
       </c>
       <c r="E234" s="0" t="s">
-        <v>732</v>
+        <v>749</v>
       </c>
       <c r="F234" s="0" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="G234" s="0" t="s">
-        <v>736</v>
+        <v>753</v>
       </c>
       <c r="H234" s="0" t="s">
         <v>16</v>
@@ -8019,10 +8070,10 @@
     </row>
     <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="0" t="s">
-        <v>737</v>
+        <v>754</v>
       </c>
       <c r="B235" s="0" t="s">
-        <v>738</v>
+        <v>755</v>
       </c>
       <c r="C235" s="0" t="s">
         <v>11</v>
@@ -8031,13 +8082,13 @@
         <v>12</v>
       </c>
       <c r="E235" s="0" t="s">
-        <v>732</v>
+        <v>749</v>
       </c>
       <c r="F235" s="0" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="G235" s="0" t="s">
-        <v>739</v>
+        <v>756</v>
       </c>
       <c r="H235" s="0" t="s">
         <v>16</v>
@@ -8045,10 +8096,10 @@
     </row>
     <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="0" t="s">
-        <v>740</v>
+        <v>757</v>
       </c>
       <c r="B236" s="0" t="s">
-        <v>741</v>
+        <v>758</v>
       </c>
       <c r="C236" s="0" t="s">
         <v>11</v>
@@ -8057,13 +8108,13 @@
         <v>12</v>
       </c>
       <c r="E236" s="0" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="F236" s="0" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="G236" s="0" t="s">
-        <v>742</v>
+        <v>759</v>
       </c>
       <c r="H236" s="0" t="s">
         <v>16</v>
@@ -8071,10 +8122,10 @@
     </row>
     <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="0" t="s">
-        <v>743</v>
+        <v>760</v>
       </c>
       <c r="B237" s="0" t="s">
-        <v>744</v>
+        <v>761</v>
       </c>
       <c r="C237" s="0" t="s">
         <v>11</v>
@@ -8083,13 +8134,13 @@
         <v>12</v>
       </c>
       <c r="E237" s="0" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="F237" s="0" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="G237" s="0" t="s">
-        <v>745</v>
+        <v>762</v>
       </c>
       <c r="H237" s="0" t="s">
         <v>16</v>
@@ -8097,10 +8148,10 @@
     </row>
     <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="0" t="s">
-        <v>746</v>
+        <v>763</v>
       </c>
       <c r="B238" s="0" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="C238" s="0" t="s">
         <v>11</v>
@@ -8109,13 +8160,13 @@
         <v>12</v>
       </c>
       <c r="E238" s="0" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="F238" s="0" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="G238" s="0" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="H238" s="0" t="s">
         <v>16</v>
@@ -8123,10 +8174,10 @@
     </row>
     <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="0" t="s">
-        <v>749</v>
+        <v>766</v>
       </c>
       <c r="B239" s="0" t="s">
-        <v>750</v>
+        <v>767</v>
       </c>
       <c r="C239" s="0" t="s">
         <v>11</v>
@@ -8135,13 +8186,13 @@
         <v>12</v>
       </c>
       <c r="E239" s="0" t="s">
-        <v>751</v>
+        <v>768</v>
       </c>
       <c r="F239" s="0" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="G239" s="0" t="s">
-        <v>752</v>
+        <v>769</v>
       </c>
       <c r="H239" s="0" t="s">
         <v>16</v>
@@ -8149,10 +8200,10 @@
     </row>
     <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="0" t="s">
-        <v>753</v>
+        <v>770</v>
       </c>
       <c r="B240" s="0" t="s">
-        <v>754</v>
+        <v>771</v>
       </c>
       <c r="C240" s="0" t="s">
         <v>11</v>
@@ -8161,13 +8212,13 @@
         <v>12</v>
       </c>
       <c r="E240" s="0" t="s">
-        <v>751</v>
+        <v>768</v>
       </c>
       <c r="F240" s="0" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="G240" s="0" t="s">
-        <v>755</v>
+        <v>772</v>
       </c>
       <c r="H240" s="0" t="s">
         <v>16</v>
@@ -8175,10 +8226,10 @@
     </row>
     <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="0" t="s">
-        <v>756</v>
+        <v>773</v>
       </c>
       <c r="B241" s="0" t="s">
-        <v>757</v>
+        <v>774</v>
       </c>
       <c r="C241" s="0" t="s">
         <v>11</v>
@@ -8187,13 +8238,13 @@
         <v>12</v>
       </c>
       <c r="E241" s="0" t="s">
-        <v>758</v>
+        <v>775</v>
       </c>
       <c r="F241" s="0" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="G241" s="0" t="s">
-        <v>759</v>
+        <v>776</v>
       </c>
       <c r="H241" s="0" t="s">
         <v>16</v>
@@ -8201,10 +8252,10 @@
     </row>
     <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="0" t="s">
-        <v>760</v>
+        <v>777</v>
       </c>
       <c r="B242" s="0" t="s">
-        <v>761</v>
+        <v>778</v>
       </c>
       <c r="C242" s="0" t="s">
         <v>34</v>
@@ -8213,13 +8264,13 @@
         <v>12</v>
       </c>
       <c r="E242" s="0" t="s">
-        <v>758</v>
+        <v>775</v>
       </c>
       <c r="F242" s="0" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="G242" s="0" t="s">
-        <v>762</v>
+        <v>779</v>
       </c>
       <c r="H242" s="0" t="s">
         <v>16</v>
@@ -8227,10 +8278,10 @@
     </row>
     <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="0" t="s">
-        <v>763</v>
+        <v>780</v>
       </c>
       <c r="B243" s="0" t="s">
-        <v>764</v>
+        <v>781</v>
       </c>
       <c r="C243" s="0" t="s">
         <v>11</v>
@@ -8239,13 +8290,13 @@
         <v>12</v>
       </c>
       <c r="E243" s="0" t="s">
-        <v>765</v>
+        <v>782</v>
       </c>
       <c r="F243" s="0" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="G243" s="0" t="s">
-        <v>766</v>
+        <v>783</v>
       </c>
       <c r="H243" s="0" t="s">
         <v>16</v>
@@ -8253,10 +8304,10 @@
     </row>
     <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="0" t="s">
-        <v>767</v>
+        <v>784</v>
       </c>
       <c r="B244" s="0" t="s">
-        <v>768</v>
+        <v>785</v>
       </c>
       <c r="C244" s="0" t="s">
         <v>34</v>
@@ -8265,13 +8316,13 @@
         <v>12</v>
       </c>
       <c r="E244" s="0" t="s">
-        <v>765</v>
+        <v>782</v>
       </c>
       <c r="F244" s="0" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="G244" s="0" t="s">
-        <v>769</v>
+        <v>786</v>
       </c>
       <c r="H244" s="0" t="s">
         <v>16</v>
@@ -8279,10 +8330,10 @@
     </row>
     <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="0" t="s">
-        <v>770</v>
+        <v>787</v>
       </c>
       <c r="B245" s="0" t="s">
-        <v>771</v>
+        <v>788</v>
       </c>
       <c r="C245" s="0" t="s">
         <v>11</v>
@@ -8291,13 +8342,13 @@
         <v>12</v>
       </c>
       <c r="E245" s="0" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F245" s="0" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G245" s="0" t="s">
-        <v>772</v>
+        <v>789</v>
       </c>
       <c r="H245" s="0" t="s">
         <v>16</v>
@@ -8305,10 +8356,10 @@
     </row>
     <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="0" t="s">
-        <v>773</v>
+        <v>790</v>
       </c>
       <c r="B246" s="0" t="s">
-        <v>774</v>
+        <v>791</v>
       </c>
       <c r="C246" s="0" t="s">
         <v>11</v>
@@ -8317,13 +8368,13 @@
         <v>12</v>
       </c>
       <c r="E246" s="0" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F246" s="0" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G246" s="0" t="s">
-        <v>775</v>
+        <v>792</v>
       </c>
       <c r="H246" s="0" t="s">
         <v>16</v>
@@ -8331,10 +8382,10 @@
     </row>
     <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="0" t="s">
-        <v>776</v>
+        <v>793</v>
       </c>
       <c r="B247" s="0" t="s">
-        <v>777</v>
+        <v>794</v>
       </c>
       <c r="C247" s="0" t="s">
         <v>11</v>
@@ -8343,13 +8394,13 @@
         <v>12</v>
       </c>
       <c r="E247" s="0" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F247" s="0" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G247" s="0" t="s">
-        <v>778</v>
+        <v>795</v>
       </c>
       <c r="H247" s="0" t="s">
         <v>16</v>
@@ -8357,10 +8408,10 @@
     </row>
     <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="0" t="s">
-        <v>779</v>
+        <v>796</v>
       </c>
       <c r="B248" s="0" t="s">
-        <v>780</v>
+        <v>797</v>
       </c>
       <c r="C248" s="0" t="s">
         <v>11</v>
@@ -8369,13 +8420,13 @@
         <v>12</v>
       </c>
       <c r="E248" s="0" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F248" s="0" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G248" s="0" t="s">
-        <v>781</v>
+        <v>798</v>
       </c>
       <c r="H248" s="0" t="s">
         <v>16</v>
@@ -8383,10 +8434,10 @@
     </row>
     <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="0" t="s">
-        <v>782</v>
+        <v>799</v>
       </c>
       <c r="B249" s="0" t="s">
-        <v>783</v>
+        <v>800</v>
       </c>
       <c r="C249" s="0" t="s">
         <v>11</v>
@@ -8395,13 +8446,13 @@
         <v>12</v>
       </c>
       <c r="E249" s="0" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F249" s="0" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G249" s="0" t="s">
-        <v>784</v>
+        <v>801</v>
       </c>
       <c r="H249" s="0" t="s">
         <v>16</v>
@@ -8409,10 +8460,10 @@
     </row>
     <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="0" t="s">
-        <v>785</v>
+        <v>802</v>
       </c>
       <c r="B250" s="0" t="s">
-        <v>786</v>
+        <v>803</v>
       </c>
       <c r="C250" s="0" t="s">
         <v>34</v>
@@ -8421,13 +8472,13 @@
         <v>12</v>
       </c>
       <c r="E250" s="0" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F250" s="0" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G250" s="0" t="s">
-        <v>787</v>
+        <v>804</v>
       </c>
       <c r="H250" s="0" t="s">
         <v>16</v>
@@ -8435,10 +8486,10 @@
     </row>
     <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="0" t="s">
-        <v>788</v>
+        <v>805</v>
       </c>
       <c r="B251" s="0" t="s">
-        <v>789</v>
+        <v>806</v>
       </c>
       <c r="C251" s="0" t="s">
         <v>34</v>
@@ -8447,13 +8498,13 @@
         <v>12</v>
       </c>
       <c r="E251" s="0" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F251" s="0" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G251" s="0" t="s">
-        <v>790</v>
+        <v>807</v>
       </c>
       <c r="H251" s="0" t="s">
         <v>16</v>
@@ -8461,10 +8512,10 @@
     </row>
     <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="0" t="s">
-        <v>791</v>
+        <v>808</v>
       </c>
       <c r="B252" s="0" t="s">
-        <v>792</v>
+        <v>809</v>
       </c>
       <c r="C252" s="0" t="s">
         <v>11</v>
@@ -8473,13 +8524,13 @@
         <v>12</v>
       </c>
       <c r="E252" s="0" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F252" s="0" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G252" s="0" t="s">
-        <v>793</v>
+        <v>810</v>
       </c>
       <c r="H252" s="0" t="s">
         <v>16</v>
@@ -8487,10 +8538,10 @@
     </row>
     <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="0" t="s">
-        <v>794</v>
+        <v>811</v>
       </c>
       <c r="B253" s="0" t="s">
-        <v>795</v>
+        <v>812</v>
       </c>
       <c r="C253" s="0" t="s">
         <v>11</v>
@@ -8499,13 +8550,13 @@
         <v>12</v>
       </c>
       <c r="E253" s="0" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F253" s="0" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G253" s="0" t="s">
-        <v>796</v>
+        <v>813</v>
       </c>
       <c r="H253" s="0" t="s">
         <v>16</v>
@@ -8513,10 +8564,10 @@
     </row>
     <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="0" t="s">
-        <v>797</v>
+        <v>814</v>
       </c>
       <c r="B254" s="0" t="s">
-        <v>798</v>
+        <v>815</v>
       </c>
       <c r="C254" s="0" t="s">
         <v>11</v>
@@ -8525,13 +8576,13 @@
         <v>12</v>
       </c>
       <c r="E254" s="0" t="s">
-        <v>799</v>
+        <v>816</v>
       </c>
       <c r="F254" s="0" t="s">
-        <v>799</v>
+        <v>816</v>
       </c>
       <c r="G254" s="0" t="s">
-        <v>800</v>
+        <v>817</v>
       </c>
       <c r="H254" s="0" t="s">
         <v>16</v>
@@ -8539,10 +8590,10 @@
     </row>
     <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="0" t="s">
-        <v>801</v>
+        <v>818</v>
       </c>
       <c r="B255" s="0" t="s">
-        <v>802</v>
+        <v>819</v>
       </c>
       <c r="C255" s="0" t="s">
         <v>11</v>
@@ -8551,13 +8602,13 @@
         <v>12</v>
       </c>
       <c r="E255" s="0" t="s">
-        <v>799</v>
+        <v>816</v>
       </c>
       <c r="F255" s="0" t="s">
-        <v>799</v>
+        <v>816</v>
       </c>
       <c r="G255" s="0" t="s">
-        <v>803</v>
+        <v>820</v>
       </c>
       <c r="H255" s="0" t="s">
         <v>16</v>
@@ -8565,10 +8616,10 @@
     </row>
     <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="0" t="s">
-        <v>804</v>
+        <v>821</v>
       </c>
       <c r="B256" s="0" t="s">
-        <v>805</v>
+        <v>822</v>
       </c>
       <c r="C256" s="0" t="s">
         <v>34</v>
@@ -8577,13 +8628,13 @@
         <v>12</v>
       </c>
       <c r="E256" s="0" t="s">
-        <v>799</v>
+        <v>816</v>
       </c>
       <c r="F256" s="0" t="s">
-        <v>799</v>
+        <v>816</v>
       </c>
       <c r="G256" s="0" t="s">
-        <v>806</v>
+        <v>823</v>
       </c>
       <c r="H256" s="0" t="s">
         <v>16</v>
@@ -8591,10 +8642,10 @@
     </row>
     <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="0" t="s">
-        <v>807</v>
+        <v>824</v>
       </c>
       <c r="B257" s="0" t="s">
-        <v>808</v>
+        <v>825</v>
       </c>
       <c r="C257" s="0" t="s">
         <v>11</v>
@@ -8603,13 +8654,13 @@
         <v>12</v>
       </c>
       <c r="E257" s="0" t="s">
-        <v>799</v>
+        <v>816</v>
       </c>
       <c r="F257" s="0" t="s">
-        <v>799</v>
+        <v>816</v>
       </c>
       <c r="G257" s="0" t="s">
-        <v>809</v>
+        <v>826</v>
       </c>
       <c r="H257" s="0" t="s">
         <v>16</v>
@@ -8617,10 +8668,10 @@
     </row>
     <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="0" t="s">
-        <v>810</v>
+        <v>827</v>
       </c>
       <c r="B258" s="0" t="s">
-        <v>811</v>
+        <v>828</v>
       </c>
       <c r="C258" s="0" t="s">
         <v>11</v>
@@ -8629,13 +8680,13 @@
         <v>12</v>
       </c>
       <c r="E258" s="0" t="s">
-        <v>799</v>
+        <v>816</v>
       </c>
       <c r="F258" s="0" t="s">
-        <v>799</v>
+        <v>816</v>
       </c>
       <c r="G258" s="0" t="s">
-        <v>812</v>
+        <v>829</v>
       </c>
       <c r="H258" s="0" t="s">
         <v>16</v>
@@ -8643,13 +8694,13 @@
     </row>
     <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="0" t="s">
-        <v>813</v>
+        <v>830</v>
       </c>
       <c r="B259" s="0" t="s">
-        <v>814</v>
+        <v>831</v>
       </c>
       <c r="C259" s="0" t="s">
-        <v>815</v>
+        <v>832</v>
       </c>
       <c r="D259" s="0" t="s">
         <v>45</v>
@@ -8661,7 +8712,7 @@
         <v>14</v>
       </c>
       <c r="G259" s="0" t="s">
-        <v>816</v>
+        <v>833</v>
       </c>
       <c r="H259" s="0" t="s">
         <v>16</v>
@@ -8669,13 +8720,13 @@
     </row>
     <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="0" t="s">
-        <v>817</v>
+        <v>834</v>
       </c>
       <c r="B260" s="0" t="s">
-        <v>818</v>
+        <v>835</v>
       </c>
       <c r="C260" s="0" t="s">
-        <v>815</v>
+        <v>832</v>
       </c>
       <c r="D260" s="0" t="s">
         <v>45</v>
@@ -8687,7 +8738,7 @@
         <v>30</v>
       </c>
       <c r="G260" s="0" t="s">
-        <v>819</v>
+        <v>836</v>
       </c>
       <c r="H260" s="0" t="s">
         <v>16</v>
@@ -8695,25 +8746,25 @@
     </row>
     <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="0" t="s">
-        <v>820</v>
+        <v>837</v>
       </c>
       <c r="B261" s="0" t="s">
-        <v>821</v>
+        <v>838</v>
       </c>
       <c r="C261" s="0" t="s">
-        <v>822</v>
+        <v>839</v>
       </c>
       <c r="D261" s="0" t="s">
         <v>45</v>
       </c>
       <c r="E261" s="0" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="F261" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G261" s="0" t="s">
-        <v>823</v>
+        <v>840</v>
       </c>
       <c r="H261" s="0" t="s">
         <v>16</v>
@@ -8721,25 +8772,25 @@
     </row>
     <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="0" t="s">
-        <v>824</v>
+        <v>841</v>
       </c>
       <c r="B262" s="0" t="s">
-        <v>825</v>
+        <v>842</v>
       </c>
       <c r="C262" s="0" t="s">
-        <v>815</v>
+        <v>832</v>
       </c>
       <c r="D262" s="0" t="s">
         <v>45</v>
       </c>
       <c r="E262" s="0" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="F262" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G262" s="0" t="s">
-        <v>826</v>
+        <v>843</v>
       </c>
       <c r="H262" s="0" t="s">
         <v>16</v>
@@ -8747,13 +8798,13 @@
     </row>
     <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="0" t="s">
-        <v>827</v>
+        <v>844</v>
       </c>
       <c r="B263" s="0" t="s">
-        <v>828</v>
+        <v>845</v>
       </c>
       <c r="C263" s="0" t="s">
-        <v>815</v>
+        <v>832</v>
       </c>
       <c r="D263" s="0" t="s">
         <v>45</v>
@@ -8765,7 +8816,7 @@
         <v>14</v>
       </c>
       <c r="G263" s="0" t="s">
-        <v>598</v>
+        <v>614</v>
       </c>
       <c r="H263" s="0" t="s">
         <v>16</v>

--- a/reports/manual_image_qa.xlsx
+++ b/reports/manual_image_qa.xlsx
@@ -145,7 +145,7 @@
     <t xml:space="preserve">Gifu</t>
   </si>
   <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/a/a2/Shirakawa-go_%282017-07-22%29.jpg/1280px-Shirakawa-go_%282017-07-22%29.jpg</t>
+    <t xml:space="preserve">https://plus.unsplash.com/premium_photo-1661947436461-a9ab4ecdd37a?q=80&amp;w=1332&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
   </si>
   <si>
     <t xml:space="preserve">abeno-harukas-300-osaka</t>

--- a/reports/manual_image_qa.xlsx
+++ b/reports/manual_image_qa.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1841" uniqueCount="846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1835" uniqueCount="844">
   <si>
     <t xml:space="preserve">Destination ID</t>
   </si>
@@ -445,346 +445,340 @@
     <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/d/dc/1_magome_juku_2024.jpg/3840px-1_magome_juku_2024.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">gifu-shirakawa-go</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shirakawa-go</t>
+    <t xml:space="preserve">ginza-urban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ginza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/5/5b/Ginza-WAKO_at_night.jpg/1280px-Ginza-WAKO_at_night.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gunma-ikaho-onsen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ikaho Onsen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gunma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/8/82/Ikaho_Onsen_03.jpg/250px-Ikaho_Onsen_03.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gunma-kusatsu-onsen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kusatsu Onsen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/7a/Bath_in_kusatsu.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gunma-shima-onsen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shima Onsen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/%E5%9B%9B%E4%B8%87%E6%B8%A9%E6%B3%89_%E4%B8%AD%E4%B9%8B%E6%9D%A1_2013_%289993444756%29.jpg/3840px-%E5%9B%9B%E4%B8%87%E6%B8%A9%E6%B3%89_%E4%B8%AD%E4%B9%8B%E6%9D%A1_2013_%289993444756%29.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hachioji-tokyo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hachioji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/1/11/Takao-san-Top_10.11.13_saturday.JPG/1280px-Takao-san-Top_10.11.13_saturday.JPG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hakkeijima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hakkeijima Sea Paradise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/b/b2/Yokohama_Hakkeijima_Sea_Paradise_-_01.jpg/330px-Yokohama_Hakkeijima_Sea_Paradise_-_01.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hakodate-night-view</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mount Hakodate Night View</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hokkaido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/1/1b/Kanemori_Red_Brick_Warehouse_Hakodate_Hokkaido_pref_Japan01n.jpg/3840px-Kanemori_Red_Brick_Warehouse_Hakodate_Hokkaido_pref_Japan01n.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">harry-potter-studio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Potter Studio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/5/55/Warner_Bros._Studio_Tour_Tokyo_entrance_%282%29_2023-08-17.jpg/330px-Warner_Bros._Studio_Tour_Tokyo_entrance_%282%29_2023-08-17.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">higashiyama-sky-tower-nagoya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Higashiyama Sky Tower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://images.unsplash.com/photo-1545569341-9eb8b30979d9?auto=format&amp;fit=crop&amp;q=80&amp;w=1200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hikone-castle-shiga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hikone Castle (National Treasure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shiga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/9/9f/Hikone_Castle_November_2016_-02.jpg/1280px-Hikone_Castle_November_2016_-02.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">himeji-castle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Himeji Castle (White Heron Castle)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/c/c1/Himeji_castle_in_may_2015.jpg/1280px-Himeji_castle_in_may_2015.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hirosaki-castle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hirosaki Castle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aomori</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tohoku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/f/f3/Hirosaki-castle_Aomori_with_Sakura_blossoms.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ibaraki-fukuroda-falls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fukuroda Falls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/8/80/Fukuroda_Falls_-_%E8%A2%8B%E7%94%B0%E3%81%AE%E6%BB%9D%28%E3%81%B5%E3%81%8F%E3%82%8D%E3%81%A0%E3%81%AE%E3%81%9F%E3%81%8D%29.jpg/3840px-Fukuroda_Falls_-_%E8%A2%8B%E7%94%B0%E3%81%AE%E6%BB%9D%28%E3%81%B5%E3%81%8F%E3%82%8D%E3%81%A0%E3%81%AE%E3%81%9F%E3%81%8D%29.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ibaraki-hitachi-seaside-park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hitachi Seaside Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/b/bc/Ferris_wheel_of_the_Hitachi_beach_park%2Chitachi-kaihin-koen%2Chitachinaka-city%2Cjapan.JPG/330px-Ferris_wheel_of_the_Hitachi_beach_park%2Chitachi-kaihin-koen%2Chitachinaka-city%2Cjapan.JPG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ibaraki-mount-tsukuba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mount Tsukuba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/2/2a/Mount_Tsukuba_seen_from_the_WSW_%282006%29.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ikebukuro-toshima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ikebukuro (Toshima)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Sunshine_60_Observatory_%40_Sunshine_Building_%40_Ikebukuro_%2811547419543%29.jpg/3840px-Sunshine_60_Observatory_%40_Sunshine_Building_%40_Ikebukuro_%2811547419543%29.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">imperial-palace-chiyoda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imperial Palace (Chiyoda)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/5/5f/Edo_P_detail.jpg/960px-Edo_P_detail.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ise-grand-shrine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ise Grand Shrine (Ise Jingu)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/8/8d/Naiku_04.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">izu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Izu Peninsula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shizuoka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/a/ad/Izu_Peninsula_Shizuoka_Japan_SRTM.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">izumo-taisha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Izumo Taisha Grand Shrine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shimane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/e/e6/Izumo-taisha14bs4592.jpg/3840px-Izumo-taisha14bs4592.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jogashima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miura Peninsula &amp; Jogashima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/d/d2/Miura_Peninsula_Kanagawa_Japan_SRTM.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joypolis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joypolis Odaiba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://images.unsplash.com/photo-1503899036084-c55cdd92da26?auto=format&amp;fit=crop&amp;q=80&amp;w=1200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kairakuen-mito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kairakuen Garden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/e/ec/Kairaku-en%2C_Ibaraki_24.jpg/3840px-Kairaku-en%2C_Ibaraki_24.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kakegawa-castle-shizuoka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kakegawa Castle &amp; Ninomaru Goten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/5/5c/Kakegawajo_20090321.jpg/1280px-Kakegawajo_20090321.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kanazawa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kanazawa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ishikawa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/3/31/Stone_lantern_Kenrokuen.jpg/3840px-Stone_lantern_Kenrokuen.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kanazawa-castle-ishikawa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kanazawa Castle Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/7/7e/Kanazawa-M-5932.jpg/1280px-Kanazawa-M-5932.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kawagoe-castle-saitama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kawagoe Castle Honmaru Goten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saitama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/e/ef/Kawagoe-Castle_Honmaru-Goten.jpg/1280px-Kawagoe-Castle_Honmaru-Goten.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kegon-falls-nikko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegon Falls (Nikko)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tochigi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kinosaki-onsen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kinosaki Onsen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/3/35/Kinosaki_Onsen_by_day.jpg/3840px-Kinosaki_Onsen_by_day.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kinugawa-onsen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kinugawa Onsen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/5/5c/Kinugawa_Onsen_03.JPG/1280px-Kinugawa_Onsen_03.JPG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kiso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiso Valley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nagano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/8/88/Kiso_Valley_from_Doppyo.jpg/1280px-Kiso_Valley_from_Doppyo.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kobe-maya-night-view</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mount Maya Kikuseidai (Kobe)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/6/6e/View_of_Kikuseidai_from_Mount_Maya_Kobe.jpg/3840px-View_of_Kikuseidai_from_Mount_Maya_Kobe.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kochi-castle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kochi Castle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kochi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shikoku</t>
   </si>
   <si>
     <t xml:space="preserve">https://images.unsplash.com/photo-1507525428034-b723cf961d3e?auto=format&amp;fit=crop&amp;q=80&amp;w=1200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ginza-urban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ginza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/5/5b/Ginza-WAKO_at_night.jpg/1280px-Ginza-WAKO_at_night.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gunma-ikaho-onsen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ikaho Onsen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gunma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/8/82/Ikaho_Onsen_03.jpg/250px-Ikaho_Onsen_03.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gunma-kusatsu-onsen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kusatsu Onsen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/7a/Bath_in_kusatsu.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gunma-shima-onsen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shima Onsen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/%E5%9B%9B%E4%B8%87%E6%B8%A9%E6%B3%89_%E4%B8%AD%E4%B9%8B%E6%9D%A1_2013_%289993444756%29.jpg/3840px-%E5%9B%9B%E4%B8%87%E6%B8%A9%E6%B3%89_%E4%B8%AD%E4%B9%8B%E6%9D%A1_2013_%289993444756%29.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hachioji-tokyo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hachioji</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/1/11/Takao-san-Top_10.11.13_saturday.JPG/1280px-Takao-san-Top_10.11.13_saturday.JPG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hakkeijima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hakkeijima Sea Paradise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/b/b2/Yokohama_Hakkeijima_Sea_Paradise_-_01.jpg/330px-Yokohama_Hakkeijima_Sea_Paradise_-_01.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hakodate-night-view</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mount Hakodate Night View</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hokkaido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/1/1b/Kanemori_Red_Brick_Warehouse_Hakodate_Hokkaido_pref_Japan01n.jpg/3840px-Kanemori_Red_Brick_Warehouse_Hakodate_Hokkaido_pref_Japan01n.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">harry-potter-studio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harry Potter Studio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/5/55/Warner_Bros._Studio_Tour_Tokyo_entrance_%282%29_2023-08-17.jpg/330px-Warner_Bros._Studio_Tour_Tokyo_entrance_%282%29_2023-08-17.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">higashiyama-sky-tower-nagoya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Higashiyama Sky Tower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://images.unsplash.com/photo-1545569341-9eb8b30979d9?auto=format&amp;fit=crop&amp;q=80&amp;w=1200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hikone-castle-shiga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hikone Castle (National Treasure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shiga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/9/9f/Hikone_Castle_November_2016_-02.jpg/1280px-Hikone_Castle_November_2016_-02.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">himeji-castle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Himeji Castle (White Heron Castle)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/c/c1/Himeji_castle_in_may_2015.jpg/1280px-Himeji_castle_in_may_2015.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hirosaki-castle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hirosaki Castle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aomori</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tohoku</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/f/f3/Hirosaki-castle_Aomori_with_Sakura_blossoms.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ibaraki-fukuroda-falls</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fukuroda Falls</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/8/80/Fukuroda_Falls_-_%E8%A2%8B%E7%94%B0%E3%81%AE%E6%BB%9D%28%E3%81%B5%E3%81%8F%E3%82%8D%E3%81%A0%E3%81%AE%E3%81%9F%E3%81%8D%29.jpg/3840px-Fukuroda_Falls_-_%E8%A2%8B%E7%94%B0%E3%81%AE%E6%BB%9D%28%E3%81%B5%E3%81%8F%E3%82%8D%E3%81%A0%E3%81%AE%E3%81%9F%E3%81%8D%29.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ibaraki-hitachi-seaside-park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hitachi Seaside Park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/b/bc/Ferris_wheel_of_the_Hitachi_beach_park%2Chitachi-kaihin-koen%2Chitachinaka-city%2Cjapan.JPG/330px-Ferris_wheel_of_the_Hitachi_beach_park%2Chitachi-kaihin-koen%2Chitachinaka-city%2Cjapan.JPG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ibaraki-mount-tsukuba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mount Tsukuba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/2/2a/Mount_Tsukuba_seen_from_the_WSW_%282006%29.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ikebukuro-toshima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ikebukuro (Toshima)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Sunshine_60_Observatory_%40_Sunshine_Building_%40_Ikebukuro_%2811547419543%29.jpg/3840px-Sunshine_60_Observatory_%40_Sunshine_Building_%40_Ikebukuro_%2811547419543%29.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">imperial-palace-chiyoda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imperial Palace (Chiyoda)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/5/5f/Edo_P_detail.jpg/960px-Edo_P_detail.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ise-grand-shrine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ise Grand Shrine (Ise Jingu)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/8/8d/Naiku_04.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">izu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Izu Peninsula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shizuoka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/a/ad/Izu_Peninsula_Shizuoka_Japan_SRTM.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">izumo-taisha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Izumo Taisha Grand Shrine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shimane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/e/e6/Izumo-taisha14bs4592.jpg/3840px-Izumo-taisha14bs4592.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jogashima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miura Peninsula &amp; Jogashima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/d/d2/Miura_Peninsula_Kanagawa_Japan_SRTM.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">joypolis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joypolis Odaiba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://images.unsplash.com/photo-1503899036084-c55cdd92da26?auto=format&amp;fit=crop&amp;q=80&amp;w=1200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kairakuen-mito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kairakuen Garden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/e/ec/Kairaku-en%2C_Ibaraki_24.jpg/3840px-Kairaku-en%2C_Ibaraki_24.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kakegawa-castle-shizuoka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kakegawa Castle &amp; Ninomaru Goten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/5/5c/Kakegawajo_20090321.jpg/1280px-Kakegawajo_20090321.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kanazawa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kanazawa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ishikawa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/3/31/Stone_lantern_Kenrokuen.jpg/3840px-Stone_lantern_Kenrokuen.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kanazawa-castle-ishikawa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kanazawa Castle Park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/7/7e/Kanazawa-M-5932.jpg/1280px-Kanazawa-M-5932.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kawagoe-castle-saitama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kawagoe Castle Honmaru Goten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saitama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/e/ef/Kawagoe-Castle_Honmaru-Goten.jpg/1280px-Kawagoe-Castle_Honmaru-Goten.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kegon-falls-nikko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kegon Falls (Nikko)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tochigi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kinosaki-onsen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kinosaki Onsen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/3/35/Kinosaki_Onsen_by_day.jpg/3840px-Kinosaki_Onsen_by_day.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kinugawa-onsen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kinugawa Onsen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/5/5c/Kinugawa_Onsen_03.JPG/1280px-Kinugawa_Onsen_03.JPG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kiso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiso Valley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nagano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/8/88/Kiso_Valley_from_Doppyo.jpg/1280px-Kiso_Valley_from_Doppyo.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kobe-maya-night-view</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mount Maya Kikuseidai (Kobe)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/6/6e/View_of_Kikuseidai_from_Mount_Maya_Kobe.jpg/3840px-View_of_Kikuseidai_from_Mount_Maya_Kobe.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kochi-castle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kochi Castle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kochi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shikoku</t>
   </si>
   <si>
     <t xml:space="preserve">korakuen-okayama</t>
@@ -2759,7 +2753,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I263"/>
+  <dimension ref="A1:I262"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.39"/>
@@ -3578,10 +3572,10 @@
         <v>142</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G38" s="0" t="s">
         <v>143</v>
@@ -3598,13 +3592,13 @@
         <v>145</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>29</v>
+        <v>146</v>
       </c>
       <c r="F39" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H39" s="0" t="s">
         <v>16</v>
@@ -3612,13 +3606,13 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F40" s="0" t="s">
         <v>30</v>
@@ -3638,7 +3632,7 @@
         <v>152</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F41" s="0" t="s">
         <v>30</v>
@@ -3658,7 +3652,7 @@
         <v>155</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>149</v>
+        <v>29</v>
       </c>
       <c r="F42" s="0" t="s">
         <v>30</v>
@@ -3678,7 +3672,7 @@
         <v>158</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F43" s="0" t="s">
         <v>30</v>
@@ -3698,13 +3692,13 @@
         <v>161</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>35</v>
+        <v>162</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>30</v>
+        <v>162</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H44" s="0" t="s">
         <v>16</v>
@@ -3712,16 +3706,16 @@
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>165</v>
+        <v>29</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>165</v>
+        <v>30</v>
       </c>
       <c r="G45" s="0" t="s">
         <v>166</v>
@@ -3738,10 +3732,10 @@
         <v>168</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G46" s="0" t="s">
         <v>169</v>
@@ -3758,13 +3752,13 @@
         <v>171</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>13</v>
+        <v>172</v>
       </c>
       <c r="F47" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H47" s="0" t="s">
         <v>16</v>
@@ -3772,16 +3766,16 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>175</v>
+        <v>58</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G48" s="0" t="s">
         <v>176</v>
@@ -3798,13 +3792,13 @@
         <v>178</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="G49" s="0" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H49" s="0" t="s">
         <v>16</v>
@@ -3812,16 +3806,16 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>182</v>
+        <v>62</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>183</v>
+        <v>30</v>
       </c>
       <c r="G50" s="0" t="s">
         <v>184</v>
@@ -3878,7 +3872,7 @@
         <v>192</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="F53" s="0" t="s">
         <v>30</v>
@@ -3918,13 +3912,13 @@
         <v>198</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>29</v>
+        <v>199</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H55" s="0" t="s">
         <v>16</v>
@@ -3932,19 +3926,19 @@
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H56" s="0" t="s">
         <v>16</v>
@@ -3952,19 +3946,19 @@
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H57" s="0" t="s">
         <v>16</v>
@@ -3972,16 +3966,16 @@
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>210</v>
+        <v>35</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="G58" s="0" t="s">
         <v>211</v>
@@ -3998,7 +3992,7 @@
         <v>213</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F59" s="0" t="s">
         <v>30</v>
@@ -4018,7 +4012,7 @@
         <v>216</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="F60" s="0" t="s">
         <v>30</v>
@@ -4038,10 +4032,10 @@
         <v>219</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>62</v>
+        <v>203</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G61" s="0" t="s">
         <v>220</v>
@@ -4058,13 +4052,13 @@
         <v>222</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="F62" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H62" s="0" t="s">
         <v>16</v>
@@ -4072,13 +4066,13 @@
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F63" s="0" t="s">
         <v>14</v>
@@ -4098,13 +4092,13 @@
         <v>229</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H64" s="0" t="s">
         <v>16</v>
@@ -4112,19 +4106,19 @@
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F65" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G65" s="0" t="s">
-        <v>234</v>
+        <v>25</v>
       </c>
       <c r="H65" s="0" t="s">
         <v>16</v>
@@ -4138,13 +4132,13 @@
         <v>236</v>
       </c>
       <c r="E66" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="F66" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G66" s="0" t="s">
         <v>237</v>
-      </c>
-      <c r="F66" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G66" s="0" t="s">
-        <v>25</v>
       </c>
       <c r="H66" s="0" t="s">
         <v>16</v>
@@ -4158,10 +4152,10 @@
         <v>239</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>58</v>
+        <v>234</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G67" s="0" t="s">
         <v>240</v>
@@ -4178,13 +4172,13 @@
         <v>242</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H68" s="0" t="s">
         <v>16</v>
@@ -4192,16 +4186,16 @@
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>246</v>
+        <v>58</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G69" s="0" t="s">
         <v>247</v>
@@ -4218,13 +4212,13 @@
         <v>249</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>58</v>
+        <v>250</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>20</v>
+        <v>251</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H70" s="0" t="s">
         <v>16</v>
@@ -4232,19 +4226,19 @@
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>253</v>
+        <v>75</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>254</v>
+        <v>76</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>143</v>
+        <v>255</v>
       </c>
       <c r="H71" s="0" t="s">
         <v>16</v>
@@ -4252,19 +4246,19 @@
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>75</v>
+        <v>258</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>76</v>
+        <v>259</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="H72" s="0" t="s">
         <v>16</v>
@@ -4272,19 +4266,19 @@
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>261</v>
+        <v>14</v>
       </c>
       <c r="G73" s="0" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H73" s="0" t="s">
         <v>16</v>
@@ -4292,19 +4286,19 @@
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>265</v>
+        <v>19</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H74" s="0" t="s">
         <v>16</v>
@@ -4312,19 +4306,19 @@
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>19</v>
+        <v>203</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G75" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H75" s="0" t="s">
         <v>16</v>
@@ -4332,19 +4326,19 @@
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>206</v>
+        <v>35</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H76" s="0" t="s">
         <v>16</v>
@@ -4352,19 +4346,19 @@
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F77" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H77" s="0" t="s">
         <v>16</v>
@@ -4372,19 +4366,19 @@
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>29</v>
+        <v>279</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>30</v>
+        <v>251</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H78" s="0" t="s">
         <v>16</v>
@@ -4392,19 +4386,19 @@
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>281</v>
+        <v>120</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>254</v>
+        <v>14</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H79" s="0" t="s">
         <v>16</v>
@@ -4412,19 +4406,19 @@
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>120</v>
+        <v>207</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H80" s="0" t="s">
         <v>16</v>
@@ -4432,19 +4426,19 @@
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>210</v>
+        <v>289</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>76</v>
+        <v>180</v>
       </c>
       <c r="G81" s="0" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="H81" s="0" t="s">
         <v>16</v>
@@ -4452,19 +4446,19 @@
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>183</v>
+        <v>251</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H82" s="0" t="s">
         <v>16</v>
@@ -4472,19 +4466,19 @@
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>295</v>
+        <v>13</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>254</v>
+        <v>14</v>
       </c>
       <c r="G83" s="0" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H83" s="0" t="s">
         <v>16</v>
@@ -4492,19 +4486,19 @@
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E84" s="0" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G84" s="0" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H84" s="0" t="s">
         <v>16</v>
@@ -4512,19 +4506,19 @@
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>62</v>
+        <v>303</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H85" s="0" t="s">
         <v>16</v>
@@ -4532,19 +4526,19 @@
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>305</v>
+        <v>80</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="G86" s="0" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H86" s="0" t="s">
         <v>16</v>
@@ -4552,19 +4546,19 @@
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>80</v>
+        <v>203</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G87" s="0" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H87" s="0" t="s">
         <v>16</v>
@@ -4572,19 +4566,19 @@
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E88" s="0" t="s">
-        <v>206</v>
+        <v>313</v>
       </c>
       <c r="F88" s="0" t="s">
-        <v>14</v>
+        <v>259</v>
       </c>
       <c r="G88" s="0" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H88" s="0" t="s">
         <v>16</v>
@@ -4592,19 +4586,19 @@
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E89" s="0" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>261</v>
+        <v>20</v>
       </c>
       <c r="G89" s="0" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H89" s="0" t="s">
         <v>16</v>
@@ -4612,19 +4606,19 @@
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E90" s="0" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F90" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G90" s="0" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H90" s="0" t="s">
         <v>16</v>
@@ -4632,19 +4626,19 @@
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E91" s="0" t="s">
-        <v>323</v>
+        <v>243</v>
       </c>
       <c r="F91" s="0" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G91" s="0" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H91" s="0" t="s">
         <v>16</v>
@@ -4652,19 +4646,25 @@
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>326</v>
+        <v>327</v>
+      </c>
+      <c r="C92" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="D92" s="0" t="s">
+        <v>12</v>
       </c>
       <c r="E92" s="0" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F92" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G92" s="0" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H92" s="0" t="s">
         <v>16</v>
@@ -4672,25 +4672,19 @@
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>329</v>
-      </c>
-      <c r="C93" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="D93" s="0" t="s">
-        <v>12</v>
+        <v>330</v>
       </c>
       <c r="E93" s="0" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F93" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G93" s="0" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H93" s="0" t="s">
         <v>16</v>
@@ -4698,19 +4692,19 @@
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E94" s="0" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F94" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G94" s="0" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H94" s="0" t="s">
         <v>16</v>
@@ -4718,19 +4712,19 @@
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E95" s="0" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F95" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G95" s="0" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H95" s="0" t="s">
         <v>16</v>
@@ -4738,19 +4732,19 @@
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E96" s="0" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F96" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G96" s="0" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H96" s="0" t="s">
         <v>16</v>
@@ -4758,19 +4752,19 @@
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E97" s="0" t="s">
-        <v>246</v>
+        <v>13</v>
       </c>
       <c r="F97" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G97" s="0" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H97" s="0" t="s">
         <v>16</v>
@@ -4778,19 +4772,19 @@
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E98" s="0" t="s">
-        <v>13</v>
+        <v>317</v>
       </c>
       <c r="F98" s="0" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G98" s="0" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H98" s="0" t="s">
         <v>16</v>
@@ -4798,19 +4792,19 @@
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>319</v>
+        <v>19</v>
       </c>
       <c r="F99" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G99" s="0" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H99" s="0" t="s">
         <v>16</v>
@@ -4818,19 +4812,19 @@
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E100" s="0" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="F100" s="0" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G100" s="0" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H100" s="0" t="s">
         <v>16</v>
@@ -4838,19 +4832,19 @@
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E101" s="0" t="s">
-        <v>226</v>
+        <v>62</v>
       </c>
       <c r="F101" s="0" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G101" s="0" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H101" s="0" t="s">
         <v>16</v>
@@ -4858,19 +4852,19 @@
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E102" s="0" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="F102" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G102" s="0" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H102" s="0" t="s">
         <v>16</v>
@@ -4878,19 +4872,19 @@
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E103" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F103" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G103" s="0" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H103" s="0" t="s">
         <v>16</v>
@@ -4898,19 +4892,19 @@
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E104" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F104" s="0" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G104" s="0" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H104" s="0" t="s">
         <v>16</v>
@@ -4918,19 +4912,19 @@
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E105" s="0" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G105" s="0" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H105" s="0" t="s">
         <v>16</v>
@@ -4938,19 +4932,19 @@
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E106" s="0" t="s">
-        <v>29</v>
+        <v>230</v>
       </c>
       <c r="F106" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G106" s="0" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H106" s="0" t="s">
         <v>16</v>
@@ -4958,19 +4952,19 @@
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E107" s="0" t="s">
-        <v>233</v>
+        <v>24</v>
       </c>
       <c r="F107" s="0" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G107" s="0" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H107" s="0" t="s">
         <v>16</v>
@@ -4978,19 +4972,19 @@
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E108" s="0" t="s">
-        <v>24</v>
+        <v>146</v>
       </c>
       <c r="F108" s="0" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G108" s="0" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H108" s="0" t="s">
         <v>16</v>
@@ -4998,19 +4992,19 @@
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E109" s="0" t="s">
-        <v>149</v>
+        <v>29</v>
       </c>
       <c r="F109" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G109" s="0" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H109" s="0" t="s">
         <v>16</v>
@@ -5018,19 +5012,19 @@
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E110" s="0" t="s">
-        <v>29</v>
+        <v>124</v>
       </c>
       <c r="F110" s="0" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G110" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H110" s="0" t="s">
         <v>16</v>
@@ -5038,19 +5032,25 @@
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>383</v>
+        <v>384</v>
+      </c>
+      <c r="C111" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="D111" s="0" t="s">
+        <v>12</v>
       </c>
       <c r="E111" s="0" t="s">
-        <v>124</v>
+        <v>230</v>
       </c>
       <c r="F111" s="0" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G111" s="0" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H111" s="0" t="s">
         <v>16</v>
@@ -5058,25 +5058,19 @@
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="0" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>386</v>
-      </c>
-      <c r="C112" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="D112" s="0" t="s">
-        <v>12</v>
+        <v>387</v>
       </c>
       <c r="E112" s="0" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F112" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G112" s="0" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H112" s="0" t="s">
         <v>16</v>
@@ -5084,19 +5078,19 @@
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E113" s="0" t="s">
-        <v>233</v>
+        <v>80</v>
       </c>
       <c r="F113" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G113" s="0" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H113" s="0" t="s">
         <v>16</v>
@@ -5104,19 +5098,19 @@
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="0" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E114" s="0" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="F114" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G114" s="0" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H114" s="0" t="s">
         <v>16</v>
@@ -5124,10 +5118,10 @@
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="0" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E115" s="0" t="s">
         <v>29</v>
@@ -5136,7 +5130,7 @@
         <v>30</v>
       </c>
       <c r="G115" s="0" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H115" s="0" t="s">
         <v>16</v>
@@ -5144,10 +5138,10 @@
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E116" s="0" t="s">
         <v>29</v>
@@ -5156,7 +5150,7 @@
         <v>30</v>
       </c>
       <c r="G116" s="0" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H116" s="0" t="s">
         <v>16</v>
@@ -5164,10 +5158,10 @@
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E117" s="0" t="s">
         <v>29</v>
@@ -5176,7 +5170,7 @@
         <v>30</v>
       </c>
       <c r="G117" s="0" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H117" s="0" t="s">
         <v>16</v>
@@ -5184,19 +5178,19 @@
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E118" s="0" t="s">
-        <v>29</v>
+        <v>263</v>
       </c>
       <c r="F118" s="0" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G118" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H118" s="0" t="s">
         <v>16</v>
@@ -5204,19 +5198,19 @@
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E119" s="0" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="F119" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G119" s="0" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H119" s="0" t="s">
         <v>16</v>
@@ -5224,19 +5218,19 @@
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E120" s="0" t="s">
-        <v>246</v>
+        <v>117</v>
       </c>
       <c r="F120" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G120" s="0" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H120" s="0" t="s">
         <v>16</v>
@@ -5244,19 +5238,19 @@
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E121" s="0" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="F121" s="0" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G121" s="0" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H121" s="0" t="s">
         <v>16</v>
@@ -5264,19 +5258,19 @@
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="0" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E122" s="0" t="s">
-        <v>29</v>
+        <v>124</v>
       </c>
       <c r="F122" s="0" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G122" s="0" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H122" s="0" t="s">
         <v>16</v>
@@ -5284,19 +5278,19 @@
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E123" s="0" t="s">
-        <v>124</v>
+        <v>29</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G123" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H123" s="0" t="s">
         <v>16</v>
@@ -5304,10 +5298,10 @@
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="0" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E124" s="0" t="s">
         <v>29</v>
@@ -5316,7 +5310,7 @@
         <v>30</v>
       </c>
       <c r="G124" s="0" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H124" s="0" t="s">
         <v>16</v>
@@ -5324,10 +5318,10 @@
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E125" s="0" t="s">
         <v>29</v>
@@ -5336,7 +5330,7 @@
         <v>30</v>
       </c>
       <c r="G125" s="0" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H125" s="0" t="s">
         <v>16</v>
@@ -5344,10 +5338,10 @@
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="0" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E126" s="0" t="s">
         <v>29</v>
@@ -5356,7 +5350,7 @@
         <v>30</v>
       </c>
       <c r="G126" s="0" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H126" s="0" t="s">
         <v>16</v>
@@ -5364,10 +5358,10 @@
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E127" s="0" t="s">
         <v>29</v>
@@ -5376,7 +5370,7 @@
         <v>30</v>
       </c>
       <c r="G127" s="0" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H127" s="0" t="s">
         <v>16</v>
@@ -5384,10 +5378,10 @@
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E128" s="0" t="s">
         <v>29</v>
@@ -5396,7 +5390,7 @@
         <v>30</v>
       </c>
       <c r="G128" s="0" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H128" s="0" t="s">
         <v>16</v>
@@ -5404,10 +5398,10 @@
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E129" s="0" t="s">
         <v>29</v>
@@ -5416,7 +5410,7 @@
         <v>30</v>
       </c>
       <c r="G129" s="0" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H129" s="0" t="s">
         <v>16</v>
@@ -5424,19 +5418,19 @@
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="0" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B130" s="0" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E130" s="0" t="s">
-        <v>29</v>
+        <v>263</v>
       </c>
       <c r="F130" s="0" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G130" s="0" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H130" s="0" t="s">
         <v>16</v>
@@ -5444,19 +5438,19 @@
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="0" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E131" s="0" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="F131" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G131" s="0" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H131" s="0" t="s">
         <v>16</v>
@@ -5464,19 +5458,19 @@
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="0" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B132" s="0" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E132" s="0" t="s">
-        <v>246</v>
+        <v>29</v>
       </c>
       <c r="F132" s="0" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G132" s="0" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H132" s="0" t="s">
         <v>16</v>
@@ -5484,19 +5478,19 @@
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E133" s="0" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="F133" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G133" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H133" s="0" t="s">
         <v>16</v>
@@ -5504,19 +5498,19 @@
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E134" s="0" t="s">
-        <v>62</v>
+        <v>234</v>
       </c>
       <c r="F134" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G134" s="0" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H134" s="0" t="s">
         <v>16</v>
@@ -5524,19 +5518,19 @@
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="0" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E135" s="0" t="s">
-        <v>237</v>
+        <v>293</v>
       </c>
       <c r="F135" s="0" t="s">
-        <v>30</v>
+        <v>251</v>
       </c>
       <c r="G135" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H135" s="0" t="s">
         <v>16</v>
@@ -5544,19 +5538,19 @@
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E136" s="0" t="s">
-        <v>295</v>
+        <v>117</v>
       </c>
       <c r="F136" s="0" t="s">
-        <v>254</v>
+        <v>14</v>
       </c>
       <c r="G136" s="0" t="s">
-        <v>459</v>
+        <v>169</v>
       </c>
       <c r="H136" s="0" t="s">
         <v>16</v>
@@ -5576,7 +5570,7 @@
         <v>14</v>
       </c>
       <c r="G137" s="0" t="s">
-        <v>172</v>
+        <v>96</v>
       </c>
       <c r="H137" s="0" t="s">
         <v>16</v>
@@ -5596,7 +5590,7 @@
         <v>14</v>
       </c>
       <c r="G138" s="0" t="s">
-        <v>96</v>
+        <v>464</v>
       </c>
       <c r="H138" s="0" t="s">
         <v>16</v>
@@ -5604,19 +5598,25 @@
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="0" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
+      </c>
+      <c r="C139" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="D139" s="0" t="s">
+        <v>12</v>
       </c>
       <c r="E139" s="0" t="s">
-        <v>117</v>
+        <v>35</v>
       </c>
       <c r="F139" s="0" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G139" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H139" s="0" t="s">
         <v>16</v>
@@ -5624,16 +5624,10 @@
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="0" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>468</v>
-      </c>
-      <c r="C140" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="D140" s="0" t="s">
-        <v>12</v>
+        <v>469</v>
       </c>
       <c r="E140" s="0" t="s">
         <v>35</v>
@@ -5642,7 +5636,7 @@
         <v>30</v>
       </c>
       <c r="G140" s="0" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H140" s="0" t="s">
         <v>16</v>
@@ -5650,10 +5644,10 @@
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E141" s="0" t="s">
         <v>35</v>
@@ -5662,7 +5656,7 @@
         <v>30</v>
       </c>
       <c r="G141" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H141" s="0" t="s">
         <v>16</v>
@@ -5670,19 +5664,19 @@
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B142" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E142" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F142" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G142" s="0" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H142" s="0" t="s">
         <v>16</v>
@@ -5690,19 +5684,19 @@
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="0" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E143" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F143" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G143" s="0" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H143" s="0" t="s">
         <v>16</v>
@@ -5710,19 +5704,25 @@
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="0" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B144" s="0" t="s">
-        <v>480</v>
+        <v>481</v>
+      </c>
+      <c r="C144" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D144" s="0" t="s">
+        <v>12</v>
       </c>
       <c r="E144" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F144" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G144" s="0" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H144" s="0" t="s">
         <v>16</v>
@@ -5730,10 +5730,10 @@
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="0" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B145" s="0" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C145" s="0" t="s">
         <v>28</v>
@@ -5748,7 +5748,7 @@
         <v>30</v>
       </c>
       <c r="G145" s="0" t="s">
-        <v>484</v>
+        <v>143</v>
       </c>
       <c r="H145" s="0" t="s">
         <v>16</v>
@@ -5774,7 +5774,7 @@
         <v>30</v>
       </c>
       <c r="G146" s="0" t="s">
-        <v>146</v>
+        <v>487</v>
       </c>
       <c r="H146" s="0" t="s">
         <v>16</v>
@@ -5782,10 +5782,10 @@
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="0" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B147" s="0" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C147" s="0" t="s">
         <v>28</v>
@@ -5800,7 +5800,7 @@
         <v>30</v>
       </c>
       <c r="G147" s="0" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H147" s="0" t="s">
         <v>16</v>
@@ -5808,10 +5808,10 @@
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="0" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B148" s="0" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C148" s="0" t="s">
         <v>28</v>
@@ -5826,7 +5826,7 @@
         <v>30</v>
       </c>
       <c r="G148" s="0" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H148" s="0" t="s">
         <v>16</v>
@@ -5834,10 +5834,10 @@
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="0" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B149" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C149" s="0" t="s">
         <v>28</v>
@@ -5852,7 +5852,7 @@
         <v>30</v>
       </c>
       <c r="G149" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H149" s="0" t="s">
         <v>16</v>
@@ -5860,10 +5860,10 @@
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="0" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B150" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C150" s="0" t="s">
         <v>28</v>
@@ -5878,7 +5878,7 @@
         <v>30</v>
       </c>
       <c r="G150" s="0" t="s">
-        <v>498</v>
+        <v>433</v>
       </c>
       <c r="H150" s="0" t="s">
         <v>16</v>
@@ -5904,7 +5904,7 @@
         <v>30</v>
       </c>
       <c r="G151" s="0" t="s">
-        <v>435</v>
+        <v>501</v>
       </c>
       <c r="H151" s="0" t="s">
         <v>16</v>
@@ -5912,10 +5912,10 @@
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="0" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B152" s="0" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C152" s="0" t="s">
         <v>28</v>
@@ -5930,7 +5930,7 @@
         <v>30</v>
       </c>
       <c r="G152" s="0" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H152" s="0" t="s">
         <v>16</v>
@@ -5938,10 +5938,10 @@
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="0" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B153" s="0" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C153" s="0" t="s">
         <v>28</v>
@@ -5956,7 +5956,7 @@
         <v>30</v>
       </c>
       <c r="G153" s="0" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H153" s="0" t="s">
         <v>16</v>
@@ -5964,10 +5964,10 @@
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="0" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B154" s="0" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C154" s="0" t="s">
         <v>28</v>
@@ -5982,7 +5982,7 @@
         <v>30</v>
       </c>
       <c r="G154" s="0" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H154" s="0" t="s">
         <v>16</v>
@@ -5990,10 +5990,10 @@
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="0" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B155" s="0" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C155" s="0" t="s">
         <v>28</v>
@@ -6008,7 +6008,7 @@
         <v>30</v>
       </c>
       <c r="G155" s="0" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H155" s="0" t="s">
         <v>16</v>
@@ -6016,10 +6016,10 @@
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="0" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B156" s="0" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C156" s="0" t="s">
         <v>28</v>
@@ -6034,7 +6034,7 @@
         <v>30</v>
       </c>
       <c r="G156" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H156" s="0" t="s">
         <v>16</v>
@@ -6042,10 +6042,10 @@
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="0" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B157" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C157" s="0" t="s">
         <v>28</v>
@@ -6060,7 +6060,7 @@
         <v>30</v>
       </c>
       <c r="G157" s="0" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H157" s="0" t="s">
         <v>16</v>
@@ -6068,10 +6068,10 @@
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="0" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B158" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C158" s="0" t="s">
         <v>28</v>
@@ -6086,7 +6086,7 @@
         <v>30</v>
       </c>
       <c r="G158" s="0" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H158" s="0" t="s">
         <v>16</v>
@@ -6094,10 +6094,10 @@
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="0" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B159" s="0" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C159" s="0" t="s">
         <v>28</v>
@@ -6112,7 +6112,7 @@
         <v>30</v>
       </c>
       <c r="G159" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H159" s="0" t="s">
         <v>16</v>
@@ -6120,10 +6120,10 @@
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="0" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B160" s="0" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C160" s="0" t="s">
         <v>28</v>
@@ -6138,7 +6138,7 @@
         <v>30</v>
       </c>
       <c r="G160" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H160" s="0" t="s">
         <v>16</v>
@@ -6146,10 +6146,10 @@
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="0" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B161" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C161" s="0" t="s">
         <v>28</v>
@@ -6164,7 +6164,7 @@
         <v>30</v>
       </c>
       <c r="G161" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H161" s="0" t="s">
         <v>16</v>
@@ -6172,10 +6172,10 @@
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="0" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B162" s="0" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C162" s="0" t="s">
         <v>28</v>
@@ -6190,7 +6190,7 @@
         <v>30</v>
       </c>
       <c r="G162" s="0" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H162" s="0" t="s">
         <v>16</v>
@@ -6198,10 +6198,10 @@
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="0" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B163" s="0" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C163" s="0" t="s">
         <v>28</v>
@@ -6216,7 +6216,7 @@
         <v>30</v>
       </c>
       <c r="G163" s="0" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H163" s="0" t="s">
         <v>16</v>
@@ -6224,10 +6224,10 @@
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="0" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B164" s="0" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C164" s="0" t="s">
         <v>28</v>
@@ -6242,7 +6242,7 @@
         <v>30</v>
       </c>
       <c r="G164" s="0" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H164" s="0" t="s">
         <v>16</v>
@@ -6250,10 +6250,10 @@
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="0" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B165" s="0" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C165" s="0" t="s">
         <v>28</v>
@@ -6268,7 +6268,7 @@
         <v>30</v>
       </c>
       <c r="G165" s="0" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H165" s="0" t="s">
         <v>16</v>
@@ -6276,25 +6276,25 @@
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B166" s="0" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C166" s="0" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D166" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E166" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F166" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G166" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H166" s="0" t="s">
         <v>16</v>
@@ -6302,10 +6302,10 @@
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B167" s="0" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C167" s="0" t="s">
         <v>11</v>
@@ -6320,7 +6320,7 @@
         <v>30</v>
       </c>
       <c r="G167" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H167" s="0" t="s">
         <v>16</v>
@@ -6328,10 +6328,10 @@
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B168" s="0" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C168" s="0" t="s">
         <v>11</v>
@@ -6346,7 +6346,7 @@
         <v>30</v>
       </c>
       <c r="G168" s="0" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H168" s="0" t="s">
         <v>16</v>
@@ -6354,10 +6354,10 @@
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="0" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B169" s="0" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C169" s="0" t="s">
         <v>11</v>
@@ -6372,7 +6372,7 @@
         <v>30</v>
       </c>
       <c r="G169" s="0" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H169" s="0" t="s">
         <v>16</v>
@@ -6380,10 +6380,10 @@
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="0" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B170" s="0" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C170" s="0" t="s">
         <v>11</v>
@@ -6398,7 +6398,7 @@
         <v>30</v>
       </c>
       <c r="G170" s="0" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H170" s="0" t="s">
         <v>16</v>
@@ -6406,10 +6406,10 @@
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="0" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B171" s="0" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C171" s="0" t="s">
         <v>11</v>
@@ -6424,7 +6424,7 @@
         <v>30</v>
       </c>
       <c r="G171" s="0" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H171" s="0" t="s">
         <v>16</v>
@@ -6432,10 +6432,10 @@
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="0" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B172" s="0" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C172" s="0" t="s">
         <v>11</v>
@@ -6450,7 +6450,7 @@
         <v>30</v>
       </c>
       <c r="G172" s="0" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H172" s="0" t="s">
         <v>16</v>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="0" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B173" s="0" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C173" s="0" t="s">
         <v>11</v>
@@ -6470,13 +6470,13 @@
         <v>12</v>
       </c>
       <c r="E173" s="0" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="F173" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G173" s="0" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H173" s="0" t="s">
         <v>16</v>
@@ -6484,10 +6484,10 @@
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="0" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B174" s="0" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C174" s="0" t="s">
         <v>11</v>
@@ -6502,7 +6502,7 @@
         <v>30</v>
       </c>
       <c r="G174" s="0" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H174" s="0" t="s">
         <v>16</v>
@@ -6510,10 +6510,10 @@
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="0" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B175" s="0" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C175" s="0" t="s">
         <v>11</v>
@@ -6528,7 +6528,7 @@
         <v>30</v>
       </c>
       <c r="G175" s="0" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H175" s="0" t="s">
         <v>16</v>
@@ -6536,10 +6536,10 @@
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="0" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B176" s="0" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C176" s="0" t="s">
         <v>11</v>
@@ -6554,7 +6554,7 @@
         <v>30</v>
       </c>
       <c r="G176" s="0" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H176" s="0" t="s">
         <v>16</v>
@@ -6562,10 +6562,10 @@
     </row>
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="0" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B177" s="0" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C177" s="0" t="s">
         <v>11</v>
@@ -6580,7 +6580,7 @@
         <v>30</v>
       </c>
       <c r="G177" s="0" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H177" s="0" t="s">
         <v>16</v>
@@ -6588,10 +6588,10 @@
     </row>
     <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="0" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B178" s="0" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C178" s="0" t="s">
         <v>11</v>
@@ -6600,13 +6600,13 @@
         <v>12</v>
       </c>
       <c r="E178" s="0" t="s">
-        <v>80</v>
+        <v>230</v>
       </c>
       <c r="F178" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G178" s="0" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H178" s="0" t="s">
         <v>16</v>
@@ -6614,10 +6614,10 @@
     </row>
     <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="0" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B179" s="0" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C179" s="0" t="s">
         <v>11</v>
@@ -6626,13 +6626,13 @@
         <v>12</v>
       </c>
       <c r="E179" s="0" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F179" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G179" s="0" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H179" s="0" t="s">
         <v>16</v>
@@ -6640,10 +6640,10 @@
     </row>
     <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="0" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B180" s="0" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C180" s="0" t="s">
         <v>11</v>
@@ -6652,13 +6652,13 @@
         <v>12</v>
       </c>
       <c r="E180" s="0" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F180" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G180" s="0" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H180" s="0" t="s">
         <v>16</v>
@@ -6666,10 +6666,10 @@
     </row>
     <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="0" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B181" s="0" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C181" s="0" t="s">
         <v>11</v>
@@ -6678,13 +6678,13 @@
         <v>12</v>
       </c>
       <c r="E181" s="0" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F181" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G181" s="0" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H181" s="0" t="s">
         <v>16</v>
@@ -6692,10 +6692,10 @@
     </row>
     <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="0" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B182" s="0" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C182" s="0" t="s">
         <v>11</v>
@@ -6704,13 +6704,13 @@
         <v>12</v>
       </c>
       <c r="E182" s="0" t="s">
-        <v>233</v>
+        <v>62</v>
       </c>
       <c r="F182" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G182" s="0" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H182" s="0" t="s">
         <v>16</v>
@@ -6718,10 +6718,10 @@
     </row>
     <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="0" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B183" s="0" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C183" s="0" t="s">
         <v>11</v>
@@ -6736,7 +6736,7 @@
         <v>30</v>
       </c>
       <c r="G183" s="0" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H183" s="0" t="s">
         <v>16</v>
@@ -6744,10 +6744,10 @@
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="0" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B184" s="0" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C184" s="0" t="s">
         <v>11</v>
@@ -6756,13 +6756,13 @@
         <v>12</v>
       </c>
       <c r="E184" s="0" t="s">
-        <v>62</v>
+        <v>234</v>
       </c>
       <c r="F184" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G184" s="0" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H184" s="0" t="s">
         <v>16</v>
@@ -6770,10 +6770,10 @@
     </row>
     <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="0" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B185" s="0" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C185" s="0" t="s">
         <v>11</v>
@@ -6782,13 +6782,13 @@
         <v>12</v>
       </c>
       <c r="E185" s="0" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F185" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G185" s="0" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H185" s="0" t="s">
         <v>16</v>
@@ -6796,25 +6796,25 @@
     </row>
     <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B186" s="0" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C186" s="0" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D186" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E186" s="0" t="s">
-        <v>237</v>
+        <v>146</v>
       </c>
       <c r="F186" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G186" s="0" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H186" s="0" t="s">
         <v>16</v>
@@ -6822,10 +6822,10 @@
     </row>
     <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="0" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B187" s="0" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C187" s="0" t="s">
         <v>34</v>
@@ -6834,13 +6834,13 @@
         <v>12</v>
       </c>
       <c r="E187" s="0" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F187" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G187" s="0" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H187" s="0" t="s">
         <v>16</v>
@@ -6848,25 +6848,25 @@
     </row>
     <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="0" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B188" s="0" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C188" s="0" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D188" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E188" s="0" t="s">
-        <v>149</v>
+        <v>13</v>
       </c>
       <c r="F188" s="0" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G188" s="0" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H188" s="0" t="s">
         <v>16</v>
@@ -6874,10 +6874,10 @@
     </row>
     <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="0" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B189" s="0" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C189" s="0" t="s">
         <v>11</v>
@@ -6892,7 +6892,7 @@
         <v>14</v>
       </c>
       <c r="G189" s="0" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H189" s="0" t="s">
         <v>16</v>
@@ -6900,10 +6900,10 @@
     </row>
     <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="0" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B190" s="0" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C190" s="0" t="s">
         <v>11</v>
@@ -6918,7 +6918,7 @@
         <v>14</v>
       </c>
       <c r="G190" s="0" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H190" s="0" t="s">
         <v>16</v>
@@ -6926,10 +6926,10 @@
     </row>
     <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="0" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B191" s="0" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C191" s="0" t="s">
         <v>11</v>
@@ -6938,13 +6938,13 @@
         <v>12</v>
       </c>
       <c r="E191" s="0" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="F191" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G191" s="0" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H191" s="0" t="s">
         <v>16</v>
@@ -6952,10 +6952,10 @@
     </row>
     <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="0" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B192" s="0" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C192" s="0" t="s">
         <v>11</v>
@@ -6970,7 +6970,7 @@
         <v>14</v>
       </c>
       <c r="G192" s="0" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H192" s="0" t="s">
         <v>16</v>
@@ -6978,10 +6978,10 @@
     </row>
     <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="0" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B193" s="0" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C193" s="0" t="s">
         <v>11</v>
@@ -6996,7 +6996,7 @@
         <v>14</v>
       </c>
       <c r="G193" s="0" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H193" s="0" t="s">
         <v>16</v>
@@ -7004,10 +7004,10 @@
     </row>
     <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="0" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B194" s="0" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C194" s="0" t="s">
         <v>11</v>
@@ -7016,13 +7016,13 @@
         <v>12</v>
       </c>
       <c r="E194" s="0" t="s">
-        <v>40</v>
+        <v>203</v>
       </c>
       <c r="F194" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G194" s="0" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H194" s="0" t="s">
         <v>16</v>
@@ -7030,10 +7030,10 @@
     </row>
     <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="0" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B195" s="0" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C195" s="0" t="s">
         <v>11</v>
@@ -7042,13 +7042,13 @@
         <v>12</v>
       </c>
       <c r="E195" s="0" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F195" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G195" s="0" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H195" s="0" t="s">
         <v>16</v>
@@ -7056,10 +7056,10 @@
     </row>
     <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="0" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B196" s="0" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C196" s="0" t="s">
         <v>11</v>
@@ -7068,13 +7068,13 @@
         <v>12</v>
       </c>
       <c r="E196" s="0" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F196" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G196" s="0" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H196" s="0" t="s">
         <v>16</v>
@@ -7082,10 +7082,10 @@
     </row>
     <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="0" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B197" s="0" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C197" s="0" t="s">
         <v>11</v>
@@ -7094,13 +7094,13 @@
         <v>12</v>
       </c>
       <c r="E197" s="0" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F197" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G197" s="0" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H197" s="0" t="s">
         <v>16</v>
@@ -7108,10 +7108,10 @@
     </row>
     <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="0" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B198" s="0" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C198" s="0" t="s">
         <v>11</v>
@@ -7120,13 +7120,13 @@
         <v>12</v>
       </c>
       <c r="E198" s="0" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F198" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G198" s="0" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H198" s="0" t="s">
         <v>16</v>
@@ -7134,10 +7134,10 @@
     </row>
     <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="0" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B199" s="0" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C199" s="0" t="s">
         <v>11</v>
@@ -7146,13 +7146,13 @@
         <v>12</v>
       </c>
       <c r="E199" s="0" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F199" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G199" s="0" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H199" s="0" t="s">
         <v>16</v>
@@ -7160,10 +7160,10 @@
     </row>
     <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="0" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B200" s="0" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C200" s="0" t="s">
         <v>11</v>
@@ -7172,13 +7172,13 @@
         <v>12</v>
       </c>
       <c r="E200" s="0" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F200" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G200" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H200" s="0" t="s">
         <v>16</v>
@@ -7186,10 +7186,10 @@
     </row>
     <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="0" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B201" s="0" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C201" s="0" t="s">
         <v>11</v>
@@ -7198,13 +7198,13 @@
         <v>12</v>
       </c>
       <c r="E201" s="0" t="s">
-        <v>206</v>
+        <v>117</v>
       </c>
       <c r="F201" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G201" s="0" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H201" s="0" t="s">
         <v>16</v>
@@ -7212,13 +7212,13 @@
     </row>
     <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B202" s="0" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C202" s="0" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D202" s="0" t="s">
         <v>12</v>
@@ -7230,7 +7230,7 @@
         <v>14</v>
       </c>
       <c r="G202" s="0" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H202" s="0" t="s">
         <v>16</v>
@@ -7238,25 +7238,25 @@
     </row>
     <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="0" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B203" s="0" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C203" s="0" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D203" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E203" s="0" t="s">
-        <v>117</v>
+        <v>243</v>
       </c>
       <c r="F203" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G203" s="0" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H203" s="0" t="s">
         <v>16</v>
@@ -7264,25 +7264,25 @@
     </row>
     <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="0" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B204" s="0" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C204" s="0" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D204" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E204" s="0" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F204" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G204" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H204" s="0" t="s">
         <v>16</v>
@@ -7290,25 +7290,25 @@
     </row>
     <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B205" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C205" s="0" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D205" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E205" s="0" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F205" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G205" s="0" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H205" s="0" t="s">
         <v>16</v>
@@ -7316,25 +7316,25 @@
     </row>
     <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="0" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B206" s="0" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C206" s="0" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D206" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E206" s="0" t="s">
-        <v>246</v>
+        <v>19</v>
       </c>
       <c r="F206" s="0" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G206" s="0" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H206" s="0" t="s">
         <v>16</v>
@@ -7342,10 +7342,10 @@
     </row>
     <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="0" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B207" s="0" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C207" s="0" t="s">
         <v>11</v>
@@ -7360,7 +7360,7 @@
         <v>20</v>
       </c>
       <c r="G207" s="0" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H207" s="0" t="s">
         <v>16</v>
@@ -7368,10 +7368,10 @@
     </row>
     <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="0" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B208" s="0" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C208" s="0" t="s">
         <v>11</v>
@@ -7380,13 +7380,13 @@
         <v>12</v>
       </c>
       <c r="E208" s="0" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F208" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G208" s="0" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H208" s="0" t="s">
         <v>16</v>
@@ -7394,10 +7394,10 @@
     </row>
     <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="0" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B209" s="0" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C209" s="0" t="s">
         <v>11</v>
@@ -7406,13 +7406,13 @@
         <v>12</v>
       </c>
       <c r="E209" s="0" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="F209" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G209" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H209" s="0" t="s">
         <v>16</v>
@@ -7420,10 +7420,10 @@
     </row>
     <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B210" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C210" s="0" t="s">
         <v>11</v>
@@ -7438,7 +7438,7 @@
         <v>20</v>
       </c>
       <c r="G210" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H210" s="0" t="s">
         <v>16</v>
@@ -7446,10 +7446,10 @@
     </row>
     <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="0" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B211" s="0" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C211" s="0" t="s">
         <v>11</v>
@@ -7458,13 +7458,13 @@
         <v>12</v>
       </c>
       <c r="E211" s="0" t="s">
-        <v>58</v>
+        <v>317</v>
       </c>
       <c r="F211" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G211" s="0" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H211" s="0" t="s">
         <v>16</v>
@@ -7472,25 +7472,25 @@
     </row>
     <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="0" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B212" s="0" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C212" s="0" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D212" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E212" s="0" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F212" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G212" s="0" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H212" s="0" t="s">
         <v>16</v>
@@ -7498,25 +7498,25 @@
     </row>
     <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="0" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B213" s="0" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C213" s="0" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D213" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E213" s="0" t="s">
-        <v>319</v>
+        <v>172</v>
       </c>
       <c r="F213" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G213" s="0" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H213" s="0" t="s">
         <v>16</v>
@@ -7524,10 +7524,10 @@
     </row>
     <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="0" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B214" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C214" s="0" t="s">
         <v>11</v>
@@ -7536,13 +7536,13 @@
         <v>12</v>
       </c>
       <c r="E214" s="0" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F214" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G214" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H214" s="0" t="s">
         <v>16</v>
@@ -7550,10 +7550,10 @@
     </row>
     <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B215" s="0" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C215" s="0" t="s">
         <v>11</v>
@@ -7562,13 +7562,13 @@
         <v>12</v>
       </c>
       <c r="E215" s="0" t="s">
-        <v>175</v>
+        <v>321</v>
       </c>
       <c r="F215" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G215" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H215" s="0" t="s">
         <v>16</v>
@@ -7576,25 +7576,25 @@
     </row>
     <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B216" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C216" s="0" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D216" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E216" s="0" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F216" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G216" s="0" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H216" s="0" t="s">
         <v>16</v>
@@ -7602,10 +7602,10 @@
     </row>
     <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="0" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B217" s="0" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C217" s="0" t="s">
         <v>34</v>
@@ -7614,13 +7614,13 @@
         <v>12</v>
       </c>
       <c r="E217" s="0" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F217" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G217" s="0" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H217" s="0" t="s">
         <v>16</v>
@@ -7628,25 +7628,25 @@
     </row>
     <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="0" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B218" s="0" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C218" s="0" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D218" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E218" s="0" t="s">
-        <v>323</v>
+        <v>303</v>
       </c>
       <c r="F218" s="0" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="G218" s="0" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H218" s="0" t="s">
         <v>16</v>
@@ -7654,10 +7654,10 @@
     </row>
     <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="0" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B219" s="0" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C219" s="0" t="s">
         <v>11</v>
@@ -7666,13 +7666,13 @@
         <v>12</v>
       </c>
       <c r="E219" s="0" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F219" s="0" t="s">
         <v>76</v>
       </c>
       <c r="G219" s="0" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H219" s="0" t="s">
         <v>16</v>
@@ -7680,10 +7680,10 @@
     </row>
     <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="0" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B220" s="0" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C220" s="0" t="s">
         <v>11</v>
@@ -7692,13 +7692,13 @@
         <v>12</v>
       </c>
       <c r="E220" s="0" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F220" s="0" t="s">
         <v>76</v>
       </c>
       <c r="G220" s="0" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H220" s="0" t="s">
         <v>16</v>
@@ -7706,10 +7706,10 @@
     </row>
     <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="0" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B221" s="0" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C221" s="0" t="s">
         <v>11</v>
@@ -7718,13 +7718,13 @@
         <v>12</v>
       </c>
       <c r="E221" s="0" t="s">
-        <v>305</v>
+        <v>75</v>
       </c>
       <c r="F221" s="0" t="s">
         <v>76</v>
       </c>
       <c r="G221" s="0" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H221" s="0" t="s">
         <v>16</v>
@@ -7732,10 +7732,10 @@
     </row>
     <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="0" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B222" s="0" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C222" s="0" t="s">
         <v>11</v>
@@ -7750,7 +7750,7 @@
         <v>76</v>
       </c>
       <c r="G222" s="0" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H222" s="0" t="s">
         <v>16</v>
@@ -7758,10 +7758,10 @@
     </row>
     <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="0" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B223" s="0" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C223" s="0" t="s">
         <v>11</v>
@@ -7770,13 +7770,13 @@
         <v>12</v>
       </c>
       <c r="E223" s="0" t="s">
-        <v>75</v>
+        <v>207</v>
       </c>
       <c r="F223" s="0" t="s">
         <v>76</v>
       </c>
       <c r="G223" s="0" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H223" s="0" t="s">
         <v>16</v>
@@ -7784,10 +7784,10 @@
     </row>
     <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="0" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B224" s="0" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C224" s="0" t="s">
         <v>11</v>
@@ -7796,13 +7796,13 @@
         <v>12</v>
       </c>
       <c r="E224" s="0" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F224" s="0" t="s">
         <v>76</v>
       </c>
       <c r="G224" s="0" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H224" s="0" t="s">
         <v>16</v>
@@ -7810,10 +7810,10 @@
     </row>
     <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="0" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B225" s="0" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C225" s="0" t="s">
         <v>11</v>
@@ -7822,13 +7822,13 @@
         <v>12</v>
       </c>
       <c r="E225" s="0" t="s">
-        <v>210</v>
+        <v>723</v>
       </c>
       <c r="F225" s="0" t="s">
         <v>76</v>
       </c>
       <c r="G225" s="0" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="H225" s="0" t="s">
         <v>16</v>
@@ -7836,10 +7836,10 @@
     </row>
     <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="0" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="B226" s="0" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C226" s="0" t="s">
         <v>11</v>
@@ -7848,13 +7848,13 @@
         <v>12</v>
       </c>
       <c r="E226" s="0" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="F226" s="0" t="s">
         <v>76</v>
       </c>
       <c r="G226" s="0" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="H226" s="0" t="s">
         <v>16</v>
@@ -7862,10 +7862,10 @@
     </row>
     <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="0" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B227" s="0" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C227" s="0" t="s">
         <v>11</v>
@@ -7874,13 +7874,13 @@
         <v>12</v>
       </c>
       <c r="E227" s="0" t="s">
-        <v>729</v>
+        <v>279</v>
       </c>
       <c r="F227" s="0" t="s">
-        <v>76</v>
+        <v>251</v>
       </c>
       <c r="G227" s="0" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H227" s="0" t="s">
         <v>16</v>
@@ -7888,10 +7888,10 @@
     </row>
     <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="0" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B228" s="0" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C228" s="0" t="s">
         <v>11</v>
@@ -7900,13 +7900,13 @@
         <v>12</v>
       </c>
       <c r="E228" s="0" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="F228" s="0" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="G228" s="0" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H228" s="0" t="s">
         <v>16</v>
@@ -7914,10 +7914,10 @@
     </row>
     <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="0" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B229" s="0" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C229" s="0" t="s">
         <v>11</v>
@@ -7926,13 +7926,13 @@
         <v>12</v>
       </c>
       <c r="E229" s="0" t="s">
-        <v>295</v>
+        <v>250</v>
       </c>
       <c r="F229" s="0" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="G229" s="0" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H229" s="0" t="s">
         <v>16</v>
@@ -7940,10 +7940,10 @@
     </row>
     <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="0" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B230" s="0" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C230" s="0" t="s">
         <v>11</v>
@@ -7952,13 +7952,13 @@
         <v>12</v>
       </c>
       <c r="E230" s="0" t="s">
-        <v>253</v>
+        <v>740</v>
       </c>
       <c r="F230" s="0" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="G230" s="0" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="H230" s="0" t="s">
         <v>16</v>
@@ -7966,10 +7966,10 @@
     </row>
     <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="0" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B231" s="0" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C231" s="0" t="s">
         <v>11</v>
@@ -7978,13 +7978,13 @@
         <v>12</v>
       </c>
       <c r="E231" s="0" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="F231" s="0" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="G231" s="0" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H231" s="0" t="s">
         <v>16</v>
@@ -7992,10 +7992,10 @@
     </row>
     <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="0" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B232" s="0" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C232" s="0" t="s">
         <v>11</v>
@@ -8004,13 +8004,13 @@
         <v>12</v>
       </c>
       <c r="E232" s="0" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="F232" s="0" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="G232" s="0" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="H232" s="0" t="s">
         <v>16</v>
@@ -8018,10 +8018,10 @@
     </row>
     <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="0" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B233" s="0" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C233" s="0" t="s">
         <v>11</v>
@@ -8030,13 +8030,13 @@
         <v>12</v>
       </c>
       <c r="E233" s="0" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="F233" s="0" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G233" s="0" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H233" s="0" t="s">
         <v>16</v>
@@ -8044,10 +8044,10 @@
     </row>
     <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="0" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B234" s="0" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C234" s="0" t="s">
         <v>11</v>
@@ -8056,13 +8056,13 @@
         <v>12</v>
       </c>
       <c r="E234" s="0" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="F234" s="0" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G234" s="0" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H234" s="0" t="s">
         <v>16</v>
@@ -8070,10 +8070,10 @@
     </row>
     <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="0" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B235" s="0" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C235" s="0" t="s">
         <v>11</v>
@@ -8082,13 +8082,13 @@
         <v>12</v>
       </c>
       <c r="E235" s="0" t="s">
-        <v>749</v>
+        <v>313</v>
       </c>
       <c r="F235" s="0" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G235" s="0" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H235" s="0" t="s">
         <v>16</v>
@@ -8096,10 +8096,10 @@
     </row>
     <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="0" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B236" s="0" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C236" s="0" t="s">
         <v>11</v>
@@ -8108,13 +8108,13 @@
         <v>12</v>
       </c>
       <c r="E236" s="0" t="s">
-        <v>315</v>
+        <v>258</v>
       </c>
       <c r="F236" s="0" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G236" s="0" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H236" s="0" t="s">
         <v>16</v>
@@ -8122,10 +8122,10 @@
     </row>
     <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="0" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B237" s="0" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C237" s="0" t="s">
         <v>11</v>
@@ -8134,13 +8134,13 @@
         <v>12</v>
       </c>
       <c r="E237" s="0" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F237" s="0" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G237" s="0" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H237" s="0" t="s">
         <v>16</v>
@@ -8148,10 +8148,10 @@
     </row>
     <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="0" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B238" s="0" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C238" s="0" t="s">
         <v>11</v>
@@ -8160,13 +8160,13 @@
         <v>12</v>
       </c>
       <c r="E238" s="0" t="s">
-        <v>260</v>
+        <v>766</v>
       </c>
       <c r="F238" s="0" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G238" s="0" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="H238" s="0" t="s">
         <v>16</v>
@@ -8174,10 +8174,10 @@
     </row>
     <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="0" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="B239" s="0" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C239" s="0" t="s">
         <v>11</v>
@@ -8186,13 +8186,13 @@
         <v>12</v>
       </c>
       <c r="E239" s="0" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="F239" s="0" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G239" s="0" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H239" s="0" t="s">
         <v>16</v>
@@ -8200,10 +8200,10 @@
     </row>
     <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="0" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B240" s="0" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C240" s="0" t="s">
         <v>11</v>
@@ -8212,13 +8212,13 @@
         <v>12</v>
       </c>
       <c r="E240" s="0" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="F240" s="0" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G240" s="0" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="H240" s="0" t="s">
         <v>16</v>
@@ -8226,25 +8226,25 @@
     </row>
     <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="0" t="s">
+        <v>775</v>
+      </c>
+      <c r="B241" s="0" t="s">
+        <v>776</v>
+      </c>
+      <c r="C241" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="D241" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="E241" s="0" t="s">
         <v>773</v>
       </c>
-      <c r="B241" s="0" t="s">
-        <v>774</v>
-      </c>
-      <c r="C241" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="D241" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E241" s="0" t="s">
-        <v>775</v>
-      </c>
       <c r="F241" s="0" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G241" s="0" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H241" s="0" t="s">
         <v>16</v>
@@ -8252,25 +8252,25 @@
     </row>
     <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="0" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B242" s="0" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C242" s="0" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D242" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E242" s="0" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="F242" s="0" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G242" s="0" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="H242" s="0" t="s">
         <v>16</v>
@@ -8278,25 +8278,25 @@
     </row>
     <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="0" t="s">
+        <v>782</v>
+      </c>
+      <c r="B243" s="0" t="s">
+        <v>783</v>
+      </c>
+      <c r="C243" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="D243" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="E243" s="0" t="s">
         <v>780</v>
       </c>
-      <c r="B243" s="0" t="s">
-        <v>781</v>
-      </c>
-      <c r="C243" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="D243" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E243" s="0" t="s">
-        <v>782</v>
-      </c>
       <c r="F243" s="0" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G243" s="0" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H243" s="0" t="s">
         <v>16</v>
@@ -8304,25 +8304,25 @@
     </row>
     <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="0" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B244" s="0" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C244" s="0" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D244" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E244" s="0" t="s">
-        <v>782</v>
+        <v>162</v>
       </c>
       <c r="F244" s="0" t="s">
-        <v>261</v>
+        <v>162</v>
       </c>
       <c r="G244" s="0" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H244" s="0" t="s">
         <v>16</v>
@@ -8330,10 +8330,10 @@
     </row>
     <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="0" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B245" s="0" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C245" s="0" t="s">
         <v>11</v>
@@ -8342,13 +8342,13 @@
         <v>12</v>
       </c>
       <c r="E245" s="0" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F245" s="0" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G245" s="0" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H245" s="0" t="s">
         <v>16</v>
@@ -8356,10 +8356,10 @@
     </row>
     <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="0" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B246" s="0" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C246" s="0" t="s">
         <v>11</v>
@@ -8368,13 +8368,13 @@
         <v>12</v>
       </c>
       <c r="E246" s="0" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F246" s="0" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G246" s="0" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H246" s="0" t="s">
         <v>16</v>
@@ -8382,10 +8382,10 @@
     </row>
     <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="0" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B247" s="0" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C247" s="0" t="s">
         <v>11</v>
@@ -8394,13 +8394,13 @@
         <v>12</v>
       </c>
       <c r="E247" s="0" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F247" s="0" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G247" s="0" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H247" s="0" t="s">
         <v>16</v>
@@ -8408,10 +8408,10 @@
     </row>
     <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="0" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B248" s="0" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C248" s="0" t="s">
         <v>11</v>
@@ -8420,13 +8420,13 @@
         <v>12</v>
       </c>
       <c r="E248" s="0" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F248" s="0" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G248" s="0" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H248" s="0" t="s">
         <v>16</v>
@@ -8434,25 +8434,25 @@
     </row>
     <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="0" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B249" s="0" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C249" s="0" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D249" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E249" s="0" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F249" s="0" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G249" s="0" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H249" s="0" t="s">
         <v>16</v>
@@ -8460,10 +8460,10 @@
     </row>
     <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="0" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B250" s="0" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C250" s="0" t="s">
         <v>34</v>
@@ -8472,13 +8472,13 @@
         <v>12</v>
       </c>
       <c r="E250" s="0" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F250" s="0" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G250" s="0" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H250" s="0" t="s">
         <v>16</v>
@@ -8486,25 +8486,25 @@
     </row>
     <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="0" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B251" s="0" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C251" s="0" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D251" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E251" s="0" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F251" s="0" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G251" s="0" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H251" s="0" t="s">
         <v>16</v>
@@ -8512,10 +8512,10 @@
     </row>
     <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="0" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B252" s="0" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C252" s="0" t="s">
         <v>11</v>
@@ -8524,13 +8524,13 @@
         <v>12</v>
       </c>
       <c r="E252" s="0" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F252" s="0" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G252" s="0" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H252" s="0" t="s">
         <v>16</v>
@@ -8538,10 +8538,10 @@
     </row>
     <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="0" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B253" s="0" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C253" s="0" t="s">
         <v>11</v>
@@ -8550,13 +8550,13 @@
         <v>12</v>
       </c>
       <c r="E253" s="0" t="s">
-        <v>165</v>
+        <v>814</v>
       </c>
       <c r="F253" s="0" t="s">
-        <v>165</v>
+        <v>814</v>
       </c>
       <c r="G253" s="0" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="H253" s="0" t="s">
         <v>16</v>
@@ -8564,10 +8564,10 @@
     </row>
     <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="0" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B254" s="0" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="C254" s="0" t="s">
         <v>11</v>
@@ -8576,13 +8576,13 @@
         <v>12</v>
       </c>
       <c r="E254" s="0" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="F254" s="0" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="G254" s="0" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H254" s="0" t="s">
         <v>16</v>
@@ -8590,25 +8590,25 @@
     </row>
     <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="0" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B255" s="0" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C255" s="0" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D255" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E255" s="0" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="F255" s="0" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="G255" s="0" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H255" s="0" t="s">
         <v>16</v>
@@ -8616,25 +8616,25 @@
     </row>
     <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="0" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B256" s="0" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C256" s="0" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D256" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E256" s="0" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="F256" s="0" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="G256" s="0" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H256" s="0" t="s">
         <v>16</v>
@@ -8642,10 +8642,10 @@
     </row>
     <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="0" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B257" s="0" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C257" s="0" t="s">
         <v>11</v>
@@ -8654,13 +8654,13 @@
         <v>12</v>
       </c>
       <c r="E257" s="0" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="F257" s="0" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="G257" s="0" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H257" s="0" t="s">
         <v>16</v>
@@ -8668,25 +8668,25 @@
     </row>
     <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="0" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B258" s="0" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C258" s="0" t="s">
-        <v>11</v>
+        <v>830</v>
       </c>
       <c r="D258" s="0" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="E258" s="0" t="s">
-        <v>816</v>
+        <v>13</v>
       </c>
       <c r="F258" s="0" t="s">
-        <v>816</v>
+        <v>14</v>
       </c>
       <c r="G258" s="0" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="H258" s="0" t="s">
         <v>16</v>
@@ -8694,25 +8694,25 @@
     </row>
     <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="0" t="s">
+        <v>832</v>
+      </c>
+      <c r="B259" s="0" t="s">
+        <v>833</v>
+      </c>
+      <c r="C259" s="0" t="s">
         <v>830</v>
-      </c>
-      <c r="B259" s="0" t="s">
-        <v>831</v>
-      </c>
-      <c r="C259" s="0" t="s">
-        <v>832</v>
       </c>
       <c r="D259" s="0" t="s">
         <v>45</v>
       </c>
       <c r="E259" s="0" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F259" s="0" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G259" s="0" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H259" s="0" t="s">
         <v>16</v>
@@ -8720,25 +8720,25 @@
     </row>
     <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="0" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B260" s="0" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C260" s="0" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="D260" s="0" t="s">
         <v>45</v>
       </c>
       <c r="E260" s="0" t="s">
-        <v>29</v>
+        <v>234</v>
       </c>
       <c r="F260" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G260" s="0" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="H260" s="0" t="s">
         <v>16</v>
@@ -8746,25 +8746,25 @@
     </row>
     <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="0" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B261" s="0" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="C261" s="0" t="s">
-        <v>839</v>
+        <v>830</v>
       </c>
       <c r="D261" s="0" t="s">
         <v>45</v>
       </c>
       <c r="E261" s="0" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="F261" s="0" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G261" s="0" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H261" s="0" t="s">
         <v>16</v>
@@ -8772,53 +8772,27 @@
     </row>
     <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="0" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B262" s="0" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C262" s="0" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="D262" s="0" t="s">
         <v>45</v>
       </c>
       <c r="E262" s="0" t="s">
-        <v>246</v>
+        <v>13</v>
       </c>
       <c r="F262" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G262" s="0" t="s">
-        <v>843</v>
+        <v>612</v>
       </c>
       <c r="H262" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="0" t="s">
-        <v>844</v>
-      </c>
-      <c r="B263" s="0" t="s">
-        <v>845</v>
-      </c>
-      <c r="C263" s="0" t="s">
-        <v>832</v>
-      </c>
-      <c r="D263" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="E263" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F263" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="G263" s="0" t="s">
-        <v>614</v>
-      </c>
-      <c r="H263" s="0" t="s">
         <v>16</v>
       </c>
     </row>

--- a/reports/manual_image_qa.xlsx
+++ b/reports/manual_image_qa.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1835" uniqueCount="844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1829" uniqueCount="841">
   <si>
     <t xml:space="preserve">Destination ID</t>
   </si>
@@ -1097,15 +1097,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/4/4a/Odaiba_close_up_-_2025_Jan_14_01-27PM.jpeg/3840px-Odaiba_close_up_-_2025_Jan_14_01-27PM.jpeg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">odawara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Odawara &amp; Manazuru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/3/38/Aerial_views_of_Odawara_Japan.jpg/250px-Aerial_views_of_Odawara_Japan.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">okuhida</t>
@@ -2753,7 +2744,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I262"/>
+  <dimension ref="A1:I261"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.39"/>
@@ -4878,10 +4869,10 @@
         <v>360</v>
       </c>
       <c r="E103" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F103" s="0" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G103" s="0" t="s">
         <v>361</v>
@@ -4898,10 +4889,10 @@
         <v>363</v>
       </c>
       <c r="E104" s="0" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="F104" s="0" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G104" s="0" t="s">
         <v>364</v>
@@ -4918,7 +4909,7 @@
         <v>366</v>
       </c>
       <c r="E105" s="0" t="s">
-        <v>29</v>
+        <v>230</v>
       </c>
       <c r="F105" s="0" t="s">
         <v>30</v>
@@ -4938,10 +4929,10 @@
         <v>369</v>
       </c>
       <c r="E106" s="0" t="s">
-        <v>230</v>
+        <v>24</v>
       </c>
       <c r="F106" s="0" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G106" s="0" t="s">
         <v>370</v>
@@ -4958,10 +4949,10 @@
         <v>372</v>
       </c>
       <c r="E107" s="0" t="s">
-        <v>24</v>
+        <v>146</v>
       </c>
       <c r="F107" s="0" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G107" s="0" t="s">
         <v>373</v>
@@ -4978,7 +4969,7 @@
         <v>375</v>
       </c>
       <c r="E108" s="0" t="s">
-        <v>146</v>
+        <v>29</v>
       </c>
       <c r="F108" s="0" t="s">
         <v>30</v>
@@ -4998,10 +4989,10 @@
         <v>378</v>
       </c>
       <c r="E109" s="0" t="s">
-        <v>29</v>
+        <v>124</v>
       </c>
       <c r="F109" s="0" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G109" s="0" t="s">
         <v>379</v>
@@ -5017,11 +5008,17 @@
       <c r="B110" s="0" t="s">
         <v>381</v>
       </c>
+      <c r="C110" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="D110" s="0" t="s">
+        <v>12</v>
+      </c>
       <c r="E110" s="0" t="s">
-        <v>124</v>
+        <v>230</v>
       </c>
       <c r="F110" s="0" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G110" s="0" t="s">
         <v>382</v>
@@ -5037,12 +5034,6 @@
       <c r="B111" s="0" t="s">
         <v>384</v>
       </c>
-      <c r="C111" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="D111" s="0" t="s">
-        <v>12</v>
-      </c>
       <c r="E111" s="0" t="s">
         <v>230</v>
       </c>
@@ -5064,7 +5055,7 @@
         <v>387</v>
       </c>
       <c r="E112" s="0" t="s">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="F112" s="0" t="s">
         <v>30</v>
@@ -5084,7 +5075,7 @@
         <v>390</v>
       </c>
       <c r="E113" s="0" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="F113" s="0" t="s">
         <v>30</v>
@@ -5164,10 +5155,10 @@
         <v>402</v>
       </c>
       <c r="E117" s="0" t="s">
-        <v>29</v>
+        <v>263</v>
       </c>
       <c r="F117" s="0" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G117" s="0" t="s">
         <v>403</v>
@@ -5184,7 +5175,7 @@
         <v>405</v>
       </c>
       <c r="E118" s="0" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="F118" s="0" t="s">
         <v>14</v>
@@ -5204,7 +5195,7 @@
         <v>408</v>
       </c>
       <c r="E119" s="0" t="s">
-        <v>243</v>
+        <v>117</v>
       </c>
       <c r="F119" s="0" t="s">
         <v>14</v>
@@ -5224,10 +5215,10 @@
         <v>411</v>
       </c>
       <c r="E120" s="0" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="F120" s="0" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G120" s="0" t="s">
         <v>412</v>
@@ -5244,10 +5235,10 @@
         <v>414</v>
       </c>
       <c r="E121" s="0" t="s">
-        <v>29</v>
+        <v>124</v>
       </c>
       <c r="F121" s="0" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G121" s="0" t="s">
         <v>415</v>
@@ -5264,10 +5255,10 @@
         <v>417</v>
       </c>
       <c r="E122" s="0" t="s">
-        <v>124</v>
+        <v>29</v>
       </c>
       <c r="F122" s="0" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G122" s="0" t="s">
         <v>418</v>
@@ -5404,10 +5395,10 @@
         <v>438</v>
       </c>
       <c r="E129" s="0" t="s">
-        <v>29</v>
+        <v>263</v>
       </c>
       <c r="F129" s="0" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G129" s="0" t="s">
         <v>439</v>
@@ -5424,7 +5415,7 @@
         <v>441</v>
       </c>
       <c r="E130" s="0" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="F130" s="0" t="s">
         <v>14</v>
@@ -5444,10 +5435,10 @@
         <v>444</v>
       </c>
       <c r="E131" s="0" t="s">
-        <v>243</v>
+        <v>29</v>
       </c>
       <c r="F131" s="0" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G131" s="0" t="s">
         <v>445</v>
@@ -5464,7 +5455,7 @@
         <v>447</v>
       </c>
       <c r="E132" s="0" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="F132" s="0" t="s">
         <v>30</v>
@@ -5484,7 +5475,7 @@
         <v>450</v>
       </c>
       <c r="E133" s="0" t="s">
-        <v>62</v>
+        <v>234</v>
       </c>
       <c r="F133" s="0" t="s">
         <v>30</v>
@@ -5504,10 +5495,10 @@
         <v>453</v>
       </c>
       <c r="E134" s="0" t="s">
-        <v>234</v>
+        <v>293</v>
       </c>
       <c r="F134" s="0" t="s">
-        <v>30</v>
+        <v>251</v>
       </c>
       <c r="G134" s="0" t="s">
         <v>454</v>
@@ -5524,13 +5515,13 @@
         <v>456</v>
       </c>
       <c r="E135" s="0" t="s">
-        <v>293</v>
+        <v>117</v>
       </c>
       <c r="F135" s="0" t="s">
-        <v>251</v>
+        <v>14</v>
       </c>
       <c r="G135" s="0" t="s">
-        <v>457</v>
+        <v>169</v>
       </c>
       <c r="H135" s="0" t="s">
         <v>16</v>
@@ -5538,10 +5529,10 @@
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="0" t="s">
+        <v>457</v>
+      </c>
+      <c r="B136" s="0" t="s">
         <v>458</v>
-      </c>
-      <c r="B136" s="0" t="s">
-        <v>459</v>
       </c>
       <c r="E136" s="0" t="s">
         <v>117</v>
@@ -5550,7 +5541,7 @@
         <v>14</v>
       </c>
       <c r="G136" s="0" t="s">
-        <v>169</v>
+        <v>96</v>
       </c>
       <c r="H136" s="0" t="s">
         <v>16</v>
@@ -5558,10 +5549,10 @@
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="0" t="s">
+        <v>459</v>
+      </c>
+      <c r="B137" s="0" t="s">
         <v>460</v>
-      </c>
-      <c r="B137" s="0" t="s">
-        <v>461</v>
       </c>
       <c r="E137" s="0" t="s">
         <v>117</v>
@@ -5570,7 +5561,7 @@
         <v>14</v>
       </c>
       <c r="G137" s="0" t="s">
-        <v>96</v>
+        <v>461</v>
       </c>
       <c r="H137" s="0" t="s">
         <v>16</v>
@@ -5583,11 +5574,17 @@
       <c r="B138" s="0" t="s">
         <v>463</v>
       </c>
+      <c r="C138" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="D138" s="0" t="s">
+        <v>12</v>
+      </c>
       <c r="E138" s="0" t="s">
-        <v>117</v>
+        <v>35</v>
       </c>
       <c r="F138" s="0" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G138" s="0" t="s">
         <v>464</v>
@@ -5603,12 +5600,6 @@
       <c r="B139" s="0" t="s">
         <v>466</v>
       </c>
-      <c r="C139" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="D139" s="0" t="s">
-        <v>12</v>
-      </c>
       <c r="E139" s="0" t="s">
         <v>35</v>
       </c>
@@ -5650,7 +5641,7 @@
         <v>472</v>
       </c>
       <c r="E141" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F141" s="0" t="s">
         <v>30</v>
@@ -5670,7 +5661,7 @@
         <v>475</v>
       </c>
       <c r="E142" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F142" s="0" t="s">
         <v>30</v>
@@ -5689,8 +5680,14 @@
       <c r="B143" s="0" t="s">
         <v>478</v>
       </c>
+      <c r="C143" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D143" s="0" t="s">
+        <v>12</v>
+      </c>
       <c r="E143" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F143" s="0" t="s">
         <v>30</v>
@@ -5722,7 +5719,7 @@
         <v>30</v>
       </c>
       <c r="G144" s="0" t="s">
-        <v>482</v>
+        <v>143</v>
       </c>
       <c r="H144" s="0" t="s">
         <v>16</v>
@@ -5730,10 +5727,10 @@
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="0" t="s">
+        <v>482</v>
+      </c>
+      <c r="B145" s="0" t="s">
         <v>483</v>
-      </c>
-      <c r="B145" s="0" t="s">
-        <v>484</v>
       </c>
       <c r="C145" s="0" t="s">
         <v>28</v>
@@ -5748,7 +5745,7 @@
         <v>30</v>
       </c>
       <c r="G145" s="0" t="s">
-        <v>143</v>
+        <v>484</v>
       </c>
       <c r="H145" s="0" t="s">
         <v>16</v>
@@ -5852,7 +5849,7 @@
         <v>30</v>
       </c>
       <c r="G149" s="0" t="s">
-        <v>496</v>
+        <v>430</v>
       </c>
       <c r="H149" s="0" t="s">
         <v>16</v>
@@ -5860,10 +5857,10 @@
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="0" t="s">
+        <v>496</v>
+      </c>
+      <c r="B150" s="0" t="s">
         <v>497</v>
-      </c>
-      <c r="B150" s="0" t="s">
-        <v>498</v>
       </c>
       <c r="C150" s="0" t="s">
         <v>28</v>
@@ -5878,7 +5875,7 @@
         <v>30</v>
       </c>
       <c r="G150" s="0" t="s">
-        <v>433</v>
+        <v>498</v>
       </c>
       <c r="H150" s="0" t="s">
         <v>16</v>
@@ -6256,13 +6253,13 @@
         <v>542</v>
       </c>
       <c r="C165" s="0" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D165" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E165" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F165" s="0" t="s">
         <v>30</v>
@@ -6444,7 +6441,7 @@
         <v>12</v>
       </c>
       <c r="E172" s="0" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="F172" s="0" t="s">
         <v>30</v>
@@ -6574,7 +6571,7 @@
         <v>12</v>
       </c>
       <c r="E177" s="0" t="s">
-        <v>80</v>
+        <v>230</v>
       </c>
       <c r="F177" s="0" t="s">
         <v>30</v>
@@ -6678,7 +6675,7 @@
         <v>12</v>
       </c>
       <c r="E181" s="0" t="s">
-        <v>230</v>
+        <v>62</v>
       </c>
       <c r="F181" s="0" t="s">
         <v>30</v>
@@ -6730,7 +6727,7 @@
         <v>12</v>
       </c>
       <c r="E183" s="0" t="s">
-        <v>62</v>
+        <v>234</v>
       </c>
       <c r="F183" s="0" t="s">
         <v>30</v>
@@ -6776,13 +6773,13 @@
         <v>602</v>
       </c>
       <c r="C185" s="0" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D185" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E185" s="0" t="s">
-        <v>234</v>
+        <v>146</v>
       </c>
       <c r="F185" s="0" t="s">
         <v>30</v>
@@ -6828,16 +6825,16 @@
         <v>608</v>
       </c>
       <c r="C187" s="0" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D187" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E187" s="0" t="s">
-        <v>146</v>
+        <v>13</v>
       </c>
       <c r="F187" s="0" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G187" s="0" t="s">
         <v>609</v>
@@ -6912,7 +6909,7 @@
         <v>12</v>
       </c>
       <c r="E190" s="0" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="F190" s="0" t="s">
         <v>14</v>
@@ -6990,7 +6987,7 @@
         <v>12</v>
       </c>
       <c r="E193" s="0" t="s">
-        <v>40</v>
+        <v>203</v>
       </c>
       <c r="F193" s="0" t="s">
         <v>14</v>
@@ -7172,7 +7169,7 @@
         <v>12</v>
       </c>
       <c r="E200" s="0" t="s">
-        <v>203</v>
+        <v>117</v>
       </c>
       <c r="F200" s="0" t="s">
         <v>14</v>
@@ -7192,7 +7189,7 @@
         <v>650</v>
       </c>
       <c r="C201" s="0" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D201" s="0" t="s">
         <v>12</v>
@@ -7218,13 +7215,13 @@
         <v>653</v>
       </c>
       <c r="C202" s="0" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D202" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E202" s="0" t="s">
-        <v>117</v>
+        <v>243</v>
       </c>
       <c r="F202" s="0" t="s">
         <v>14</v>
@@ -7244,7 +7241,7 @@
         <v>656</v>
       </c>
       <c r="C203" s="0" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D203" s="0" t="s">
         <v>12</v>
@@ -7270,7 +7267,7 @@
         <v>659</v>
       </c>
       <c r="C204" s="0" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D204" s="0" t="s">
         <v>12</v>
@@ -7296,16 +7293,16 @@
         <v>662</v>
       </c>
       <c r="C205" s="0" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D205" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E205" s="0" t="s">
-        <v>243</v>
+        <v>19</v>
       </c>
       <c r="F205" s="0" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G205" s="0" t="s">
         <v>663</v>
@@ -7354,7 +7351,7 @@
         <v>12</v>
       </c>
       <c r="E207" s="0" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F207" s="0" t="s">
         <v>20</v>
@@ -7380,7 +7377,7 @@
         <v>12</v>
       </c>
       <c r="E208" s="0" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="F208" s="0" t="s">
         <v>20</v>
@@ -7432,7 +7429,7 @@
         <v>12</v>
       </c>
       <c r="E210" s="0" t="s">
-        <v>58</v>
+        <v>317</v>
       </c>
       <c r="F210" s="0" t="s">
         <v>20</v>
@@ -7452,7 +7449,7 @@
         <v>680</v>
       </c>
       <c r="C211" s="0" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D211" s="0" t="s">
         <v>12</v>
@@ -7478,13 +7475,13 @@
         <v>683</v>
       </c>
       <c r="C212" s="0" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D212" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E212" s="0" t="s">
-        <v>317</v>
+        <v>172</v>
       </c>
       <c r="F212" s="0" t="s">
         <v>20</v>
@@ -7536,7 +7533,7 @@
         <v>12</v>
       </c>
       <c r="E214" s="0" t="s">
-        <v>172</v>
+        <v>321</v>
       </c>
       <c r="F214" s="0" t="s">
         <v>20</v>
@@ -7556,7 +7553,7 @@
         <v>692</v>
       </c>
       <c r="C215" s="0" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D215" s="0" t="s">
         <v>12</v>
@@ -7608,16 +7605,16 @@
         <v>698</v>
       </c>
       <c r="C217" s="0" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D217" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E217" s="0" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="F217" s="0" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="G217" s="0" t="s">
         <v>699</v>
@@ -7692,7 +7689,7 @@
         <v>12</v>
       </c>
       <c r="E220" s="0" t="s">
-        <v>303</v>
+        <v>75</v>
       </c>
       <c r="F220" s="0" t="s">
         <v>76</v>
@@ -7744,7 +7741,7 @@
         <v>12</v>
       </c>
       <c r="E222" s="0" t="s">
-        <v>75</v>
+        <v>207</v>
       </c>
       <c r="F222" s="0" t="s">
         <v>76</v>
@@ -7796,13 +7793,13 @@
         <v>12</v>
       </c>
       <c r="E224" s="0" t="s">
-        <v>207</v>
+        <v>720</v>
       </c>
       <c r="F224" s="0" t="s">
         <v>76</v>
       </c>
       <c r="G224" s="0" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H224" s="0" t="s">
         <v>16</v>
@@ -7810,10 +7807,10 @@
     </row>
     <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="0" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B225" s="0" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C225" s="0" t="s">
         <v>11</v>
@@ -7822,13 +7819,13 @@
         <v>12</v>
       </c>
       <c r="E225" s="0" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="F225" s="0" t="s">
         <v>76</v>
       </c>
       <c r="G225" s="0" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H225" s="0" t="s">
         <v>16</v>
@@ -7836,10 +7833,10 @@
     </row>
     <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="0" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B226" s="0" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C226" s="0" t="s">
         <v>11</v>
@@ -7848,10 +7845,10 @@
         <v>12</v>
       </c>
       <c r="E226" s="0" t="s">
-        <v>727</v>
+        <v>279</v>
       </c>
       <c r="F226" s="0" t="s">
-        <v>76</v>
+        <v>251</v>
       </c>
       <c r="G226" s="0" t="s">
         <v>728</v>
@@ -7874,7 +7871,7 @@
         <v>12</v>
       </c>
       <c r="E227" s="0" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="F227" s="0" t="s">
         <v>251</v>
@@ -7900,7 +7897,7 @@
         <v>12</v>
       </c>
       <c r="E228" s="0" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="F228" s="0" t="s">
         <v>251</v>
@@ -7926,13 +7923,13 @@
         <v>12</v>
       </c>
       <c r="E229" s="0" t="s">
-        <v>250</v>
+        <v>737</v>
       </c>
       <c r="F229" s="0" t="s">
         <v>251</v>
       </c>
       <c r="G229" s="0" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H229" s="0" t="s">
         <v>16</v>
@@ -7940,10 +7937,10 @@
     </row>
     <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="0" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B230" s="0" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C230" s="0" t="s">
         <v>11</v>
@@ -7952,7 +7949,7 @@
         <v>12</v>
       </c>
       <c r="E230" s="0" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="F230" s="0" t="s">
         <v>251</v>
@@ -7978,13 +7975,13 @@
         <v>12</v>
       </c>
       <c r="E231" s="0" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="F231" s="0" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="G231" s="0" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H231" s="0" t="s">
         <v>16</v>
@@ -7992,10 +7989,10 @@
     </row>
     <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="0" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B232" s="0" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C232" s="0" t="s">
         <v>11</v>
@@ -8004,7 +8001,7 @@
         <v>12</v>
       </c>
       <c r="E232" s="0" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="F232" s="0" t="s">
         <v>259</v>
@@ -8030,7 +8027,7 @@
         <v>12</v>
       </c>
       <c r="E233" s="0" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="F233" s="0" t="s">
         <v>259</v>
@@ -8056,7 +8053,7 @@
         <v>12</v>
       </c>
       <c r="E234" s="0" t="s">
-        <v>747</v>
+        <v>313</v>
       </c>
       <c r="F234" s="0" t="s">
         <v>259</v>
@@ -8082,7 +8079,7 @@
         <v>12</v>
       </c>
       <c r="E235" s="0" t="s">
-        <v>313</v>
+        <v>258</v>
       </c>
       <c r="F235" s="0" t="s">
         <v>259</v>
@@ -8134,13 +8131,13 @@
         <v>12</v>
       </c>
       <c r="E237" s="0" t="s">
-        <v>258</v>
+        <v>763</v>
       </c>
       <c r="F237" s="0" t="s">
         <v>259</v>
       </c>
       <c r="G237" s="0" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H237" s="0" t="s">
         <v>16</v>
@@ -8148,10 +8145,10 @@
     </row>
     <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="0" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B238" s="0" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C238" s="0" t="s">
         <v>11</v>
@@ -8160,7 +8157,7 @@
         <v>12</v>
       </c>
       <c r="E238" s="0" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="F238" s="0" t="s">
         <v>259</v>
@@ -8186,13 +8183,13 @@
         <v>12</v>
       </c>
       <c r="E239" s="0" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="F239" s="0" t="s">
         <v>259</v>
       </c>
       <c r="G239" s="0" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H239" s="0" t="s">
         <v>16</v>
@@ -8200,19 +8197,19 @@
     </row>
     <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="0" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B240" s="0" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C240" s="0" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D240" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E240" s="0" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="F240" s="0" t="s">
         <v>259</v>
@@ -8232,19 +8229,19 @@
         <v>776</v>
       </c>
       <c r="C241" s="0" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D241" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E241" s="0" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="F241" s="0" t="s">
         <v>259</v>
       </c>
       <c r="G241" s="0" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H241" s="0" t="s">
         <v>16</v>
@@ -8252,19 +8249,19 @@
     </row>
     <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="0" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B242" s="0" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C242" s="0" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D242" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E242" s="0" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="F242" s="0" t="s">
         <v>259</v>
@@ -8284,16 +8281,16 @@
         <v>783</v>
       </c>
       <c r="C243" s="0" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D243" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E243" s="0" t="s">
-        <v>780</v>
+        <v>162</v>
       </c>
       <c r="F243" s="0" t="s">
-        <v>259</v>
+        <v>162</v>
       </c>
       <c r="G243" s="0" t="s">
         <v>784</v>
@@ -8414,7 +8411,7 @@
         <v>798</v>
       </c>
       <c r="C248" s="0" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D248" s="0" t="s">
         <v>12</v>
@@ -8466,7 +8463,7 @@
         <v>804</v>
       </c>
       <c r="C250" s="0" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D250" s="0" t="s">
         <v>12</v>
@@ -8524,13 +8521,13 @@
         <v>12</v>
       </c>
       <c r="E252" s="0" t="s">
-        <v>162</v>
+        <v>811</v>
       </c>
       <c r="F252" s="0" t="s">
-        <v>162</v>
+        <v>811</v>
       </c>
       <c r="G252" s="0" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H252" s="0" t="s">
         <v>16</v>
@@ -8538,10 +8535,10 @@
     </row>
     <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="0" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B253" s="0" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C253" s="0" t="s">
         <v>11</v>
@@ -8550,10 +8547,10 @@
         <v>12</v>
       </c>
       <c r="E253" s="0" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="F253" s="0" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="G253" s="0" t="s">
         <v>815</v>
@@ -8570,16 +8567,16 @@
         <v>817</v>
       </c>
       <c r="C254" s="0" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D254" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E254" s="0" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="F254" s="0" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="G254" s="0" t="s">
         <v>818</v>
@@ -8596,16 +8593,16 @@
         <v>820</v>
       </c>
       <c r="C255" s="0" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D255" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E255" s="0" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="F255" s="0" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="G255" s="0" t="s">
         <v>821</v>
@@ -8628,10 +8625,10 @@
         <v>12</v>
       </c>
       <c r="E256" s="0" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="F256" s="0" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="G256" s="0" t="s">
         <v>824</v>
@@ -8648,19 +8645,19 @@
         <v>826</v>
       </c>
       <c r="C257" s="0" t="s">
-        <v>11</v>
+        <v>827</v>
       </c>
       <c r="D257" s="0" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="E257" s="0" t="s">
-        <v>814</v>
+        <v>13</v>
       </c>
       <c r="F257" s="0" t="s">
-        <v>814</v>
+        <v>14</v>
       </c>
       <c r="G257" s="0" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H257" s="0" t="s">
         <v>16</v>
@@ -8668,22 +8665,22 @@
     </row>
     <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="0" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B258" s="0" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C258" s="0" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="D258" s="0" t="s">
         <v>45</v>
       </c>
       <c r="E258" s="0" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F258" s="0" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G258" s="0" t="s">
         <v>831</v>
@@ -8700,19 +8697,19 @@
         <v>833</v>
       </c>
       <c r="C259" s="0" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="D259" s="0" t="s">
         <v>45</v>
       </c>
       <c r="E259" s="0" t="s">
-        <v>29</v>
+        <v>234</v>
       </c>
       <c r="F259" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G259" s="0" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H259" s="0" t="s">
         <v>16</v>
@@ -8720,22 +8717,22 @@
     </row>
     <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="0" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B260" s="0" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C260" s="0" t="s">
-        <v>837</v>
+        <v>827</v>
       </c>
       <c r="D260" s="0" t="s">
         <v>45</v>
       </c>
       <c r="E260" s="0" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="F260" s="0" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G260" s="0" t="s">
         <v>838</v>
@@ -8752,47 +8749,21 @@
         <v>840</v>
       </c>
       <c r="C261" s="0" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="D261" s="0" t="s">
         <v>45</v>
       </c>
       <c r="E261" s="0" t="s">
-        <v>243</v>
+        <v>13</v>
       </c>
       <c r="F261" s="0" t="s">
         <v>14</v>
       </c>
       <c r="G261" s="0" t="s">
-        <v>841</v>
+        <v>609</v>
       </c>
       <c r="H261" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A262" s="0" t="s">
-        <v>842</v>
-      </c>
-      <c r="B262" s="0" t="s">
-        <v>843</v>
-      </c>
-      <c r="C262" s="0" t="s">
-        <v>830</v>
-      </c>
-      <c r="D262" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="E262" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F262" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="G262" s="0" t="s">
-        <v>612</v>
-      </c>
-      <c r="H262" s="0" t="s">
         <v>16</v>
       </c>
     </row>
